--- a/research/traditional_assets/database/data/united_states/united_states_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/united_states/united_states_insurance_general.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ24"/>
+  <dimension ref="A1:AQ23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0487</v>
+        <v>0.0675</v>
       </c>
       <c r="E2">
-        <v>0.183</v>
+        <v>0.09845000000000001</v>
       </c>
       <c r="F2">
-        <v>0.176</v>
+        <v>0.121</v>
       </c>
       <c r="G2">
-        <v>0.1600671542759148</v>
+        <v>0.2214626804977691</v>
       </c>
       <c r="H2">
-        <v>0.1594067997865291</v>
+        <v>0.2206847751190767</v>
       </c>
       <c r="I2">
-        <v>0.1697822429726009</v>
+        <v>0.2185703390077878</v>
       </c>
       <c r="J2">
-        <v>0.1494867113332763</v>
+        <v>0.1961365270528074</v>
       </c>
       <c r="K2">
-        <v>16403.99</v>
+        <v>20197.72</v>
       </c>
       <c r="L2">
-        <v>0.1263996317425699</v>
+        <v>0.1520998550369938</v>
       </c>
       <c r="M2">
-        <v>10742.2234</v>
+        <v>13786.246</v>
       </c>
       <c r="N2">
-        <v>0.04218597257222657</v>
+        <v>0.06102478285263415</v>
       </c>
       <c r="O2">
-        <v>0.6548543006914781</v>
+        <v>0.6825644676725887</v>
       </c>
       <c r="P2">
-        <v>4730.2804</v>
+        <v>3403.408</v>
       </c>
       <c r="Q2">
-        <v>0.01857636652886412</v>
+        <v>0.01506517685517275</v>
       </c>
       <c r="R2">
-        <v>0.2883615754459737</v>
+        <v>0.1685045638814678</v>
       </c>
       <c r="S2">
-        <v>6011.943</v>
+        <v>10382.838</v>
       </c>
       <c r="T2">
-        <v>0.5596553689248354</v>
+        <v>0.7531301849684099</v>
       </c>
       <c r="U2">
-        <v>15491.196</v>
+        <v>7944.585</v>
       </c>
       <c r="V2">
-        <v>0.06083574556520448</v>
+        <v>0.03516668529484347</v>
       </c>
       <c r="W2">
-        <v>0.1399976155612465</v>
+        <v>0.03139612558450233</v>
       </c>
       <c r="X2">
-        <v>0.04749542201813305</v>
+        <v>0.0840075374701095</v>
       </c>
       <c r="Y2">
-        <v>0.09250219354311341</v>
+        <v>-0.05261141188560717</v>
       </c>
       <c r="Z2">
-        <v>0.8645945516829258</v>
+        <v>0.9863525347406512</v>
       </c>
       <c r="AA2">
-        <v>0.1190343670397281</v>
+        <v>0.03451336288628625</v>
       </c>
       <c r="AB2">
-        <v>0.04371116555956189</v>
+        <v>0.07440689448871776</v>
       </c>
       <c r="AC2">
-        <v>0.07552573013953343</v>
+        <v>-0.0373960702348238</v>
       </c>
       <c r="AD2">
-        <v>63026.67</v>
+        <v>64470.14</v>
       </c>
       <c r="AE2">
-        <v>5017.928206761405</v>
+        <v>4408.181286541706</v>
       </c>
       <c r="AF2">
-        <v>68044.59820676141</v>
+        <v>68878.3212865417</v>
       </c>
       <c r="AG2">
-        <v>52553.40220676141</v>
+        <v>60933.7362865417</v>
       </c>
       <c r="AH2">
-        <v>0.2108704965965265</v>
+        <v>0.2336517107244612</v>
       </c>
       <c r="AI2">
-        <v>0.3412303059565275</v>
+        <v>0.4415462078889338</v>
       </c>
       <c r="AJ2">
-        <v>0.1710761141094551</v>
+        <v>0.2124266651779907</v>
       </c>
       <c r="AK2">
-        <v>0.2857430337377593</v>
+        <v>0.4115785125488376</v>
       </c>
       <c r="AL2">
-        <v>2723.398</v>
+        <v>2521.352</v>
       </c>
       <c r="AM2">
-        <v>2591.597</v>
+        <v>2354.298</v>
       </c>
       <c r="AN2">
-        <v>2.075089549964594</v>
+        <v>1.715849910220817</v>
       </c>
       <c r="AO2">
-        <v>8.082623252275283</v>
+        <v>11.49292522424477</v>
       </c>
       <c r="AP2">
-        <v>1.73026776972886</v>
+        <v>1.621729779657397</v>
       </c>
       <c r="AQ2">
-        <v>8.493681695109231</v>
+        <v>12.30842909436274</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ryan Specialty Group Holdings, Inc. (NYSE:RYAN)</t>
+          <t>Brown &amp; Brown, Inc. (NYSE:BRO)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,110 +724,125 @@
           <t>Insurance (General)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.134</v>
+      </c>
+      <c r="E3">
+        <v>0.184</v>
+      </c>
+      <c r="F3">
+        <v>0.08</v>
+      </c>
       <c r="G3">
-        <v>0.1798363149127254</v>
+        <v>0.296435382132903</v>
       </c>
       <c r="H3">
-        <v>0.1798363149127254</v>
+        <v>0.296435382132903</v>
       </c>
       <c r="I3">
-        <v>0.1636241663095782</v>
+        <v>0.2729399148600213</v>
       </c>
       <c r="J3">
-        <v>0.1503936184868896</v>
+        <v>0.2084708831832621</v>
       </c>
       <c r="K3">
-        <v>51.5</v>
+        <v>628.3</v>
       </c>
       <c r="L3">
-        <v>0.03729992033026725</v>
+        <v>0.1843332844359689</v>
       </c>
       <c r="M3">
-        <v>976.83</v>
+        <v>238.8</v>
       </c>
       <c r="N3">
-        <v>0.2202746583682857</v>
+        <v>0.01479994050275175</v>
       </c>
       <c r="O3">
-        <v>18.96757281553398</v>
+        <v>0.3800732134330734</v>
       </c>
       <c r="P3">
-        <v>1.33</v>
+        <v>115.9</v>
       </c>
       <c r="Q3">
-        <v>0.0002999143101970865</v>
+        <v>0.007183053200456146</v>
       </c>
       <c r="R3">
-        <v>0.0258252427184466</v>
+        <v>0.1844660194174758</v>
       </c>
       <c r="S3">
-        <v>975.5</v>
+        <v>122.9</v>
       </c>
       <c r="T3">
-        <v>0.9986384529549666</v>
+        <v>0.5146566164154104</v>
       </c>
       <c r="U3">
-        <v>413.7</v>
+        <v>579.5</v>
       </c>
       <c r="V3">
-        <v>0.09328913543498848</v>
+        <v>0.03591526600228073</v>
+      </c>
+      <c r="W3">
+        <v>0.1529603661505502</v>
       </c>
       <c r="X3">
-        <v>0.05185195639674777</v>
+        <v>0.08223365469762907</v>
+      </c>
+      <c r="Y3">
+        <v>0.0707267114529211</v>
       </c>
       <c r="Z3">
-        <v>13.22249081773374</v>
+        <v>4.061018329623091</v>
       </c>
       <c r="AA3">
-        <v>1.988578239488649</v>
+        <v>0.8466040777999416</v>
       </c>
       <c r="AB3">
-        <v>0.0437575271376403</v>
+        <v>0.07453624640906038</v>
       </c>
       <c r="AC3">
-        <v>1.944820712351009</v>
+        <v>0.7720678313908812</v>
       </c>
       <c r="AD3">
-        <v>1595.2</v>
+        <v>4107.9</v>
       </c>
       <c r="AE3">
-        <v>104.420567881827</v>
+        <v>195.4215009980871</v>
       </c>
       <c r="AF3">
-        <v>1699.620567881827</v>
+        <v>4303.321500998087</v>
       </c>
       <c r="AG3">
-        <v>1285.920567881827</v>
+        <v>3723.821500998087</v>
       </c>
       <c r="AH3">
-        <v>0.2770719684878748</v>
+        <v>0.2105495498188526</v>
       </c>
       <c r="AI3">
-        <v>0.7484280128155812</v>
+        <v>0.4995775153627143</v>
       </c>
       <c r="AJ3">
-        <v>0.2247908302439638</v>
+        <v>0.187512838979047</v>
       </c>
       <c r="AK3">
-        <v>0.6923897947934253</v>
+        <v>0.4634834630639543</v>
       </c>
       <c r="AL3">
-        <v>82.3</v>
+        <v>112</v>
       </c>
       <c r="AM3">
-        <v>81.76899999999999</v>
+        <v>110</v>
       </c>
       <c r="AN3">
-        <v>4.429880588725355</v>
+        <v>3.588312368972746</v>
       </c>
       <c r="AO3">
-        <v>2.720534629404618</v>
+        <v>8.220535714285715</v>
       </c>
       <c r="AP3">
-        <v>3.571009630329984</v>
+        <v>3.252814029523137</v>
       </c>
       <c r="AQ3">
-        <v>2.738201518913036</v>
+        <v>8.370000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -838,7 +853,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Quad M Solutions, Inc. (OTCPK:MMMM)</t>
+          <t>Ryan Specialty Holdings, Inc. (NYSE:RYAN)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -847,106 +862,115 @@
         </is>
       </c>
       <c r="G4">
-        <v>0.0443213296398892</v>
+        <v>0.2160813086360356</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>0.2160813086360356</v>
       </c>
       <c r="I4">
-        <v>-0.09695290858725761</v>
+        <v>0.1855173780523455</v>
       </c>
       <c r="J4">
-        <v>-0.09695290858725761</v>
+        <v>0.1675236728759977</v>
       </c>
       <c r="K4">
-        <v>-9.970000000000001</v>
+        <v>53.2</v>
       </c>
       <c r="L4">
-        <v>-0.2761772853185596</v>
+        <v>0.03199422660572528</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>39.79000000000001</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.008530754882833438</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>0.7479323308270678</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>32.7</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.007010698282700512</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>0.6146616541353384</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>7.090000000000003</v>
+      </c>
+      <c r="T4">
+        <v>0.1781854737371199</v>
       </c>
       <c r="U4">
-        <v>0.846</v>
+        <v>833.1</v>
       </c>
       <c r="V4">
-        <v>0.02927335640138408</v>
+        <v>0.178612010376691</v>
       </c>
       <c r="W4">
-        <v>2.92375366568915</v>
+        <v>0.1701311160857052</v>
       </c>
       <c r="X4">
-        <v>0.04694376291251059</v>
+        <v>0.08700137792463322</v>
       </c>
       <c r="Y4">
-        <v>2.876809902776639</v>
+        <v>0.08312973816107194</v>
       </c>
       <c r="Z4">
-        <v>-12.49134948096886</v>
+        <v>4.530685023625583</v>
       </c>
       <c r="AA4">
-        <v>1.211072664359861</v>
+        <v>0.7589969958020342</v>
       </c>
       <c r="AB4">
-        <v>0.04964933532968675</v>
+        <v>0.07807649723862552</v>
       </c>
       <c r="AC4">
-        <v>1.161423329030175</v>
+        <v>0.6809204985634086</v>
       </c>
       <c r="AD4">
-        <v>4.31</v>
+        <v>1982.6</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>80.60851887279962</v>
       </c>
       <c r="AF4">
-        <v>4.31</v>
+        <v>2063.2085188728</v>
       </c>
       <c r="AG4">
-        <v>3.464</v>
+        <v>1230.1085188728</v>
       </c>
       <c r="AH4">
-        <v>0.1297801866907558</v>
+        <v>0.3066824089608871</v>
       </c>
       <c r="AI4">
-        <v>-1.932735426008968</v>
+        <v>0.7314504512140414</v>
       </c>
       <c r="AJ4">
-        <v>0.10703250525275</v>
+        <v>0.2086907473301555</v>
       </c>
       <c r="AK4">
-        <v>-1.126137841352405</v>
+        <v>0.6188887334666946</v>
       </c>
       <c r="AL4">
-        <v>1.94</v>
+        <v>95.3</v>
       </c>
       <c r="AM4">
-        <v>1.94</v>
+        <v>89.42</v>
+      </c>
+      <c r="AN4">
+        <v>4.568202764976959</v>
       </c>
       <c r="AO4">
-        <v>-1.804123711340206</v>
+        <v>3.179433368310598</v>
+      </c>
+      <c r="AP4">
+        <v>2.834351425974193</v>
       </c>
       <c r="AQ4">
-        <v>-1.804123711340206</v>
+        <v>3.388503690449564</v>
       </c>
     </row>
     <row r="5">
@@ -957,7 +981,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown, Inc. (NYSE:BRO)</t>
+          <t>Marsh &amp; McLennan Companies, Inc. (NYSE:MMC)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -966,124 +990,124 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.112</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="E5">
-        <v>0.177</v>
+        <v>0.123</v>
       </c>
       <c r="F5">
-        <v>0.18</v>
+        <v>0.0916</v>
       </c>
       <c r="G5">
-        <v>0.273669240146282</v>
+        <v>0.2639308855291577</v>
       </c>
       <c r="H5">
-        <v>0.273669240146282</v>
+        <v>0.2639308855291577</v>
       </c>
       <c r="I5">
-        <v>0.2808560070718391</v>
+        <v>0.2401784707565565</v>
       </c>
       <c r="J5">
-        <v>0.2173659122337105</v>
+        <v>0.1855825971556869</v>
       </c>
       <c r="K5">
-        <v>582.7</v>
+        <v>3387</v>
       </c>
       <c r="L5">
-        <v>0.1973113910334553</v>
+        <v>0.1625629949604032</v>
       </c>
       <c r="M5">
-        <v>286.9</v>
+        <v>3325</v>
       </c>
       <c r="N5">
-        <v>0.01445412867146959</v>
+        <v>0.04050940731995853</v>
       </c>
       <c r="O5">
-        <v>0.4923631371203019</v>
+        <v>0.9816947150870977</v>
       </c>
       <c r="P5">
-        <v>106.8</v>
+        <v>1104</v>
       </c>
       <c r="Q5">
-        <v>0.005380623709002972</v>
+        <v>0.01345034155826593</v>
       </c>
       <c r="R5">
-        <v>0.183284709112751</v>
+        <v>0.3259521700620018</v>
       </c>
       <c r="S5">
-        <v>180.1</v>
+        <v>2221</v>
       </c>
       <c r="T5">
-        <v>0.6277448588358312</v>
+        <v>0.6679699248120301</v>
       </c>
       <c r="U5">
-        <v>944</v>
+        <v>802</v>
       </c>
       <c r="V5">
-        <v>0.04755907098594388</v>
+        <v>0.009770990878377968</v>
       </c>
       <c r="W5">
-        <v>0.1574014046461372</v>
+        <v>0.3479556194781179</v>
       </c>
       <c r="X5">
-        <v>0.04620308052618791</v>
+        <v>0.07940746277059199</v>
       </c>
       <c r="Y5">
-        <v>0.1111983241199493</v>
+        <v>0.268548156707526</v>
       </c>
       <c r="Z5">
-        <v>3.557299971143543</v>
+        <v>3.850199566478005</v>
       </c>
       <c r="AA5">
-        <v>0.7732357533165685</v>
+        <v>0.714530035114688</v>
       </c>
       <c r="AB5">
-        <v>0.04391383378187513</v>
+        <v>0.07407105903660378</v>
       </c>
       <c r="AC5">
-        <v>0.7293219195346934</v>
+        <v>0.6404589760780842</v>
       </c>
       <c r="AD5">
-        <v>2045.5</v>
+        <v>11366</v>
       </c>
       <c r="AE5">
-        <v>213.3801995772238</v>
+        <v>1979.40780893572</v>
       </c>
       <c r="AF5">
-        <v>2258.880199577224</v>
+        <v>13345.40780893572</v>
       </c>
       <c r="AG5">
-        <v>1314.880199577224</v>
+        <v>12543.40780893572</v>
       </c>
       <c r="AH5">
-        <v>0.1021753410632477</v>
+        <v>0.139852163810561</v>
       </c>
       <c r="AI5">
-        <v>0.3548083287414022</v>
+        <v>0.5768141674863403</v>
       </c>
       <c r="AJ5">
-        <v>0.06212850324126717</v>
+        <v>0.1325617822050777</v>
       </c>
       <c r="AK5">
-        <v>0.2424868604738734</v>
+        <v>0.5616181058499907</v>
       </c>
       <c r="AL5">
-        <v>65.40000000000001</v>
+        <v>451</v>
       </c>
       <c r="AM5">
-        <v>63.52</v>
+        <v>400</v>
       </c>
       <c r="AN5">
-        <v>2.001663567863783</v>
+        <v>1.864807219031994</v>
       </c>
       <c r="AO5">
-        <v>12.57186544342508</v>
+        <v>11.11086474501109</v>
       </c>
       <c r="AP5">
-        <v>1.286701438083202</v>
+        <v>2.05798323362358</v>
       </c>
       <c r="AQ5">
-        <v>12.94395465994962</v>
+        <v>12.5275</v>
       </c>
     </row>
     <row r="6">
@@ -1094,7 +1118,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Marsh &amp; McLennan Companies, Inc. (NYSE:MMC)</t>
+          <t>BRP Group, Inc. (NasdaqGS:BRP)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1102,125 +1126,116 @@
           <t>Insurance (General)</t>
         </is>
       </c>
-      <c r="D6">
-        <v>0.07690000000000001</v>
-      </c>
-      <c r="E6">
-        <v>0.09720000000000001</v>
-      </c>
       <c r="F6">
-        <v>0.135</v>
+        <v>0.277</v>
       </c>
       <c r="G6">
-        <v>0.230745065186659</v>
+        <v>0.07942722899653205</v>
       </c>
       <c r="H6">
-        <v>0.230745065186659</v>
+        <v>0.07942722899653205</v>
       </c>
       <c r="I6">
-        <v>0.2374993187023854</v>
+        <v>0.02093619105116785</v>
       </c>
       <c r="J6">
-        <v>0.1722136596664247</v>
+        <v>0.02093619105116785</v>
       </c>
       <c r="K6">
-        <v>2714</v>
+        <v>-15.9</v>
       </c>
       <c r="L6">
-        <v>0.1421016807162679</v>
+        <v>-0.01778722452175859</v>
       </c>
       <c r="M6">
-        <v>1814</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.02066979714200743</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>0.6683861459100958</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>980</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.01116670407892353</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>0.3610906411201179</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>834</v>
-      </c>
-      <c r="T6">
-        <v>0.4597574421168688</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>1398</v>
+        <v>158.6</v>
       </c>
       <c r="V6">
-        <v>0.01592964520646438</v>
+        <v>0.1027002525416046</v>
       </c>
       <c r="W6">
-        <v>0.3159120009312071</v>
+        <v>-0.0275897969807392</v>
       </c>
       <c r="X6">
-        <v>0.04692842378631866</v>
+        <v>0.09984757676480271</v>
       </c>
       <c r="Y6">
-        <v>0.2689835771448884</v>
+        <v>-0.1274373737455419</v>
       </c>
       <c r="Z6">
-        <v>3.081973875836288</v>
+        <v>18.72995284650742</v>
       </c>
       <c r="AA6">
-        <v>0.5307580001540823</v>
+        <v>0.3921338711738444</v>
       </c>
       <c r="AB6">
-        <v>0.04350203579009331</v>
+        <v>0.08488845852070515</v>
       </c>
       <c r="AC6">
-        <v>0.4872559643639889</v>
+        <v>0.3072454126531392</v>
       </c>
       <c r="AD6">
-        <v>10744</v>
+        <v>1346.5</v>
       </c>
       <c r="AE6">
-        <v>2280.002560515709</v>
+        <v>67.42569409680532</v>
       </c>
       <c r="AF6">
-        <v>13024.00256051571</v>
+        <v>1413.925694096805</v>
       </c>
       <c r="AG6">
-        <v>11626.00256051571</v>
+        <v>1255.325694096805</v>
       </c>
       <c r="AH6">
-        <v>0.1292257295451124</v>
+        <v>0.477964104266392</v>
       </c>
       <c r="AI6">
-        <v>0.5684358024191213</v>
+        <v>0.5359787424591019</v>
       </c>
       <c r="AJ6">
-        <v>0.1169772098837344</v>
+        <v>0.4483905461875644</v>
       </c>
       <c r="AK6">
-        <v>0.5403923573874031</v>
+        <v>0.5062969610606097</v>
       </c>
       <c r="AL6">
-        <v>463</v>
+        <v>54.2</v>
       </c>
       <c r="AM6">
-        <v>416</v>
+        <v>54.2</v>
       </c>
       <c r="AN6">
-        <v>1.866898349261512</v>
+        <v>12.11971197119712</v>
       </c>
       <c r="AO6">
-        <v>9.8963282937365</v>
+        <v>0.3118081180811808</v>
       </c>
       <c r="AP6">
-        <v>2.020156830671713</v>
+        <v>11.29906115298655</v>
       </c>
       <c r="AQ6">
-        <v>11.01442307692308</v>
+        <v>0.3118081180811808</v>
       </c>
     </row>
     <row r="7">
@@ -1231,7 +1246,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GoHealth, Inc. (NasdaqGS:GOCO)</t>
+          <t>The Marketing Alliance, Inc. (OTCPK:MAAL)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1239,26 +1254,29 @@
           <t>Insurance (General)</t>
         </is>
       </c>
-      <c r="F7">
-        <v>0.596</v>
+      <c r="D7">
+        <v>-0.0626</v>
+      </c>
+      <c r="E7">
+        <v>0.0135</v>
       </c>
       <c r="G7">
-        <v>0.08963823557192784</v>
+        <v>0.1405797101449275</v>
       </c>
       <c r="H7">
-        <v>0.04921129687352413</v>
+        <v>0.1405797101449275</v>
       </c>
       <c r="I7">
-        <v>0.06365237165958729</v>
+        <v>0.1368487213748757</v>
       </c>
       <c r="J7">
-        <v>0.06365237165958729</v>
+        <v>0.1025621667260617</v>
       </c>
       <c r="K7">
-        <v>1.69</v>
+        <v>1.43</v>
       </c>
       <c r="L7">
-        <v>0.001596297345801455</v>
+        <v>0.06908212560386473</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1282,73 +1300,73 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>85.2</v>
+        <v>1.73</v>
       </c>
       <c r="V7">
-        <v>0.1958620689655172</v>
+        <v>0.08564356435643565</v>
       </c>
       <c r="W7">
-        <v>0.005004441812259402</v>
+        <v>0.192722371967655</v>
       </c>
       <c r="X7">
-        <v>0.06876681514002013</v>
+        <v>0.08186240456074113</v>
       </c>
       <c r="Y7">
-        <v>-0.06376237332776073</v>
+        <v>0.1108599674069139</v>
       </c>
       <c r="Z7">
-        <v>8.0383477479941</v>
+        <v>3.228746216892087</v>
       </c>
       <c r="AA7">
-        <v>0.5116598983843269</v>
+        <v>0.3311472078130272</v>
       </c>
       <c r="AB7">
-        <v>0.0437000246846359</v>
+        <v>0.07423692981121797</v>
       </c>
       <c r="AC7">
-        <v>0.467959873699691</v>
+        <v>0.2569102780018092</v>
       </c>
       <c r="AD7">
-        <v>443.5</v>
+        <v>4.92</v>
       </c>
       <c r="AE7">
-        <v>74.20617061997469</v>
+        <v>0.1911573377003664</v>
       </c>
       <c r="AF7">
-        <v>517.7061706199747</v>
+        <v>5.111157337700366</v>
       </c>
       <c r="AG7">
-        <v>432.5061706199747</v>
+        <v>3.381157337700366</v>
       </c>
       <c r="AH7">
-        <v>0.5434059173596795</v>
+        <v>0.2019329764146114</v>
       </c>
       <c r="AI7">
-        <v>0.2820509017657567</v>
+        <v>0.4312791731691034</v>
       </c>
       <c r="AJ7">
-        <v>0.4985626445871602</v>
+        <v>0.143383858954825</v>
       </c>
       <c r="AK7">
-        <v>0.2471031513685272</v>
+        <v>0.3340682517705629</v>
       </c>
       <c r="AL7">
-        <v>32.5</v>
+        <v>0.242</v>
       </c>
       <c r="AM7">
-        <v>32.5</v>
+        <v>0.242</v>
       </c>
       <c r="AN7">
-        <v>2.425750697369141</v>
+        <v>1.602084011722566</v>
       </c>
       <c r="AO7">
-        <v>2.329230769230769</v>
+        <v>11.44628099173554</v>
       </c>
       <c r="AP7">
-        <v>2.36561926718796</v>
+        <v>1.100995551188657</v>
       </c>
       <c r="AQ7">
-        <v>2.329230769230769</v>
+        <v>11.44628099173554</v>
       </c>
     </row>
     <row r="8">
@@ -1368,49 +1386,49 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0706</v>
+        <v>0.0675</v>
       </c>
       <c r="E8">
-        <v>0.197</v>
+        <v>0.166</v>
       </c>
       <c r="F8">
-        <v>0.151</v>
+        <v>0.121</v>
       </c>
       <c r="G8">
-        <v>0.2113783234261885</v>
+        <v>0.2339311047251828</v>
       </c>
       <c r="H8">
-        <v>0.2113783234261885</v>
+        <v>0.2339311047251828</v>
       </c>
       <c r="I8">
-        <v>0.1830120514065325</v>
+        <v>0.21250534944393</v>
       </c>
       <c r="J8">
-        <v>0.1814315094883801</v>
+        <v>0.1775822396642978</v>
       </c>
       <c r="K8">
-        <v>939.6</v>
+        <v>1088.1</v>
       </c>
       <c r="L8">
-        <v>0.1216830490695054</v>
+        <v>0.1319340875195519</v>
       </c>
       <c r="M8">
-        <v>379.5</v>
+        <v>421.3</v>
       </c>
       <c r="N8">
-        <v>0.01079078390282323</v>
+        <v>0.01059826221705684</v>
       </c>
       <c r="O8">
-        <v>0.4038952745849297</v>
+        <v>0.3871886775112582</v>
       </c>
       <c r="P8">
-        <v>379.5</v>
+        <v>421.3</v>
       </c>
       <c r="Q8">
-        <v>0.01079078390282323</v>
+        <v>0.01059826221705684</v>
       </c>
       <c r="R8">
-        <v>0.4038952745849297</v>
+        <v>0.3871886775112582</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1419,73 +1437,73 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>2735.1</v>
+        <v>553.7</v>
       </c>
       <c r="V8">
-        <v>0.07777041647592048</v>
+        <v>0.01392892900447275</v>
       </c>
       <c r="W8">
-        <v>0.1627943240293155</v>
+        <v>0.1292249590271015</v>
       </c>
       <c r="X8">
-        <v>0.04734568363565977</v>
+        <v>0.0795046658077041</v>
       </c>
       <c r="Y8">
-        <v>0.1154486403936557</v>
+        <v>0.04972029321939736</v>
       </c>
       <c r="Z8">
-        <v>1.763235369099165</v>
+        <v>1.674026962501625</v>
       </c>
       <c r="AA8">
-        <v>0.3199064545989625</v>
+        <v>0.2972774572594601</v>
       </c>
       <c r="AB8">
-        <v>0.04378624473742194</v>
+        <v>0.07445973741396962</v>
       </c>
       <c r="AC8">
-        <v>0.2761202098615406</v>
+        <v>0.2228177198454905</v>
       </c>
       <c r="AD8">
-        <v>5511</v>
+        <v>6247.6</v>
       </c>
       <c r="AE8">
-        <v>408.17921327089</v>
+        <v>358.0231576553791</v>
       </c>
       <c r="AF8">
-        <v>5919.17921327089</v>
+        <v>6605.623157655379</v>
       </c>
       <c r="AG8">
-        <v>3184.07921327089</v>
+        <v>6051.923157655379</v>
       </c>
       <c r="AH8">
-        <v>0.1440607428384989</v>
+        <v>0.1424933205452456</v>
       </c>
       <c r="AI8">
-        <v>0.4113603694486498</v>
+        <v>0.433589970050495</v>
       </c>
       <c r="AJ8">
-        <v>0.08302038794861431</v>
+        <v>0.1321273193627688</v>
       </c>
       <c r="AK8">
-        <v>0.2732135103641707</v>
+        <v>0.4122276147013378</v>
       </c>
       <c r="AL8">
-        <v>212.4</v>
+        <v>254.4</v>
       </c>
       <c r="AM8">
-        <v>134.1</v>
+        <v>148.2</v>
       </c>
       <c r="AN8">
-        <v>2.760468843919054</v>
+        <v>2.590860081280584</v>
       </c>
       <c r="AO8">
-        <v>6.52683615819209</v>
+        <v>6.771226415094339</v>
       </c>
       <c r="AP8">
-        <v>1.594910445437232</v>
+        <v>2.509713509851281</v>
       </c>
       <c r="AQ8">
-        <v>10.33780760626398</v>
+        <v>11.62348178137652</v>
       </c>
     </row>
     <row r="9">
@@ -1496,7 +1514,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>American Financial Group, Inc. (NYSE:AFG)</t>
+          <t>American International Group, Inc. (NYSE:AIG)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1505,121 +1523,118 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.064</v>
-      </c>
-      <c r="E9">
-        <v>0.428</v>
+        <v>0.0401</v>
       </c>
       <c r="G9">
-        <v>0.1937000470145745</v>
+        <v>0.2662097072989996</v>
       </c>
       <c r="H9">
-        <v>0.1937000470145745</v>
+        <v>0.2662097072989996</v>
       </c>
       <c r="I9">
-        <v>0.2346629455072086</v>
+        <v>0.3128977748465749</v>
       </c>
       <c r="J9">
-        <v>0.1884842935800873</v>
+        <v>0.2495824149162013</v>
       </c>
       <c r="K9">
-        <v>2332</v>
+        <v>13751</v>
       </c>
       <c r="L9">
-        <v>0.2740949694405266</v>
+        <v>0.2315840883829028</v>
       </c>
       <c r="M9">
-        <v>1752</v>
+        <v>6349</v>
       </c>
       <c r="N9">
-        <v>0.1504405021552835</v>
+        <v>0.1351250689033565</v>
       </c>
       <c r="O9">
-        <v>0.7512864493996569</v>
+        <v>0.4617118754999636</v>
       </c>
       <c r="P9">
-        <v>1354</v>
+        <v>1010</v>
       </c>
       <c r="Q9">
-        <v>0.1162650912775421</v>
+        <v>0.02149571894666721</v>
       </c>
       <c r="R9">
-        <v>0.5806174957118353</v>
+        <v>0.07344920369427678</v>
       </c>
       <c r="S9">
-        <v>398</v>
+        <v>5339</v>
       </c>
       <c r="T9">
-        <v>0.2271689497716895</v>
+        <v>0.8409198298944716</v>
       </c>
       <c r="U9">
-        <v>2833</v>
+        <v>2294</v>
       </c>
       <c r="V9">
-        <v>0.2432636658709578</v>
+        <v>0.04882294976599463</v>
       </c>
       <c r="W9">
-        <v>0.3678233438485805</v>
+        <v>0.2135978129174563</v>
       </c>
       <c r="X9">
-        <v>0.04764516040060632</v>
+        <v>0.09321889424115629</v>
       </c>
       <c r="Y9">
-        <v>0.3201781834479741</v>
+        <v>0.1203789186763</v>
       </c>
       <c r="Z9">
-        <v>1.439000218015046</v>
+        <v>0.6356177618205863</v>
       </c>
       <c r="AA9">
-        <v>0.2712289395541574</v>
+        <v>0.1586390159588128</v>
       </c>
       <c r="AB9">
-        <v>0.04344060946441</v>
+        <v>0.07291571855303169</v>
       </c>
       <c r="AC9">
-        <v>0.2277883300897474</v>
+        <v>0.08572329740578111</v>
       </c>
       <c r="AD9">
-        <v>1964</v>
+        <v>30432</v>
       </c>
       <c r="AE9">
-        <v>162.4382981233449</v>
+        <v>1113.779625800377</v>
       </c>
       <c r="AF9">
-        <v>2126.438298123345</v>
+        <v>31545.77962580038</v>
       </c>
       <c r="AG9">
-        <v>-706.5617018766552</v>
+        <v>29251.77962580038</v>
       </c>
       <c r="AH9">
-        <v>0.1544003416215287</v>
+        <v>0.4016939334205942</v>
       </c>
       <c r="AI9">
-        <v>0.2886657312618869</v>
+        <v>0.4348336313274684</v>
       </c>
       <c r="AJ9">
-        <v>-0.06458966178640316</v>
+        <v>0.3836908865957102</v>
       </c>
       <c r="AK9">
-        <v>-0.1558555902633863</v>
+        <v>0.4163789643855976</v>
       </c>
       <c r="AL9">
-        <v>95</v>
+        <v>1108</v>
       </c>
       <c r="AM9">
-        <v>95</v>
+        <v>1108</v>
       </c>
       <c r="AN9">
-        <v>0.8767857142857143</v>
+        <v>1.280646383032445</v>
       </c>
       <c r="AO9">
-        <v>20.90526315789474</v>
+        <v>16.77797833935018</v>
       </c>
       <c r="AP9">
-        <v>-0.3154293311949354</v>
+        <v>1.230980079358683</v>
       </c>
       <c r="AQ9">
-        <v>20.90526315789474</v>
+        <v>16.77797833935018</v>
       </c>
     </row>
     <row r="10">
@@ -1630,7 +1645,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Assurant, Inc. (NYSE:AIZ)</t>
+          <t>Crawford &amp; Company (NYSE:CRD.B)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1639,124 +1654,121 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.0487</v>
-      </c>
-      <c r="E10">
-        <v>0.183</v>
+        <v>0.0145</v>
       </c>
       <c r="F10">
-        <v>0.172</v>
+        <v>0.12</v>
       </c>
       <c r="G10">
-        <v>0.08824423709165542</v>
+        <v>0.06369591449750044</v>
       </c>
       <c r="H10">
-        <v>0.08824423709165542</v>
+        <v>0.06369591449750044</v>
       </c>
       <c r="I10">
-        <v>0.09672817518807382</v>
+        <v>0.04110144295346557</v>
       </c>
       <c r="J10">
-        <v>0.07149709226747913</v>
+        <v>0.04110144295346557</v>
       </c>
       <c r="K10">
-        <v>1388</v>
+        <v>-2.57</v>
       </c>
       <c r="L10">
-        <v>0.1318865091883469</v>
+        <v>-0.002215135321496294</v>
       </c>
       <c r="M10">
-        <v>860.4</v>
+        <v>53.2</v>
       </c>
       <c r="N10">
-        <v>0.09688752758884735</v>
+        <v>0.2013626040878123</v>
       </c>
       <c r="O10">
-        <v>0.6198847262247839</v>
+        <v>-20.70038910505837</v>
       </c>
       <c r="P10">
-        <v>158</v>
+        <v>12</v>
       </c>
       <c r="Q10">
-        <v>0.01779199135174091</v>
+        <v>0.04542013626040878</v>
       </c>
       <c r="R10">
-        <v>0.1138328530259366</v>
+        <v>-4.669260700389105</v>
       </c>
       <c r="S10">
-        <v>702.4</v>
+        <v>41.2</v>
       </c>
       <c r="T10">
-        <v>0.8163644816364481</v>
+        <v>0.7744360902255639</v>
       </c>
       <c r="U10">
-        <v>2027.9</v>
+        <v>33.1</v>
       </c>
       <c r="V10">
-        <v>0.2283568307733886</v>
+        <v>0.1252838758516276</v>
       </c>
       <c r="W10">
-        <v>0.2339260133142327</v>
+        <v>-0.01166061705989111</v>
       </c>
       <c r="X10">
-        <v>0.04920903194407903</v>
+        <v>0.1129553600419309</v>
       </c>
       <c r="Y10">
-        <v>0.1847169813701537</v>
+        <v>-0.1246159771018221</v>
       </c>
       <c r="Z10">
-        <v>3.008404139046954</v>
+        <v>3.310406732049743</v>
       </c>
       <c r="AA10">
-        <v>0.2150921483073062</v>
+        <v>0.1360624934501109</v>
       </c>
       <c r="AB10">
-        <v>0.04262854968242841</v>
+        <v>0.06777934456465931</v>
       </c>
       <c r="AC10">
-        <v>0.1724635986248778</v>
+        <v>0.06828314888545156</v>
       </c>
       <c r="AD10">
-        <v>2201.9</v>
+        <v>257.4</v>
       </c>
       <c r="AE10">
-        <v>82.06669342836724</v>
+        <v>112.0705294269462</v>
       </c>
       <c r="AF10">
-        <v>2283.966693428367</v>
+        <v>369.4705294269462</v>
       </c>
       <c r="AG10">
-        <v>256.0666934283672</v>
+        <v>336.3705294269462</v>
       </c>
       <c r="AH10">
-        <v>0.2045764669099205</v>
+        <v>0.5830640881485736</v>
       </c>
       <c r="AI10">
-        <v>0.2844870919134663</v>
+        <v>0.6961021928362341</v>
       </c>
       <c r="AJ10">
-        <v>0.02802688413591543</v>
+        <v>0.5600849741127074</v>
       </c>
       <c r="AK10">
-        <v>0.04267446292282701</v>
+        <v>0.6758899905410665</v>
       </c>
       <c r="AL10">
-        <v>111.5</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="AM10">
-        <v>111.5</v>
+        <v>8.316000000000001</v>
       </c>
       <c r="AN10">
-        <v>1.834152436484798</v>
+        <v>2.853658536585366</v>
       </c>
       <c r="AO10">
-        <v>9.07085201793722</v>
+        <v>4.481605351170568</v>
       </c>
       <c r="AP10">
-        <v>0.213300036175233</v>
+        <v>3.729163297416255</v>
       </c>
       <c r="AQ10">
-        <v>9.07085201793722</v>
+        <v>4.834054834054834</v>
       </c>
     </row>
     <row r="11">
@@ -1767,7 +1779,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SelectQuote, Inc. (NYSE:SLQT)</t>
+          <t>Assurant, Inc. (NYSE:AIZ)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1775,116 +1787,125 @@
           <t>Insurance (General)</t>
         </is>
       </c>
+      <c r="D11">
+        <v>0.09279999999999999</v>
+      </c>
+      <c r="E11">
+        <v>0.07389999999999999</v>
+      </c>
+      <c r="F11">
+        <v>0.127</v>
+      </c>
       <c r="G11">
-        <v>0.239215283483977</v>
+        <v>0.1076410514972665</v>
       </c>
       <c r="H11">
-        <v>0.2180566967953985</v>
+        <v>0.1076410514972665</v>
       </c>
       <c r="I11">
-        <v>0.1429012173141771</v>
+        <v>0.05334245401854962</v>
       </c>
       <c r="J11">
-        <v>0.1150809423384826</v>
+        <v>0.04317479588054818</v>
       </c>
       <c r="K11">
-        <v>84.8</v>
+        <v>340</v>
       </c>
       <c r="L11">
-        <v>0.08709942481511913</v>
+        <v>0.03361311306858063</v>
       </c>
       <c r="M11">
-        <v>8</v>
+        <v>1023.7</v>
       </c>
       <c r="N11">
-        <v>0.005385392123864019</v>
+        <v>0.154939383390595</v>
       </c>
       <c r="O11">
-        <v>0.09433962264150944</v>
+        <v>3.010882352941177</v>
       </c>
       <c r="P11">
-        <v>-0</v>
+        <v>151.8</v>
       </c>
       <c r="Q11">
-        <v>-0</v>
+        <v>0.02297528416400539</v>
       </c>
       <c r="R11">
-        <v>-0</v>
+        <v>0.4464705882352942</v>
       </c>
       <c r="S11">
-        <v>8</v>
+        <v>871.9000000000001</v>
       </c>
       <c r="T11">
-        <v>1</v>
+        <v>0.8517143694441731</v>
       </c>
       <c r="U11">
-        <v>183.6</v>
+        <v>1429.8</v>
       </c>
       <c r="V11">
-        <v>0.1235947492426792</v>
+        <v>0.2164035658609677</v>
       </c>
       <c r="W11">
-        <v>0.1555963302752293</v>
+        <v>0.05918807882459439</v>
       </c>
       <c r="X11">
-        <v>0.05109369214350699</v>
+        <v>0.08398527727912342</v>
       </c>
       <c r="Y11">
-        <v>0.1045026381317224</v>
+        <v>-0.02479719845452902</v>
       </c>
       <c r="Z11">
-        <v>1.735141815071004</v>
+        <v>2.977061942328592</v>
       </c>
       <c r="AA11">
-        <v>0.1996817551692762</v>
+        <v>0.1285340416837852</v>
       </c>
       <c r="AB11">
-        <v>0.04376171807020182</v>
+        <v>0.07191515514286217</v>
       </c>
       <c r="AC11">
-        <v>0.1559200370990744</v>
+        <v>0.05661888654092306</v>
       </c>
       <c r="AD11">
-        <v>462.4</v>
+        <v>2129.3</v>
       </c>
       <c r="AE11">
-        <v>53.20687411458593</v>
+        <v>59.17871678484325</v>
       </c>
       <c r="AF11">
-        <v>515.6068741145859</v>
+        <v>2188.478716784844</v>
       </c>
       <c r="AG11">
-        <v>332.0068741145859</v>
+        <v>758.6787167848436</v>
       </c>
       <c r="AH11">
-        <v>0.2576608380013299</v>
+        <v>0.2488157729301552</v>
       </c>
       <c r="AI11">
-        <v>0.448585166598877</v>
+        <v>0.3480748997897106</v>
       </c>
       <c r="AJ11">
-        <v>0.1826715919720116</v>
+        <v>0.1030004763862912</v>
       </c>
       <c r="AK11">
-        <v>0.3437611421216658</v>
+        <v>0.1561845439917032</v>
       </c>
       <c r="AL11">
-        <v>31.1</v>
+        <v>107.5</v>
       </c>
       <c r="AM11">
-        <v>31.1</v>
+        <v>107.5</v>
       </c>
       <c r="AN11">
-        <v>2.832118576590923</v>
+        <v>2.888361367335866</v>
       </c>
       <c r="AO11">
-        <v>4.520900321543408</v>
+        <v>4.967441860465116</v>
       </c>
       <c r="AP11">
-        <v>2.033483641297152</v>
+        <v>1.029135535519321</v>
       </c>
       <c r="AQ11">
-        <v>4.520900321543408</v>
+        <v>4.967441860465116</v>
       </c>
     </row>
     <row r="12">
@@ -1895,7 +1916,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Crawford &amp; Company (NYSE:CRD.B)</t>
+          <t>The Hartford Financial Services Group, Inc. (NYSE:HIG)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1904,121 +1925,124 @@
         </is>
       </c>
       <c r="D12">
-        <v>-0.01</v>
+        <v>0.0832</v>
+      </c>
+      <c r="E12">
+        <v>0.318</v>
       </c>
       <c r="F12">
-        <v>0.12</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G12">
-        <v>0.07866116632289519</v>
+        <v>0.171764174384459</v>
       </c>
       <c r="H12">
-        <v>0.07866116632289519</v>
+        <v>0.171764174384459</v>
       </c>
       <c r="I12">
-        <v>0.06685987488232081</v>
+        <v>0.1211702008609304</v>
       </c>
       <c r="J12">
-        <v>0.04953062297858583</v>
+        <v>0.09764540094110423</v>
       </c>
       <c r="K12">
-        <v>38.4</v>
+        <v>1955</v>
       </c>
       <c r="L12">
-        <v>0.03600225014063379</v>
+        <v>0.08832166252541224</v>
       </c>
       <c r="M12">
-        <v>18.75</v>
+        <v>2237</v>
       </c>
       <c r="N12">
-        <v>0.04867601246105919</v>
+        <v>0.09273922740802772</v>
       </c>
       <c r="O12">
-        <v>0.48828125</v>
+        <v>1.144245524296675</v>
       </c>
       <c r="P12">
-        <v>12.2</v>
+        <v>503</v>
       </c>
       <c r="Q12">
-        <v>0.03167185877466251</v>
+        <v>0.02085285265366024</v>
       </c>
       <c r="R12">
-        <v>0.3177083333333333</v>
+        <v>0.2572890025575448</v>
       </c>
       <c r="S12">
-        <v>6.550000000000001</v>
+        <v>1734</v>
       </c>
       <c r="T12">
-        <v>0.3493333333333334</v>
+        <v>0.7751452838623156</v>
       </c>
       <c r="U12">
-        <v>36.9</v>
+        <v>175</v>
       </c>
       <c r="V12">
-        <v>0.09579439252336448</v>
+        <v>0.00725496861707861</v>
       </c>
       <c r="W12">
-        <v>0.2098360655737705</v>
+        <v>0.1115358283888635</v>
       </c>
       <c r="X12">
-        <v>0.058894439468776</v>
+        <v>0.08009682728046619</v>
       </c>
       <c r="Y12">
-        <v>0.1509416261049945</v>
+        <v>0.03143900110839734</v>
       </c>
       <c r="Z12">
-        <v>3.16183002038371</v>
+        <v>1.060283701889651</v>
       </c>
       <c r="AA12">
-        <v>0.1566074106619999</v>
+        <v>0.1035318271823332</v>
       </c>
       <c r="AB12">
-        <v>0.04138639710714836</v>
+        <v>0.07303590000848924</v>
       </c>
       <c r="AC12">
-        <v>0.1152210135548515</v>
+        <v>0.03049592717384399</v>
       </c>
       <c r="AD12">
-        <v>140.6</v>
+        <v>4365</v>
       </c>
       <c r="AE12">
-        <v>136.4362872525831</v>
+        <v>169.4880197165315</v>
       </c>
       <c r="AF12">
-        <v>277.0362872525831</v>
+        <v>4534.488019716531</v>
       </c>
       <c r="AG12">
-        <v>240.1362872525831</v>
+        <v>4359.488019716531</v>
       </c>
       <c r="AH12">
-        <v>0.4183345017258453</v>
+        <v>0.1582393125139448</v>
       </c>
       <c r="AI12">
-        <v>0.5577130045901282</v>
+        <v>0.2592693402233752</v>
       </c>
       <c r="AJ12">
-        <v>0.384011438561518</v>
+        <v>0.1530671380997172</v>
       </c>
       <c r="AK12">
-        <v>0.5222212641967484</v>
+        <v>0.2517826697937733</v>
       </c>
       <c r="AL12">
-        <v>6.54</v>
+        <v>202</v>
       </c>
       <c r="AM12">
-        <v>4.84</v>
+        <v>202</v>
       </c>
       <c r="AN12">
-        <v>1.146818923327896</v>
+        <v>1.296791443850267</v>
       </c>
       <c r="AO12">
-        <v>9.26605504587156</v>
+        <v>13.23762376237624</v>
       </c>
       <c r="AP12">
-        <v>1.958697285910139</v>
+        <v>1.29515389771733</v>
       </c>
       <c r="AQ12">
-        <v>12.52066115702479</v>
+        <v>13.23762376237624</v>
       </c>
     </row>
     <row r="13">
@@ -2029,7 +2053,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>American National Group, Inc. (NasdaqGS:ANAT)</t>
+          <t>Horace Mann Educators Corporation (NYSE:HMN)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2038,115 +2062,124 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.06150000000000001</v>
+        <v>0.035</v>
       </c>
       <c r="E13">
-        <v>0.326</v>
+        <v>-0.0248</v>
+      </c>
+      <c r="F13">
+        <v>0.127</v>
       </c>
       <c r="G13">
-        <v>0.136614028644877</v>
+        <v>0.1515173674588665</v>
       </c>
       <c r="H13">
-        <v>0.136614028644877</v>
+        <v>0.1515173674588665</v>
       </c>
       <c r="I13">
-        <v>0.2090826044882863</v>
+        <v>0.06228777296790212</v>
       </c>
       <c r="J13">
-        <v>0.1661324635011475</v>
+        <v>0.05330850372366738</v>
       </c>
       <c r="K13">
-        <v>755.5</v>
+        <v>56.4</v>
       </c>
       <c r="L13">
-        <v>0.173407087770841</v>
+        <v>0.04124314442413163</v>
       </c>
       <c r="M13">
-        <v>88.2</v>
+        <v>82.3</v>
       </c>
       <c r="N13">
-        <v>0.01737759826618067</v>
+        <v>0.05384716042920701</v>
       </c>
       <c r="O13">
-        <v>0.1167438782263402</v>
+        <v>1.459219858156028</v>
       </c>
       <c r="P13">
-        <v>88.2</v>
+        <v>52.3</v>
       </c>
       <c r="Q13">
-        <v>0.01737759826618067</v>
+        <v>0.03421879089243653</v>
       </c>
       <c r="R13">
-        <v>0.1167438782263402</v>
+        <v>0.927304964539007</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>0.3645200486026732</v>
       </c>
       <c r="U13">
-        <v>504.5</v>
+        <v>35.2</v>
       </c>
       <c r="V13">
-        <v>0.09939907398285883</v>
+        <v>0.02303062025647736</v>
       </c>
       <c r="W13">
-        <v>0.1229154803546734</v>
+        <v>0.03139612558450233</v>
       </c>
       <c r="X13">
-        <v>0.04446765129093524</v>
+        <v>0.0840075374701095</v>
       </c>
       <c r="Y13">
-        <v>0.07844782906373815</v>
+        <v>-0.05261141188560717</v>
       </c>
       <c r="Z13">
-        <v>0.7354186627119594</v>
+        <v>0.6474269670968715</v>
       </c>
       <c r="AA13">
-        <v>0.1221769141410573</v>
+        <v>0.03451336288628625</v>
       </c>
       <c r="AB13">
-        <v>0.04364251071281185</v>
+        <v>0.07190943312111005</v>
       </c>
       <c r="AC13">
-        <v>0.07853440342824547</v>
+        <v>-0.0373960702348238</v>
       </c>
       <c r="AD13">
-        <v>150.4</v>
+        <v>497.9</v>
       </c>
       <c r="AE13">
-        <v>7.044543827171265</v>
+        <v>9.607352331969262</v>
       </c>
       <c r="AF13">
-        <v>157.4445438271713</v>
+        <v>507.5073523319692</v>
       </c>
       <c r="AG13">
-        <v>-347.0554561728287</v>
+        <v>472.3073523319692</v>
       </c>
       <c r="AH13">
-        <v>0.03008717988668431</v>
+        <v>0.2492782158042015</v>
       </c>
       <c r="AI13">
-        <v>0.02278092503148279</v>
+        <v>0.3203743430550121</v>
       </c>
       <c r="AJ13">
-        <v>-0.073397383210489</v>
+        <v>0.2360701837684861</v>
       </c>
       <c r="AK13">
-        <v>-0.05417032844039534</v>
+        <v>0.3049293759377431</v>
       </c>
       <c r="AL13">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AM13">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AN13">
-        <v>0.1560586880278914</v>
+        <v>4.547031963470319</v>
+      </c>
+      <c r="AO13">
+        <v>4.876470588235295</v>
       </c>
       <c r="AP13">
-        <v>-0.3601131593301395</v>
+        <v>4.313309153716614</v>
+      </c>
+      <c r="AQ13">
+        <v>4.876470588235295</v>
       </c>
     </row>
     <row r="14">
@@ -2157,7 +2190,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The Hartford Financial Services Group, Inc. (NYSE:HIG)</t>
+          <t>Atlantic American Corporation (NasdaqGM:AAME)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2166,124 +2199,121 @@
         </is>
       </c>
       <c r="D14">
-        <v>0.0365</v>
+        <v>0.0222</v>
       </c>
       <c r="E14">
-        <v>0.0922</v>
-      </c>
-      <c r="F14">
-        <v>0.07000000000000001</v>
+        <v>-0.0117</v>
       </c>
       <c r="G14">
-        <v>0.1372764283427108</v>
+        <v>0.03996881496881497</v>
       </c>
       <c r="H14">
-        <v>0.1372764283427108</v>
+        <v>0.03996881496881497</v>
       </c>
       <c r="I14">
-        <v>0.1315710089908453</v>
+        <v>0.03087567761925105</v>
       </c>
       <c r="J14">
-        <v>0.1079697139490585</v>
+        <v>0.02356143942595275</v>
       </c>
       <c r="K14">
-        <v>2173</v>
+        <v>3.14</v>
       </c>
       <c r="L14">
-        <v>0.09940075934312245</v>
+        <v>0.01632016632016632</v>
       </c>
       <c r="M14">
-        <v>1677</v>
+        <v>0.516</v>
       </c>
       <c r="N14">
-        <v>0.07136777598093455</v>
+        <v>0.01081761006289308</v>
       </c>
       <c r="O14">
-        <v>0.771744132535665</v>
+        <v>0.1643312101910828</v>
       </c>
       <c r="P14">
-        <v>481</v>
+        <v>0.408</v>
       </c>
       <c r="Q14">
-        <v>0.02046982721933781</v>
+        <v>0.008553459119496854</v>
       </c>
       <c r="R14">
-        <v>0.2213529682466636</v>
+        <v>0.1299363057324841</v>
       </c>
       <c r="S14">
-        <v>1196</v>
+        <v>0.108</v>
       </c>
       <c r="T14">
-        <v>0.7131782945736435</v>
+        <v>0.2093023255813954</v>
       </c>
       <c r="U14">
-        <v>232</v>
+        <v>21.9</v>
       </c>
       <c r="V14">
-        <v>0.009873180696229467</v>
+        <v>0.4591194968553459</v>
       </c>
       <c r="W14">
-        <v>0.1243989008472636</v>
+        <v>0.0224446032880629</v>
       </c>
       <c r="X14">
-        <v>0.04846242669988824</v>
+        <v>0.09715840139421963</v>
       </c>
       <c r="Y14">
-        <v>0.07593647414737534</v>
+        <v>-0.07471379810615673</v>
       </c>
       <c r="Z14">
-        <v>1.073373409075419</v>
+        <v>1.176020443433224</v>
       </c>
       <c r="AA14">
-        <v>0.1158918199383988</v>
+        <v>0.02770873444163399</v>
       </c>
       <c r="AB14">
-        <v>0.04337476308757741</v>
+        <v>0.07711841831041581</v>
       </c>
       <c r="AC14">
-        <v>0.07251705685082137</v>
+        <v>-0.04940968386878182</v>
       </c>
       <c r="AD14">
-        <v>4988</v>
+        <v>34.7</v>
       </c>
       <c r="AE14">
-        <v>218.6308622556529</v>
+        <v>4.247598130280487</v>
       </c>
       <c r="AF14">
-        <v>5206.630862255653</v>
+        <v>38.94759813028049</v>
       </c>
       <c r="AG14">
-        <v>4974.630862255653</v>
+        <v>17.04759813028049</v>
       </c>
       <c r="AH14">
-        <v>0.1813864420427704</v>
+        <v>0.4494942614764711</v>
       </c>
       <c r="AI14">
-        <v>0.2257017719579803</v>
+        <v>0.2846056391373558</v>
       </c>
       <c r="AJ14">
-        <v>0.1747162349107052</v>
+        <v>0.2632931355380709</v>
       </c>
       <c r="AK14">
-        <v>0.2178355858296818</v>
+        <v>0.1483075628162226</v>
       </c>
       <c r="AL14">
-        <v>188</v>
+        <v>1.64</v>
       </c>
       <c r="AM14">
-        <v>188</v>
+        <v>1.64</v>
       </c>
       <c r="AN14">
-        <v>1.390964863357501</v>
+        <v>4.494818652849741</v>
       </c>
       <c r="AO14">
-        <v>15.28191489361702</v>
+        <v>3.51219512195122</v>
       </c>
       <c r="AP14">
-        <v>1.387236715631805</v>
+        <v>2.208238099777266</v>
       </c>
       <c r="AQ14">
-        <v>15.28191489361702</v>
+        <v>3.51219512195122</v>
       </c>
     </row>
     <row r="15">
@@ -2294,7 +2324,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Atlantic American Corporation (NasdaqGM:AAME)</t>
+          <t>Goosehead Insurance, Inc (NasdaqGS:GSHD)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2302,122 +2332,116 @@
           <t>Insurance (General)</t>
         </is>
       </c>
-      <c r="D15">
-        <v>0.048</v>
-      </c>
-      <c r="E15">
-        <v>0.5720000000000001</v>
+      <c r="F15">
+        <v>0.195</v>
       </c>
       <c r="G15">
-        <v>0.08627264061010487</v>
+        <v>0.06390780513357779</v>
       </c>
       <c r="H15">
-        <v>0.08627264061010487</v>
+        <v>0.06390780513357779</v>
       </c>
       <c r="I15">
-        <v>0.08680691001861722</v>
+        <v>0.003091907057473982</v>
       </c>
       <c r="J15">
-        <v>0.06898324269526801</v>
+        <v>0.00243684200292441</v>
       </c>
       <c r="K15">
-        <v>13.5</v>
+        <v>0.34</v>
       </c>
       <c r="L15">
-        <v>0.06434699714013346</v>
+        <v>0.00178103719224725</v>
       </c>
       <c r="M15">
-        <v>0.5609999999999999</v>
+        <v>-0</v>
       </c>
       <c r="N15">
-        <v>0.01124248496993988</v>
+        <v>-0</v>
       </c>
       <c r="O15">
-        <v>0.04155555555555555</v>
+        <v>-0</v>
       </c>
       <c r="P15">
-        <v>0.408</v>
+        <v>-0</v>
       </c>
       <c r="Q15">
-        <v>0.008176352705410821</v>
+        <v>-0</v>
       </c>
       <c r="R15">
-        <v>0.03022222222222222</v>
+        <v>-0</v>
       </c>
       <c r="S15">
-        <v>0.153</v>
-      </c>
-      <c r="T15">
-        <v>0.2727272727272727</v>
+        <v>0</v>
       </c>
       <c r="U15">
-        <v>14.3</v>
+        <v>46.1</v>
       </c>
       <c r="V15">
-        <v>0.2865731462925852</v>
+        <v>0.05918603158300167</v>
       </c>
       <c r="W15">
-        <v>0.10546875</v>
+        <v>-0.01798941798941799</v>
       </c>
       <c r="X15">
-        <v>0.06030241352863829</v>
+        <v>0.08078431090757876</v>
       </c>
       <c r="Y15">
-        <v>0.04516633647136171</v>
+        <v>-0.09877372889699676</v>
       </c>
       <c r="Z15">
-        <v>1.324875086682386</v>
+        <v>1.524166607110199</v>
       </c>
       <c r="AA15">
-        <v>0.09139417964552528</v>
+        <v>0.003714153207660919</v>
       </c>
       <c r="AB15">
-        <v>0.04372230643448789</v>
+        <v>0.0738337941806165</v>
       </c>
       <c r="AC15">
-        <v>0.04767187321103739</v>
+        <v>-0.07011964097295559</v>
       </c>
       <c r="AD15">
-        <v>33.7</v>
+        <v>119.8</v>
       </c>
       <c r="AE15">
-        <v>5.539551390470539</v>
+        <v>46.34877471364108</v>
       </c>
       <c r="AF15">
-        <v>39.23955139047054</v>
+        <v>166.1487747136411</v>
       </c>
       <c r="AG15">
-        <v>24.93955139047054</v>
+        <v>120.0487747136411</v>
       </c>
       <c r="AH15">
-        <v>0.4402035996185801</v>
+        <v>0.1758097350731826</v>
       </c>
       <c r="AI15">
-        <v>0.2189223923295132</v>
+        <v>1.379414403414636</v>
       </c>
       <c r="AJ15">
-        <v>0.3332402576860735</v>
+        <v>0.1335435100313502</v>
       </c>
       <c r="AK15">
-        <v>0.1512041907488262</v>
+        <v>1.614670519803674</v>
       </c>
       <c r="AL15">
-        <v>1.4</v>
+        <v>4.36</v>
       </c>
       <c r="AM15">
-        <v>1.4</v>
+        <v>3.04</v>
       </c>
       <c r="AN15">
-        <v>1.658464566929134</v>
+        <v>7.358722358722358</v>
       </c>
       <c r="AO15">
-        <v>13.07142857142857</v>
+        <v>0.9587155963302751</v>
       </c>
       <c r="AP15">
-        <v>1.227340127483786</v>
+        <v>7.374003360788763</v>
       </c>
       <c r="AQ15">
-        <v>13.07142857142857</v>
+        <v>1.375</v>
       </c>
     </row>
     <row r="16">
@@ -2428,7 +2452,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Goosehead Insurance, Inc (NasdaqGS:GSHD)</t>
+          <t>eHealth, Inc. (NasdaqGS:EHTH)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2436,119 +2460,113 @@
           <t>Insurance (General)</t>
         </is>
       </c>
-      <c r="F16">
-        <v>0.341</v>
+      <c r="D16">
+        <v>0.245</v>
       </c>
       <c r="G16">
-        <v>0.1548030407740152</v>
+        <v>-0.1009944751381215</v>
       </c>
       <c r="H16">
-        <v>0.1548030407740152</v>
+        <v>-0.1604419889502762</v>
       </c>
       <c r="I16">
-        <v>0.0516325746897546</v>
+        <v>-0.2401079154985536</v>
       </c>
       <c r="J16">
-        <v>0.0516325746897546</v>
+        <v>-0.2401079154985536</v>
       </c>
       <c r="K16">
-        <v>7.92</v>
+        <v>-141.5</v>
       </c>
       <c r="L16">
-        <v>0.05473393227366966</v>
+        <v>-0.312707182320442</v>
       </c>
       <c r="M16">
-        <v>22.2</v>
+        <v>4.27</v>
       </c>
       <c r="N16">
-        <v>0.008483319958729795</v>
+        <v>0.03217784476262246</v>
       </c>
       <c r="O16">
-        <v>2.803030303030303</v>
+        <v>-0.03017667844522968</v>
       </c>
       <c r="P16">
-        <v>22.2</v>
+        <v>-0</v>
       </c>
       <c r="Q16">
-        <v>0.008483319958729795</v>
+        <v>-0</v>
       </c>
       <c r="R16">
-        <v>2.803030303030303</v>
+        <v>0</v>
       </c>
       <c r="S16">
+        <v>4.27</v>
+      </c>
+      <c r="T16">
+        <v>1</v>
+      </c>
+      <c r="U16">
+        <v>160.3</v>
+      </c>
+      <c r="V16">
+        <v>1.207987942727958</v>
+      </c>
+      <c r="W16">
+        <v>-0.1819467661051819</v>
+      </c>
+      <c r="X16">
+        <v>0.09676831848028891</v>
+      </c>
+      <c r="Y16">
+        <v>-0.2787150845854708</v>
+      </c>
+      <c r="Z16">
+        <v>0.5347788497807011</v>
+      </c>
+      <c r="AA16">
+        <v>-0.1284046348735583</v>
+      </c>
+      <c r="AB16">
+        <v>0.07332540904595992</v>
+      </c>
+      <c r="AC16">
+        <v>-0.2017300439195182</v>
+      </c>
+      <c r="AD16">
+        <v>65.7</v>
+      </c>
+      <c r="AE16">
+        <v>40.74415881547765</v>
+      </c>
+      <c r="AF16">
+        <v>106.4441588154776</v>
+      </c>
+      <c r="AG16">
+        <v>-53.85584118452236</v>
+      </c>
+      <c r="AH16">
+        <v>0.445104573503756</v>
+      </c>
+      <c r="AI16">
+        <v>0.106963556860122</v>
+      </c>
+      <c r="AJ16">
+        <v>-0.6830669765982729</v>
+      </c>
+      <c r="AK16">
+        <v>-0.06451005330256603</v>
+      </c>
+      <c r="AL16">
         <v>0</v>
       </c>
-      <c r="T16">
+      <c r="AM16">
         <v>0</v>
       </c>
-      <c r="U16">
-        <v>25.5</v>
-      </c>
-      <c r="V16">
-        <v>0.009744354006649088</v>
-      </c>
-      <c r="W16">
-        <v>-0.6545454545454545</v>
-      </c>
-      <c r="X16">
-        <v>0.04509663561472357</v>
-      </c>
-      <c r="Y16">
-        <v>-0.6996420901601781</v>
-      </c>
-      <c r="Z16">
-        <v>1.651942794897362</v>
-      </c>
-      <c r="AA16">
-        <v>0.08529405974074002</v>
-      </c>
-      <c r="AB16">
-        <v>0.04367701246980753</v>
-      </c>
-      <c r="AC16">
-        <v>0.04161704727093249</v>
-      </c>
-      <c r="AD16">
-        <v>123.3</v>
-      </c>
-      <c r="AE16">
-        <v>36.39383221196255</v>
-      </c>
-      <c r="AF16">
-        <v>159.6938322119626</v>
-      </c>
-      <c r="AG16">
-        <v>134.1938322119626</v>
-      </c>
-      <c r="AH16">
-        <v>0.05751429336164126</v>
-      </c>
-      <c r="AI16">
-        <v>1.901256651904718</v>
-      </c>
-      <c r="AJ16">
-        <v>0.04877835522755204</v>
-      </c>
-      <c r="AK16">
-        <v>2.294153539567862</v>
-      </c>
-      <c r="AL16">
-        <v>2.55</v>
-      </c>
-      <c r="AM16">
-        <v>1.47</v>
-      </c>
       <c r="AN16">
-        <v>6.47244094488189</v>
-      </c>
-      <c r="AO16">
-        <v>4.15686274509804</v>
+        <v>-0.6865203761755486</v>
       </c>
       <c r="AP16">
-        <v>7.044295654171263</v>
-      </c>
-      <c r="AQ16">
-        <v>7.210884353741497</v>
+        <v>0.5627569611757822</v>
       </c>
     </row>
     <row r="17">
@@ -2559,7 +2577,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Horace Mann Educators Corporation (NYSE:HMN)</t>
+          <t>Hagerty, Inc. (NYSE:HGTY)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2567,122 +2585,113 @@
           <t>Insurance (General)</t>
         </is>
       </c>
-      <c r="D17">
-        <v>0.0378</v>
-      </c>
-      <c r="E17">
-        <v>0.121</v>
-      </c>
       <c r="G17">
-        <v>0.1541080680977054</v>
+        <v>0.01624161073825503</v>
       </c>
       <c r="H17">
-        <v>0.1541080680977054</v>
+        <v>0.01624161073825503</v>
       </c>
       <c r="I17">
-        <v>0.1549137048892677</v>
+        <v>-0.07823386918352739</v>
       </c>
       <c r="J17">
-        <v>0.1264412566823224</v>
+        <v>-0.07823386918352739</v>
       </c>
       <c r="K17">
-        <v>150.1</v>
+        <v>-15</v>
       </c>
       <c r="L17">
-        <v>0.1111028867505551</v>
+        <v>-0.02013422818791946</v>
       </c>
       <c r="M17">
-        <v>54.94</v>
+        <v>-0</v>
       </c>
       <c r="N17">
-        <v>0.03421773791728949</v>
+        <v>-0</v>
       </c>
       <c r="O17">
-        <v>0.3660226515656229</v>
+        <v>0</v>
       </c>
       <c r="P17">
-        <v>51</v>
+        <v>-0</v>
       </c>
       <c r="Q17">
-        <v>0.03176382660687593</v>
+        <v>-0</v>
       </c>
       <c r="R17">
-        <v>0.3397734843437709</v>
+        <v>0</v>
       </c>
       <c r="S17">
-        <v>3.939999999999998</v>
-      </c>
-      <c r="T17">
-        <v>0.07171459774299231</v>
+        <v>0</v>
       </c>
       <c r="U17">
-        <v>38.9</v>
+        <v>180.4</v>
       </c>
       <c r="V17">
-        <v>0.02422770303936223</v>
+        <v>0.2578247820494498</v>
       </c>
       <c r="W17">
-        <v>0.08748615725359911</v>
+        <v>-0.1265822784810127</v>
       </c>
       <c r="X17">
-        <v>0.04907077118748827</v>
+        <v>0.08309330740141679</v>
       </c>
       <c r="Y17">
-        <v>0.03841538606611084</v>
+        <v>-0.2096755858824295</v>
       </c>
       <c r="Z17">
-        <v>0.6583634821153127</v>
+        <v>2.982730239635589</v>
       </c>
       <c r="AA17">
-        <v>0.08324430603240981</v>
+        <v>-0.2333505273774019</v>
       </c>
       <c r="AB17">
-        <v>0.04265292584971195</v>
+        <v>0.07347750857768411</v>
       </c>
       <c r="AC17">
-        <v>0.04059138018269786</v>
+        <v>-0.3068280359550861</v>
       </c>
       <c r="AD17">
-        <v>388.6</v>
+        <v>136</v>
       </c>
       <c r="AE17">
-        <v>13.75792347299656</v>
+        <v>72.77116270863954</v>
       </c>
       <c r="AF17">
-        <v>402.3579234729966</v>
+        <v>208.7711627086395</v>
       </c>
       <c r="AG17">
-        <v>363.4579234729966</v>
+        <v>28.37116270863953</v>
       </c>
       <c r="AH17">
-        <v>0.2003816508152082</v>
+        <v>0.2298049418389691</v>
       </c>
       <c r="AI17">
-        <v>0.1829932796046331</v>
+        <v>0.3487825269829462</v>
       </c>
       <c r="AJ17">
-        <v>0.1845846783582347</v>
+        <v>0.03896756822930664</v>
       </c>
       <c r="AK17">
-        <v>0.1682786258869127</v>
+        <v>0.0678458134818998</v>
       </c>
       <c r="AL17">
-        <v>13.9</v>
+        <v>1.33</v>
       </c>
       <c r="AM17">
-        <v>13.9</v>
+        <v>1.33</v>
       </c>
       <c r="AN17">
-        <v>1.656154108421412</v>
+        <v>-10.85395051875499</v>
       </c>
       <c r="AO17">
-        <v>14.94964028776979</v>
+        <v>-39.69924812030074</v>
       </c>
       <c r="AP17">
-        <v>1.549002401436228</v>
+        <v>-2.264258795581766</v>
       </c>
       <c r="AQ17">
-        <v>14.94964028776979</v>
+        <v>-39.69924812030074</v>
       </c>
     </row>
     <row r="18">
@@ -2693,7 +2702,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The Marketing Alliance, Inc. (OTCPK:MAAL)</t>
+          <t>SelectQuote, Inc. (NYSE:SLQT)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2701,122 +2710,116 @@
           <t>Insurance (General)</t>
         </is>
       </c>
-      <c r="D18">
-        <v>-0.00155</v>
-      </c>
-      <c r="E18">
-        <v>0.174</v>
-      </c>
       <c r="G18">
-        <v>0.08782287822878228</v>
+        <v>-0.3305645684620376</v>
       </c>
       <c r="H18">
-        <v>0.08782287822878228</v>
+        <v>-0.3631408176508761</v>
       </c>
       <c r="I18">
-        <v>0.04907749077490775</v>
+        <v>-0.3649976031113151</v>
       </c>
       <c r="J18">
-        <v>0.03693548181156552</v>
+        <v>-0.3649976031113151</v>
       </c>
       <c r="K18">
-        <v>1.69</v>
+        <v>-291.8</v>
       </c>
       <c r="L18">
-        <v>0.06236162361623616</v>
+        <v>-0.3787151200519144</v>
       </c>
       <c r="M18">
-        <v>0.6424</v>
+        <v>7.87</v>
       </c>
       <c r="N18">
-        <v>0.022</v>
+        <v>0.07070979335130279</v>
       </c>
       <c r="O18">
-        <v>0.3801183431952663</v>
+        <v>-0.02697052775873886</v>
       </c>
       <c r="P18">
-        <v>0.6424</v>
+        <v>-0</v>
       </c>
       <c r="Q18">
-        <v>0.022</v>
+        <v>-0</v>
       </c>
       <c r="R18">
-        <v>0.3801183431952663</v>
+        <v>0</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>7.87</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U18">
-        <v>1.2</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="V18">
-        <v>0.0410958904109589</v>
+        <v>0.6388140161725067</v>
       </c>
       <c r="W18">
-        <v>0.2315068493150685</v>
+        <v>-0.460397601767119</v>
       </c>
       <c r="X18">
-        <v>0.04381734796752063</v>
+        <v>0.2533299551484498</v>
       </c>
       <c r="Y18">
-        <v>0.1876895013475479</v>
+        <v>-0.7137275569155688</v>
       </c>
       <c r="Z18">
-        <v>2.04066265060241</v>
+        <v>0.8759630958577692</v>
       </c>
       <c r="AA18">
-        <v>0.07537285821486639</v>
+        <v>-0.3197244304020529</v>
       </c>
       <c r="AB18">
-        <v>0.04381734796752063</v>
+        <v>0.07909599690303717</v>
       </c>
       <c r="AC18">
-        <v>0.03155551024734576</v>
+        <v>-0.39882042730509</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>690.5</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>40.70326598634115</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>731.2032659863412</v>
       </c>
       <c r="AG18">
-        <v>-1.2</v>
+        <v>660.1032659863412</v>
       </c>
       <c r="AH18">
-        <v>0</v>
+        <v>0.867893687189808</v>
       </c>
       <c r="AI18">
-        <v>0</v>
+        <v>0.6721215836441119</v>
       </c>
       <c r="AJ18">
-        <v>-0.04285714285714286</v>
+        <v>0.855717489272374</v>
       </c>
       <c r="AK18">
-        <v>-0.1929260450160772</v>
+        <v>0.6491946751823361</v>
       </c>
       <c r="AL18">
-        <v>0.227</v>
+        <v>51.8</v>
       </c>
       <c r="AM18">
-        <v>-1.083</v>
+        <v>51.8</v>
       </c>
       <c r="AN18">
-        <v>0</v>
+        <v>-2.725048344449268</v>
       </c>
       <c r="AO18">
-        <v>5.859030837004405</v>
+        <v>-5.440154440154441</v>
       </c>
       <c r="AP18">
-        <v>-0.7100591715976331</v>
+        <v>-2.605088069719962</v>
       </c>
       <c r="AQ18">
-        <v>-1.228070175438597</v>
+        <v>-5.440154440154441</v>
       </c>
     </row>
     <row r="19">
@@ -2827,7 +2830,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>American International Group, Inc. (NYSE:AIG)</t>
+          <t>GoHealth, Inc. (NasdaqCM:GOCO)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2835,125 +2838,113 @@
           <t>Insurance (General)</t>
         </is>
       </c>
-      <c r="D19">
-        <v>-0.0229</v>
-      </c>
-      <c r="E19">
-        <v>0.7390000000000001</v>
-      </c>
-      <c r="F19">
-        <v>0.32</v>
-      </c>
       <c r="G19">
-        <v>0.1448213229703472</v>
+        <v>0.04952366834667457</v>
       </c>
       <c r="H19">
-        <v>0.1448213229703472</v>
+        <v>0.0004081430971439866</v>
       </c>
       <c r="I19">
-        <v>0.1668608435489365</v>
+        <v>-0.1755140967305918</v>
       </c>
       <c r="J19">
-        <v>0.1490774300673619</v>
+        <v>-0.1755140967305918</v>
       </c>
       <c r="K19">
-        <v>5589</v>
+        <v>-242.3</v>
       </c>
       <c r="L19">
-        <v>0.1180408887387007</v>
+        <v>-0.2394505385907699</v>
       </c>
       <c r="M19">
-        <v>2746</v>
+        <v>-0</v>
       </c>
       <c r="N19">
-        <v>0.0581647804417219</v>
+        <v>-0</v>
       </c>
       <c r="O19">
-        <v>0.4913222401145106</v>
+        <v>0</v>
       </c>
       <c r="P19">
-        <v>1095</v>
+        <v>-0</v>
       </c>
       <c r="Q19">
-        <v>0.02319389460440112</v>
+        <v>-0</v>
       </c>
       <c r="R19">
-        <v>0.1959205582393988</v>
+        <v>0</v>
       </c>
       <c r="S19">
-        <v>1651</v>
-      </c>
-      <c r="T19">
-        <v>0.601238164603059</v>
+        <v>0</v>
       </c>
       <c r="U19">
-        <v>2699</v>
+        <v>215.4</v>
       </c>
       <c r="V19">
-        <v>0.05716924341303985</v>
+        <v>2.318622174381055</v>
       </c>
       <c r="W19">
-        <v>0.08784559043113339</v>
+        <v>-0.4871330920788098</v>
       </c>
       <c r="X19">
-        <v>0.05831423887953722</v>
+        <v>0.2767036561989509</v>
       </c>
       <c r="Y19">
-        <v>0.02953135155159618</v>
+        <v>-0.7638367482777607</v>
       </c>
       <c r="Z19">
-        <v>0.479030217032956</v>
+        <v>2.049568933387344</v>
       </c>
       <c r="AA19">
-        <v>0.07141259367988369</v>
+        <v>-0.3597282400305622</v>
       </c>
       <c r="AB19">
-        <v>0.04315887238579513</v>
+        <v>0.07915976933291002</v>
       </c>
       <c r="AC19">
-        <v>0.02825372129408855</v>
+        <v>-0.4388880093634722</v>
       </c>
       <c r="AD19">
-        <v>31550</v>
+        <v>665.7</v>
       </c>
       <c r="AE19">
-        <v>1097.363898224773</v>
+        <v>24.61357240842958</v>
       </c>
       <c r="AF19">
-        <v>32647.36389822477</v>
+        <v>690.3135724084296</v>
       </c>
       <c r="AG19">
-        <v>29948.36389822477</v>
+        <v>474.9135724084297</v>
       </c>
       <c r="AH19">
-        <v>0.4088173730311351</v>
+        <v>0.881386120883571</v>
       </c>
       <c r="AI19">
-        <v>0.332098173542703</v>
+        <v>0.4834082712842671</v>
       </c>
       <c r="AJ19">
-        <v>0.3881379890472441</v>
+        <v>0.8363899622794209</v>
       </c>
       <c r="AK19">
-        <v>0.313243276219865</v>
+        <v>0.3916446122775792</v>
       </c>
       <c r="AL19">
-        <v>1366</v>
+        <v>49.4</v>
       </c>
       <c r="AM19">
-        <v>1366</v>
+        <v>49.4</v>
       </c>
       <c r="AN19">
-        <v>2.502577932894424</v>
+        <v>-10.07415254237288</v>
       </c>
       <c r="AO19">
-        <v>5.773792093704246</v>
+        <v>-3.647773279352227</v>
       </c>
       <c r="AP19">
-        <v>2.375534536227871</v>
+        <v>-7.186948734994396</v>
       </c>
       <c r="AQ19">
-        <v>5.773792093704246</v>
+        <v>-3.647773279352227</v>
       </c>
     </row>
     <row r="20">
@@ -2964,7 +2955,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>eHealth, Inc. (NasdaqGS:EHTH)</t>
+          <t>Reliance Global Group, Inc. (NasdaqCM:RELI)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2972,35 +2963,32 @@
           <t>Insurance (General)</t>
         </is>
       </c>
-      <c r="D20">
-        <v>0.249</v>
-      </c>
       <c r="G20">
-        <v>0.1346938775510204</v>
+        <v>-0.1006578947368421</v>
       </c>
       <c r="H20">
-        <v>0.09948979591836735</v>
+        <v>-0.1006578947368421</v>
       </c>
       <c r="I20">
-        <v>-0.02795120499156573</v>
+        <v>-0.4300809731665705</v>
       </c>
       <c r="J20">
-        <v>-0.02795120499156573</v>
+        <v>-0.4300809731665705</v>
       </c>
       <c r="K20">
-        <v>-12.4</v>
+        <v>7.35</v>
       </c>
       <c r="L20">
-        <v>-0.02108843537414966</v>
+        <v>0.4835526315789473</v>
       </c>
       <c r="M20">
-        <v>10.6</v>
+        <v>-0</v>
       </c>
       <c r="N20">
-        <v>0.01575271214147719</v>
+        <v>-0</v>
       </c>
       <c r="O20">
-        <v>-0.8548387096774193</v>
+        <v>-0</v>
       </c>
       <c r="P20">
         <v>-0</v>
@@ -3009,64 +2997,61 @@
         <v>-0</v>
       </c>
       <c r="R20">
+        <v>-0</v>
+      </c>
+      <c r="S20">
         <v>0</v>
       </c>
-      <c r="S20">
-        <v>10.6</v>
-      </c>
-      <c r="T20">
-        <v>1</v>
-      </c>
       <c r="U20">
-        <v>157.5</v>
+        <v>1.62</v>
       </c>
       <c r="V20">
-        <v>0.2340615247436469</v>
+        <v>0.1572815533980582</v>
       </c>
       <c r="W20">
-        <v>-0.01598556142838726</v>
+        <v>0.5742187499999999</v>
       </c>
       <c r="X20">
-        <v>0.04543352037199334</v>
+        <v>0.1187194552912791</v>
       </c>
       <c r="Y20">
-        <v>-0.06141908180038061</v>
+        <v>0.4554992947087207</v>
       </c>
       <c r="Z20">
-        <v>0.840508456374865</v>
+        <v>2.215370779777588</v>
       </c>
       <c r="AA20">
-        <v>-0.02349322416127833</v>
+        <v>-0.9527888208915289</v>
       </c>
       <c r="AB20">
-        <v>0.04364270196613497</v>
+        <v>0.09752980510868717</v>
       </c>
       <c r="AC20">
-        <v>-0.0671359261274133</v>
+        <v>-1.050318626000216</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>15.7</v>
       </c>
       <c r="AE20">
-        <v>51.87654267520324</v>
+        <v>0.8911539606593526</v>
       </c>
       <c r="AF20">
-        <v>51.87654267520324</v>
+        <v>16.59115396065935</v>
       </c>
       <c r="AG20">
-        <v>-105.6234573247968</v>
+        <v>14.97115396065935</v>
       </c>
       <c r="AH20">
-        <v>0.07157591287891731</v>
+        <v>0.6169744141486648</v>
       </c>
       <c r="AI20">
-        <v>0.0491731717026191</v>
+        <v>0.3687648015244686</v>
       </c>
       <c r="AJ20">
-        <v>-0.1861939448909523</v>
+        <v>0.5924206699846617</v>
       </c>
       <c r="AK20">
-        <v>-0.1176893793903</v>
+        <v>0.3451868948250542</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3075,10 +3060,10 @@
         <v>0</v>
       </c>
       <c r="AN20">
-        <v>-0</v>
+        <v>-4.176642724128757</v>
       </c>
       <c r="AP20">
-        <v>182.1094091806838</v>
+        <v>-3.982749124942631</v>
       </c>
     </row>
     <row r="21">
@@ -3089,7 +3074,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Reliance Global Group, Inc. (NasdaqCM:RELI)</t>
+          <t>Marpai, Inc. (NasdaqCM:MRAI)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3098,22 +3083,22 @@
         </is>
       </c>
       <c r="G21">
-        <v>-0.2729281767955801</v>
+        <v>-0.6681415929203539</v>
       </c>
       <c r="H21">
-        <v>-0.2729281767955801</v>
+        <v>-0.6681415929203539</v>
       </c>
       <c r="I21">
-        <v>-0.2893675475622262</v>
+        <v>-1.027513021453123</v>
       </c>
       <c r="J21">
-        <v>-0.2893675475622262</v>
+        <v>-1.027513021453123</v>
       </c>
       <c r="K21">
-        <v>-2.84</v>
+        <v>-23.7</v>
       </c>
       <c r="L21">
-        <v>-0.3138121546961326</v>
+        <v>-1.048672566371681</v>
       </c>
       <c r="M21">
         <v>-0</v>
@@ -3137,67 +3122,73 @@
         <v>0</v>
       </c>
       <c r="U21">
-        <v>5.66</v>
+        <v>4.75</v>
       </c>
       <c r="V21">
-        <v>0.0801699716713881</v>
+        <v>0.3145695364238411</v>
       </c>
       <c r="W21">
-        <v>-15.02645502645503</v>
+        <v>-5.129870129870129</v>
       </c>
       <c r="X21">
-        <v>0.04650131504144524</v>
+        <v>0.07865934567326352</v>
       </c>
       <c r="Y21">
-        <v>-15.07295634149647</v>
+        <v>-5.208529475543393</v>
       </c>
       <c r="Z21">
-        <v>1.534189143871472</v>
+        <v>1.936760248904606</v>
       </c>
       <c r="AA21">
-        <v>-0.4439445500586793</v>
+        <v>-1.990046375182275</v>
       </c>
       <c r="AB21">
-        <v>0.04379284326777613</v>
+        <v>0.07454792518466717</v>
       </c>
       <c r="AC21">
-        <v>-0.4877373933264555</v>
+        <v>-2.064594300366942</v>
       </c>
       <c r="AD21">
-        <v>8.58</v>
+        <v>0</v>
       </c>
       <c r="AE21">
-        <v>0.4588815271907364</v>
+        <v>2.038971424202927</v>
       </c>
       <c r="AF21">
-        <v>9.038881527190737</v>
+        <v>2.038971424202927</v>
       </c>
       <c r="AG21">
-        <v>3.378881527190737</v>
+        <v>-2.711028575797073</v>
       </c>
       <c r="AH21">
-        <v>0.1134983484681993</v>
+        <v>0.1189669656210278</v>
       </c>
       <c r="AI21">
-        <v>0.4138893979500177</v>
+        <v>0.1271260712595388</v>
       </c>
       <c r="AJ21">
-        <v>0.04567359572675938</v>
+        <v>-0.21882596084618</v>
       </c>
       <c r="AK21">
-        <v>0.2088451863320763</v>
+        <v>-0.2401484133430242</v>
       </c>
       <c r="AL21">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="AM21">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="AN21">
-        <v>-6.61526599845798</v>
+        <v>-0</v>
+      </c>
+      <c r="AO21">
+        <v>-473.9999999999999</v>
       </c>
       <c r="AP21">
-        <v>-2.605151524433876</v>
+        <v>0.1237121737609324</v>
+      </c>
+      <c r="AQ21">
+        <v>-473.9999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -3208,7 +3199,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BRP Group, Inc. (NasdaqGS:BRP)</t>
+          <t>Hippo Holdings Inc. (NYSE:HIPO)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3216,35 +3207,32 @@
           <t>Insurance (General)</t>
         </is>
       </c>
-      <c r="F22">
-        <v>0.5</v>
-      </c>
       <c r="G22">
-        <v>0.03914590747330961</v>
+        <v>-1.800862068965517</v>
       </c>
       <c r="H22">
-        <v>0.03914590747330961</v>
+        <v>-1.800862068965517</v>
       </c>
       <c r="I22">
-        <v>0.05647371229486583</v>
+        <v>-2.373483700753234</v>
       </c>
       <c r="J22">
-        <v>0.05647371229486583</v>
+        <v>-2.373483700753234</v>
       </c>
       <c r="K22">
-        <v>-18.3</v>
+        <v>-331</v>
       </c>
       <c r="L22">
-        <v>-0.03830856185890727</v>
+        <v>-2.853448275862069</v>
       </c>
       <c r="M22">
-        <v>45.7</v>
+        <v>3.5</v>
       </c>
       <c r="N22">
-        <v>0.02222978888996984</v>
+        <v>0.01116071428571428</v>
       </c>
       <c r="O22">
-        <v>-2.497267759562841</v>
+        <v>-0.01057401812688822</v>
       </c>
       <c r="P22">
         <v>-0</v>
@@ -3256,79 +3244,73 @@
         <v>0</v>
       </c>
       <c r="S22">
-        <v>45.7</v>
+        <v>3.5</v>
       </c>
       <c r="T22">
         <v>1</v>
       </c>
       <c r="U22">
-        <v>374.5</v>
+        <v>346.5</v>
       </c>
       <c r="V22">
-        <v>0.1821675260239323</v>
+        <v>1.104910714285714</v>
       </c>
       <c r="W22">
-        <v>-0.0819158460161146</v>
+        <v>-0.3672065675615709</v>
       </c>
       <c r="X22">
-        <v>0.05109734728044026</v>
+        <v>0.07764440159137836</v>
       </c>
       <c r="Y22">
-        <v>-0.1330131932965549</v>
+        <v>-0.4448509691529492</v>
       </c>
       <c r="Z22">
-        <v>-23.78100351198571</v>
+        <v>1.158603344950143</v>
       </c>
       <c r="AA22">
-        <v>-1.343001550419074</v>
+        <v>-2.749926154877341</v>
       </c>
       <c r="AB22">
-        <v>0.04787427954035479</v>
+        <v>0.07440689448871776</v>
       </c>
       <c r="AC22">
-        <v>-1.390875829959429</v>
+        <v>-2.824333049366059</v>
       </c>
       <c r="AD22">
-        <v>663.8</v>
+        <v>0</v>
       </c>
       <c r="AE22">
-        <v>50.11253818371299</v>
+        <v>30.6205464368755</v>
       </c>
       <c r="AF22">
-        <v>713.912538183713</v>
+        <v>30.6205464368755</v>
       </c>
       <c r="AG22">
-        <v>339.412538183713</v>
+        <v>-315.8794535631245</v>
       </c>
       <c r="AH22">
-        <v>0.2577569073835632</v>
+        <v>0.0889561844981</v>
       </c>
       <c r="AI22">
-        <v>0.3910537001975122</v>
+        <v>0.04572820622038972</v>
       </c>
       <c r="AJ22">
-        <v>0.1417045597302564</v>
+        <v>138.5768320413347</v>
       </c>
       <c r="AK22">
-        <v>0.2338981500418562</v>
+        <v>-0.9775901193730941</v>
       </c>
       <c r="AL22">
-        <v>23.7</v>
+        <v>0</v>
       </c>
       <c r="AM22">
-        <v>23.7</v>
+        <v>0</v>
       </c>
       <c r="AN22">
-        <v>8.402531645569619</v>
-      </c>
-      <c r="AO22">
-        <v>1.092827004219409</v>
+        <v>-0</v>
       </c>
       <c r="AP22">
-        <v>4.29636124283181</v>
-      </c>
-      <c r="AQ22">
-        <v>1.092827004219409</v>
+        <v>1.202892054695828</v>
       </c>
     </row>
     <row r="23">
@@ -3339,7 +3321,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Marpai, Inc. (NasdaqCM:MRAI)</t>
+          <t>Quad M Solutions, Inc. (OTCPK:MMMM)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3348,22 +3330,22 @@
         </is>
       </c>
       <c r="G23">
-        <v>-0.3949579831932773</v>
+        <v>0.03106796116504855</v>
       </c>
       <c r="H23">
-        <v>-0.3949579831932773</v>
+        <v>0</v>
       </c>
       <c r="I23">
-        <v>-1.291391774813788</v>
+        <v>-0.03902912621359223</v>
       </c>
       <c r="J23">
-        <v>-1.291391774813788</v>
+        <v>-0.03902912621359223</v>
       </c>
       <c r="K23">
-        <v>-11.1</v>
+        <v>-9.77</v>
       </c>
       <c r="L23">
-        <v>-1.332533013205282</v>
+        <v>-0.1897087378640777</v>
       </c>
       <c r="M23">
         <v>-0</v>
@@ -3387,192 +3369,58 @@
         <v>0</v>
       </c>
       <c r="U23">
-        <v>1.19</v>
+        <v>0.785</v>
       </c>
       <c r="V23">
-        <v>0.01350737797956867</v>
+        <v>0.1068027210884354</v>
       </c>
       <c r="W23">
-        <v>3.95017793594306</v>
+        <v>0.7816</v>
       </c>
       <c r="X23">
-        <v>0.04579032795861868</v>
+        <v>0.09316466847550452</v>
       </c>
       <c r="Y23">
-        <v>3.904387607984442</v>
-      </c>
-      <c r="Z23">
-        <v>2.153864297545517</v>
-      </c>
-      <c r="AA23">
-        <v>-2.781482637915359</v>
+        <v>0.6884353315244954</v>
       </c>
       <c r="AB23">
-        <v>0.04379877622516076</v>
-      </c>
-      <c r="AC23">
-        <v>-2.82528141414052</v>
+        <v>0.1022710116784807</v>
       </c>
       <c r="AD23">
-        <v>7.88</v>
+        <v>4.92</v>
       </c>
       <c r="AE23">
-        <v>0.4114674209942723</v>
+        <v>0</v>
       </c>
       <c r="AF23">
-        <v>8.291467420994271</v>
+        <v>4.92</v>
       </c>
       <c r="AG23">
-        <v>7.101467420994272</v>
+        <v>4.135</v>
       </c>
       <c r="AH23">
-        <v>0.08601868653768802</v>
+        <v>0.4009779951100245</v>
       </c>
       <c r="AI23">
-        <v>0.6421785495514012</v>
+        <v>2.86046511627907</v>
       </c>
       <c r="AJ23">
-        <v>0.07459409621902764</v>
+        <v>0.3600348280365694</v>
       </c>
       <c r="AK23">
-        <v>0.6058513977759186</v>
+        <v>4.42245989304813</v>
       </c>
       <c r="AL23">
-        <v>0.541</v>
+        <v>2.16</v>
       </c>
       <c r="AM23">
-        <v>0.541</v>
-      </c>
-      <c r="AN23">
-        <v>-0.7744471744471744</v>
+        <v>2.16</v>
       </c>
       <c r="AO23">
-        <v>-19.9630314232902</v>
-      </c>
-      <c r="AP23">
-        <v>-0.697932916068233</v>
+        <v>-0.9305555555555554</v>
       </c>
       <c r="AQ23">
-        <v>-19.9630314232902</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Hippo Holdings Inc. (NYSE:HIPO)</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Insurance (General)</t>
-        </is>
-      </c>
-      <c r="G24">
-        <v>-1.441059602649007</v>
-      </c>
-      <c r="H24">
-        <v>-1.441059602649007</v>
-      </c>
-      <c r="I24">
-        <v>-2.389407419302705</v>
-      </c>
-      <c r="J24">
-        <v>-2.389407419302705</v>
-      </c>
-      <c r="K24">
-        <v>-364.8</v>
-      </c>
-      <c r="L24">
-        <v>-4.831788079470199</v>
-      </c>
-      <c r="M24">
-        <v>-0</v>
-      </c>
-      <c r="N24">
-        <v>-0</v>
-      </c>
-      <c r="O24">
-        <v>0</v>
-      </c>
-      <c r="P24">
-        <v>-0</v>
-      </c>
-      <c r="Q24">
-        <v>-0</v>
-      </c>
-      <c r="R24">
-        <v>0</v>
-      </c>
-      <c r="S24">
-        <v>0</v>
-      </c>
-      <c r="U24">
-        <v>778.7</v>
-      </c>
-      <c r="V24">
-        <v>0.4890410098599511</v>
-      </c>
-      <c r="X24">
-        <v>0.0441070093866095</v>
-      </c>
-      <c r="Z24">
-        <v>3.431615281828981</v>
-      </c>
-      <c r="AA24">
-        <v>-8.199527014594711</v>
-      </c>
-      <c r="AB24">
-        <v>0.04381440541918747</v>
-      </c>
-      <c r="AC24">
-        <v>-8.243341420013898</v>
-      </c>
-      <c r="AD24">
-        <v>0</v>
-      </c>
-      <c r="AE24">
-        <v>22.00130078677119</v>
-      </c>
-      <c r="AF24">
-        <v>22.00130078677119</v>
-      </c>
-      <c r="AG24">
-        <v>-756.6986992132289</v>
-      </c>
-      <c r="AH24">
-        <v>0.01362899278842697</v>
-      </c>
-      <c r="AI24">
-        <v>0.02376717065004863</v>
-      </c>
-      <c r="AJ24">
-        <v>-0.9055738645939752</v>
-      </c>
-      <c r="AK24">
-        <v>-5.147564648498167</v>
-      </c>
-      <c r="AL24">
-        <v>25.4</v>
-      </c>
-      <c r="AM24">
-        <v>25.4</v>
-      </c>
-      <c r="AN24">
-        <v>-0</v>
-      </c>
-      <c r="AO24">
-        <v>-7.043307086614174</v>
-      </c>
-      <c r="AP24">
-        <v>4.477507095936265</v>
-      </c>
-      <c r="AQ24">
-        <v>-7.043307086614174</v>
+        <v>-0.9305555555555554</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/united_states/united_states_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/united_states/united_states_insurance_general.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0675</v>
+        <v>0.0696</v>
       </c>
       <c r="E2">
-        <v>0.09845000000000001</v>
+        <v>0.103</v>
       </c>
       <c r="F2">
-        <v>0.121</v>
+        <v>0.127</v>
       </c>
       <c r="G2">
-        <v>0.2214626804977691</v>
+        <v>0.2921100512451931</v>
       </c>
       <c r="H2">
-        <v>0.2206847751190767</v>
+        <v>0.2911392882643509</v>
       </c>
       <c r="I2">
-        <v>0.2185703390077878</v>
+        <v>0.1526842609946213</v>
       </c>
       <c r="J2">
-        <v>0.1961365270528074</v>
+        <v>0.1317797638013485</v>
       </c>
       <c r="K2">
-        <v>20197.72</v>
+        <v>9418.43</v>
       </c>
       <c r="L2">
-        <v>0.1520998550369938</v>
+        <v>0.08883660300868612</v>
       </c>
       <c r="M2">
-        <v>13786.246</v>
+        <v>7395.97</v>
       </c>
       <c r="N2">
-        <v>0.06102478285263415</v>
+        <v>0.03197388810450375</v>
       </c>
       <c r="O2">
-        <v>0.6825644676725887</v>
+        <v>0.7852656971491002</v>
       </c>
       <c r="P2">
-        <v>3403.408</v>
+        <v>3084.824</v>
       </c>
       <c r="Q2">
-        <v>0.01506517685517275</v>
+        <v>0.01333615704202257</v>
       </c>
       <c r="R2">
-        <v>0.1685045638814678</v>
+        <v>0.3275305969253899</v>
       </c>
       <c r="S2">
-        <v>10382.838</v>
+        <v>4311.146</v>
       </c>
       <c r="T2">
-        <v>0.7531301849684099</v>
+        <v>0.5829047440700813</v>
       </c>
       <c r="U2">
-        <v>7944.585</v>
+        <v>9668.162</v>
       </c>
       <c r="V2">
-        <v>0.03516668529484347</v>
+        <v>0.04179691507188579</v>
       </c>
       <c r="W2">
-        <v>0.03139612558450233</v>
+        <v>0.1062001227747084</v>
       </c>
       <c r="X2">
-        <v>0.0840075374701095</v>
+        <v>0.07648584056301141</v>
       </c>
       <c r="Y2">
-        <v>-0.05261141188560717</v>
+        <v>0.029714282211697</v>
       </c>
       <c r="Z2">
-        <v>0.9863525347406512</v>
+        <v>1.192114209344289</v>
       </c>
       <c r="AA2">
-        <v>0.03451336288628625</v>
+        <v>0.08695027790640467</v>
       </c>
       <c r="AB2">
-        <v>0.07440689448871776</v>
+        <v>0.06653971840958052</v>
       </c>
       <c r="AC2">
-        <v>-0.0373960702348238</v>
+        <v>0.0218682928291801</v>
       </c>
       <c r="AD2">
-        <v>64470.14</v>
+        <v>55883</v>
       </c>
       <c r="AE2">
-        <v>4408.181286541706</v>
+        <v>4102.372273142742</v>
       </c>
       <c r="AF2">
-        <v>68878.3212865417</v>
+        <v>59985.37227314274</v>
       </c>
       <c r="AG2">
-        <v>60933.7362865417</v>
+        <v>50317.21027314274</v>
       </c>
       <c r="AH2">
-        <v>0.2336517107244612</v>
+        <v>0.2059242910040652</v>
       </c>
       <c r="AI2">
-        <v>0.4415462078889338</v>
+        <v>0.425415876505296</v>
       </c>
       <c r="AJ2">
-        <v>0.2124266651779907</v>
+        <v>0.1786642265208419</v>
       </c>
       <c r="AK2">
-        <v>0.4115785125488376</v>
+        <v>0.3831184404870032</v>
       </c>
       <c r="AL2">
-        <v>2521.352</v>
+        <v>2766.424</v>
       </c>
       <c r="AM2">
-        <v>2354.298</v>
+        <v>2313.62</v>
       </c>
       <c r="AN2">
-        <v>1.715849910220817</v>
+        <v>2.328436601258388</v>
       </c>
       <c r="AO2">
-        <v>11.49292522424477</v>
+        <v>5.835681732084453</v>
       </c>
       <c r="AP2">
-        <v>1.621729779657397</v>
+        <v>2.09653086042625</v>
       </c>
       <c r="AQ2">
-        <v>12.30842909436274</v>
+        <v>6.977796699544437</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown, Inc. (NYSE:BRO)</t>
+          <t>Abacus Life, Inc. (NasdaqCM:ABL)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,125 +724,116 @@
           <t>Insurance (General)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.134</v>
-      </c>
-      <c r="E3">
-        <v>0.184</v>
-      </c>
-      <c r="F3">
-        <v>0.08</v>
-      </c>
       <c r="G3">
-        <v>0.296435382132903</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="H3">
-        <v>0.296435382132903</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="I3">
-        <v>0.2729399148600213</v>
+        <v>0.5769974065027389</v>
       </c>
       <c r="J3">
-        <v>0.2084708831832621</v>
+        <v>0.525891921926782</v>
       </c>
       <c r="K3">
-        <v>628.3</v>
+        <v>25.9</v>
       </c>
       <c r="L3">
-        <v>0.1843332844359689</v>
+        <v>0.4496527777777777</v>
       </c>
       <c r="M3">
-        <v>238.8</v>
+        <v>27.5</v>
       </c>
       <c r="N3">
-        <v>0.01479994050275175</v>
+        <v>0.04493464052287582</v>
       </c>
       <c r="O3">
-        <v>0.3800732134330734</v>
+        <v>1.061776061776062</v>
       </c>
       <c r="P3">
-        <v>115.9</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.007183053200456146</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.1844660194174758</v>
+        <v>-0</v>
       </c>
       <c r="S3">
-        <v>122.9</v>
+        <v>27.5</v>
       </c>
       <c r="T3">
-        <v>0.5146566164154104</v>
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>579.5</v>
+        <v>36.6</v>
       </c>
       <c r="V3">
-        <v>0.03591526600228073</v>
+        <v>0.05980392156862745</v>
       </c>
       <c r="W3">
-        <v>0.1529603661505502</v>
+        <v>1.221698113207547</v>
       </c>
       <c r="X3">
-        <v>0.08223365469762907</v>
+        <v>0.07160519065938156</v>
       </c>
       <c r="Y3">
-        <v>0.0707267114529211</v>
+        <v>1.150092922548166</v>
       </c>
       <c r="Z3">
-        <v>4.061018329623091</v>
+        <v>1.92418530011492</v>
       </c>
       <c r="AA3">
-        <v>0.8466040777999416</v>
+        <v>1.011913505620697</v>
       </c>
       <c r="AB3">
-        <v>0.07453624640906038</v>
+        <v>0.06616237368725902</v>
       </c>
       <c r="AC3">
-        <v>0.7720678313908812</v>
+        <v>0.9457511319334382</v>
       </c>
       <c r="AD3">
-        <v>4107.9</v>
+        <v>118.8</v>
       </c>
       <c r="AE3">
-        <v>195.4215009980871</v>
+        <v>0.07474692721117449</v>
       </c>
       <c r="AF3">
-        <v>4303.321500998087</v>
+        <v>118.8747469272112</v>
       </c>
       <c r="AG3">
-        <v>3723.821500998087</v>
+        <v>82.27474692721117</v>
       </c>
       <c r="AH3">
-        <v>0.2105495498188526</v>
+        <v>0.1626472216025957</v>
       </c>
       <c r="AI3">
-        <v>0.4995775153627143</v>
+        <v>0.4171413369394952</v>
       </c>
       <c r="AJ3">
-        <v>0.187512838979047</v>
+        <v>0.1185045938821061</v>
       </c>
       <c r="AK3">
-        <v>0.4634834630639543</v>
+        <v>0.3312524640491034</v>
       </c>
       <c r="AL3">
-        <v>112</v>
+        <v>3.66</v>
       </c>
       <c r="AM3">
-        <v>110</v>
+        <v>3.589</v>
       </c>
       <c r="AN3">
-        <v>3.588312368972746</v>
+        <v>3.399141630901288</v>
       </c>
       <c r="AO3">
-        <v>8.220535714285715</v>
+        <v>9.071038251366121</v>
       </c>
       <c r="AP3">
-        <v>3.252814029523137</v>
+        <v>2.354070012223496</v>
       </c>
       <c r="AQ3">
-        <v>8.370000000000001</v>
+        <v>9.250487601003066</v>
       </c>
     </row>
     <row r="4">
@@ -861,116 +852,119 @@
           <t>Insurance (General)</t>
         </is>
       </c>
+      <c r="F4">
+        <v>0.0975</v>
+      </c>
       <c r="G4">
-        <v>0.2160813086360356</v>
+        <v>0.2161422001756834</v>
       </c>
       <c r="H4">
-        <v>0.2160813086360356</v>
+        <v>0.2161422001756834</v>
       </c>
       <c r="I4">
-        <v>0.1855173780523455</v>
+        <v>0.1844123155760281</v>
       </c>
       <c r="J4">
-        <v>0.1675236728759977</v>
+        <v>0.1455128427592097</v>
       </c>
       <c r="K4">
-        <v>53.2</v>
+        <v>56.1</v>
       </c>
       <c r="L4">
-        <v>0.03199422660572528</v>
+        <v>0.02898775383661448</v>
       </c>
       <c r="M4">
-        <v>39.79000000000001</v>
+        <v>67.22999999999999</v>
       </c>
       <c r="N4">
-        <v>0.008530754882833438</v>
+        <v>0.01321032775288847</v>
       </c>
       <c r="O4">
-        <v>0.7479323308270678</v>
+        <v>1.198395721925134</v>
       </c>
       <c r="P4">
-        <v>32.7</v>
+        <v>59.8</v>
       </c>
       <c r="Q4">
-        <v>0.007010698282700512</v>
+        <v>0.01175037333962116</v>
       </c>
       <c r="R4">
-        <v>0.6146616541353384</v>
+        <v>1.065953654188948</v>
       </c>
       <c r="S4">
-        <v>7.090000000000003</v>
+        <v>7.429999999999993</v>
       </c>
       <c r="T4">
-        <v>0.1781854737371199</v>
+        <v>0.1105161386285883</v>
       </c>
       <c r="U4">
-        <v>833.1</v>
+        <v>754.4</v>
       </c>
       <c r="V4">
-        <v>0.178612010376691</v>
+        <v>0.1482354790536823</v>
       </c>
       <c r="W4">
-        <v>0.1701311160857052</v>
+        <v>0.126722385362548</v>
       </c>
       <c r="X4">
-        <v>0.08700137792463322</v>
+        <v>0.07648584056301141</v>
       </c>
       <c r="Y4">
-        <v>0.08312973816107194</v>
+        <v>0.0502365447995366</v>
       </c>
       <c r="Z4">
-        <v>4.530685023625583</v>
+        <v>4.379158426627156</v>
       </c>
       <c r="AA4">
-        <v>0.7589969958020342</v>
+        <v>0.6372237915514656</v>
       </c>
       <c r="AB4">
-        <v>0.07807649723862552</v>
+        <v>0.06838121926248363</v>
       </c>
       <c r="AC4">
-        <v>0.6809204985634086</v>
+        <v>0.5688425722889819</v>
       </c>
       <c r="AD4">
-        <v>1982.6</v>
+        <v>1981.1</v>
       </c>
       <c r="AE4">
-        <v>80.60851887279962</v>
+        <v>164.0342283285639</v>
       </c>
       <c r="AF4">
-        <v>2063.2085188728</v>
+        <v>2145.134228328564</v>
       </c>
       <c r="AG4">
-        <v>1230.1085188728</v>
+        <v>1390.734228328564</v>
       </c>
       <c r="AH4">
-        <v>0.3066824089608871</v>
+        <v>0.2965213052955918</v>
       </c>
       <c r="AI4">
-        <v>0.7314504512140414</v>
+        <v>0.6950427496280218</v>
       </c>
       <c r="AJ4">
-        <v>0.2086907473301555</v>
+        <v>0.2146216580792812</v>
       </c>
       <c r="AK4">
-        <v>0.6188887334666946</v>
+        <v>0.5963865581772372</v>
       </c>
       <c r="AL4">
-        <v>95.3</v>
+        <v>121.2</v>
       </c>
       <c r="AM4">
-        <v>89.42</v>
+        <v>76.80000000000001</v>
       </c>
       <c r="AN4">
-        <v>4.568202764976959</v>
+        <v>3.94484269215452</v>
       </c>
       <c r="AO4">
-        <v>3.179433368310598</v>
+        <v>2.964521452145215</v>
       </c>
       <c r="AP4">
-        <v>2.834351425974193</v>
+        <v>2.769283608778502</v>
       </c>
       <c r="AQ4">
-        <v>3.388503690449564</v>
+        <v>4.678385416666666</v>
       </c>
     </row>
     <row r="5">
@@ -990,124 +984,124 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.08740000000000001</v>
+        <v>0.0827</v>
       </c>
       <c r="E5">
-        <v>0.123</v>
+        <v>0.178</v>
       </c>
       <c r="F5">
-        <v>0.0916</v>
+        <v>0.115</v>
       </c>
       <c r="G5">
-        <v>0.2639308855291577</v>
+        <v>0.2357232931003423</v>
       </c>
       <c r="H5">
-        <v>0.2639308855291577</v>
+        <v>0.2357232931003423</v>
       </c>
       <c r="I5">
-        <v>0.2401784707565565</v>
+        <v>0.2345330481620297</v>
       </c>
       <c r="J5">
-        <v>0.1855825971556869</v>
+        <v>0.1792075654437813</v>
       </c>
       <c r="K5">
-        <v>3387</v>
+        <v>3466</v>
       </c>
       <c r="L5">
-        <v>0.1625629949604032</v>
+        <v>0.1560980003602954</v>
       </c>
       <c r="M5">
-        <v>3325</v>
+        <v>2628</v>
       </c>
       <c r="N5">
-        <v>0.04050940731995853</v>
+        <v>0.02813029851513128</v>
       </c>
       <c r="O5">
-        <v>0.9816947150870977</v>
+        <v>0.7582227351413734</v>
       </c>
       <c r="P5">
-        <v>1104</v>
+        <v>1229</v>
       </c>
       <c r="Q5">
-        <v>0.01345034155826593</v>
+        <v>0.0131553032249225</v>
       </c>
       <c r="R5">
-        <v>0.3259521700620018</v>
+        <v>0.3545874206578188</v>
       </c>
       <c r="S5">
-        <v>2221</v>
+        <v>1399</v>
       </c>
       <c r="T5">
-        <v>0.6679699248120301</v>
+        <v>0.5323439878234398</v>
       </c>
       <c r="U5">
-        <v>802</v>
+        <v>2901</v>
       </c>
       <c r="V5">
-        <v>0.009770990878377968</v>
+        <v>0.03105250989056158</v>
       </c>
       <c r="W5">
-        <v>0.3479556194781179</v>
+        <v>0.3623627809722949</v>
       </c>
       <c r="X5">
-        <v>0.07940746277059199</v>
+        <v>0.07098678276756931</v>
       </c>
       <c r="Y5">
-        <v>0.268548156707526</v>
+        <v>0.2913759982047255</v>
       </c>
       <c r="Z5">
-        <v>3.850199566478005</v>
+        <v>3.491117574949699</v>
       </c>
       <c r="AA5">
-        <v>0.714530035114688</v>
+        <v>0.6256346812847333</v>
       </c>
       <c r="AB5">
-        <v>0.07407105903660378</v>
+        <v>0.06632410837078581</v>
       </c>
       <c r="AC5">
-        <v>0.6404589760780842</v>
+        <v>0.5593105729139475</v>
       </c>
       <c r="AD5">
-        <v>11366</v>
+        <v>13649</v>
       </c>
       <c r="AE5">
-        <v>1979.40780893572</v>
+        <v>1807.140993051465</v>
       </c>
       <c r="AF5">
-        <v>13345.40780893572</v>
+        <v>15456.14099305146</v>
       </c>
       <c r="AG5">
-        <v>12543.40780893572</v>
+        <v>12555.14099305146</v>
       </c>
       <c r="AH5">
-        <v>0.139852163810561</v>
+        <v>0.1419576424525918</v>
       </c>
       <c r="AI5">
-        <v>0.5768141674863403</v>
+        <v>0.57155759216783</v>
       </c>
       <c r="AJ5">
-        <v>0.1325617822050777</v>
+        <v>0.1184698274314051</v>
       </c>
       <c r="AK5">
-        <v>0.5616181058499907</v>
+        <v>0.5200723941202782</v>
       </c>
       <c r="AL5">
-        <v>451</v>
+        <v>554</v>
       </c>
       <c r="AM5">
-        <v>400</v>
+        <v>505</v>
       </c>
       <c r="AN5">
-        <v>1.864807219031994</v>
+        <v>2.167195935217529</v>
       </c>
       <c r="AO5">
-        <v>11.11086474501109</v>
+        <v>9.398916967509026</v>
       </c>
       <c r="AP5">
-        <v>2.05798323362358</v>
+        <v>1.993512383780798</v>
       </c>
       <c r="AQ5">
-        <v>12.5275</v>
+        <v>10.31089108910891</v>
       </c>
     </row>
     <row r="6">
@@ -1118,7 +1112,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BRP Group, Inc. (NasdaqGS:BRP)</t>
+          <t>Brown &amp; Brown, Inc. (NYSE:BRO)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1126,116 +1120,125 @@
           <t>Insurance (General)</t>
         </is>
       </c>
+      <c r="D6">
+        <v>0.157</v>
+      </c>
+      <c r="E6">
+        <v>0.103</v>
+      </c>
       <c r="F6">
-        <v>0.277</v>
+        <v>0.118</v>
       </c>
       <c r="G6">
-        <v>0.07942722899653205</v>
+        <v>0.2816942693829694</v>
       </c>
       <c r="H6">
-        <v>0.07942722899653205</v>
+        <v>0.2816942693829694</v>
       </c>
       <c r="I6">
-        <v>0.02093619105116785</v>
+        <v>0.2819219951766621</v>
       </c>
       <c r="J6">
-        <v>0.02093619105116785</v>
+        <v>0.2137376742078215</v>
       </c>
       <c r="K6">
-        <v>-15.9</v>
+        <v>747</v>
       </c>
       <c r="L6">
-        <v>-0.01778722452175859</v>
+        <v>0.182471053788656</v>
       </c>
       <c r="M6">
-        <v>-0</v>
+        <v>170.5</v>
       </c>
       <c r="N6">
-        <v>-0</v>
+        <v>0.00842482878573758</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>0.2282463186077644</v>
       </c>
       <c r="P6">
-        <v>-0</v>
+        <v>130.5</v>
       </c>
       <c r="Q6">
-        <v>-0</v>
+        <v>0.006448329363863661</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>0.1746987951807229</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>40</v>
+      </c>
+      <c r="T6">
+        <v>0.2346041055718475</v>
       </c>
       <c r="U6">
-        <v>158.6</v>
+        <v>755.7</v>
       </c>
       <c r="V6">
-        <v>0.1027002525416046</v>
+        <v>0.03734101532775302</v>
       </c>
       <c r="W6">
-        <v>-0.0275897969807392</v>
+        <v>0.1732937410105322</v>
       </c>
       <c r="X6">
-        <v>0.09984757676480271</v>
+        <v>0.07159983482694657</v>
       </c>
       <c r="Y6">
-        <v>-0.1274373737455419</v>
+        <v>0.1016939061835856</v>
       </c>
       <c r="Z6">
-        <v>18.72995284650742</v>
+        <v>2.66603508682485</v>
       </c>
       <c r="AA6">
-        <v>0.3921338711738444</v>
+        <v>0.569832138814391</v>
       </c>
       <c r="AB6">
-        <v>0.08488845852070515</v>
+        <v>0.06665322941155531</v>
       </c>
       <c r="AC6">
-        <v>0.3072454126531392</v>
+        <v>0.5031789094028357</v>
       </c>
       <c r="AD6">
-        <v>1346.5</v>
+        <v>3707.1</v>
       </c>
       <c r="AE6">
-        <v>67.42569409680532</v>
+        <v>218.8386807289044</v>
       </c>
       <c r="AF6">
-        <v>1413.925694096805</v>
+        <v>3925.938680728904</v>
       </c>
       <c r="AG6">
-        <v>1255.325694096805</v>
+        <v>3170.238680728904</v>
       </c>
       <c r="AH6">
-        <v>0.477964104266392</v>
+        <v>0.1624723198922824</v>
       </c>
       <c r="AI6">
-        <v>0.5359787424591019</v>
+        <v>0.4302568921463626</v>
       </c>
       <c r="AJ6">
-        <v>0.4483905461875644</v>
+        <v>0.1354337594861743</v>
       </c>
       <c r="AK6">
-        <v>0.5062969610606097</v>
+        <v>0.3788101217695608</v>
       </c>
       <c r="AL6">
-        <v>54.2</v>
+        <v>187.5</v>
       </c>
       <c r="AM6">
-        <v>54.2</v>
+        <v>149</v>
       </c>
       <c r="AN6">
-        <v>12.11971197119712</v>
+        <v>2.645283288140431</v>
       </c>
       <c r="AO6">
-        <v>0.3118081180811808</v>
+        <v>6.112</v>
       </c>
       <c r="AP6">
-        <v>11.29906115298655</v>
+        <v>2.262194006514131</v>
       </c>
       <c r="AQ6">
-        <v>0.3118081180811808</v>
+        <v>7.691275167785235</v>
       </c>
     </row>
     <row r="7">
@@ -1246,7 +1249,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Marketing Alliance, Inc. (OTCPK:MAAL)</t>
+          <t>Assurant, Inc. (NYSE:AIZ)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1255,118 +1258,124 @@
         </is>
       </c>
       <c r="D7">
-        <v>-0.0626</v>
+        <v>0.0781</v>
       </c>
       <c r="E7">
-        <v>0.0135</v>
+        <v>-0.00404</v>
+      </c>
+      <c r="F7">
+        <v>0.146</v>
       </c>
       <c r="G7">
-        <v>0.1405797101449275</v>
+        <v>0.06499217686759927</v>
       </c>
       <c r="H7">
-        <v>0.1405797101449275</v>
+        <v>0.06499217686759927</v>
       </c>
       <c r="I7">
-        <v>0.1368487213748757</v>
+        <v>0.07912601232013002</v>
       </c>
       <c r="J7">
-        <v>0.1025621667260617</v>
+        <v>0.06176858404473121</v>
       </c>
       <c r="K7">
-        <v>1.43</v>
+        <v>528.1</v>
       </c>
       <c r="L7">
-        <v>0.06908212560386473</v>
+        <v>0.04889226296834641</v>
       </c>
       <c r="M7">
-        <v>-0</v>
+        <v>238.8</v>
       </c>
       <c r="N7">
-        <v>-0</v>
+        <v>0.02694955422638529</v>
       </c>
       <c r="O7">
-        <v>-0</v>
+        <v>0.4521870857792085</v>
       </c>
       <c r="P7">
-        <v>-0</v>
+        <v>151.3</v>
       </c>
       <c r="Q7">
-        <v>-0</v>
+        <v>0.01707482225482451</v>
       </c>
       <c r="R7">
-        <v>-0</v>
+        <v>0.2864987691725052</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>87.5</v>
+      </c>
+      <c r="T7">
+        <v>0.3664154103852596</v>
       </c>
       <c r="U7">
-        <v>1.73</v>
+        <v>1425.3</v>
       </c>
       <c r="V7">
-        <v>0.08564356435643565</v>
+        <v>0.1608509197607493</v>
       </c>
       <c r="W7">
-        <v>0.192722371967655</v>
+        <v>0.1288394447290737</v>
       </c>
       <c r="X7">
-        <v>0.08186240456074113</v>
+        <v>0.07256740699709405</v>
       </c>
       <c r="Y7">
-        <v>0.1108599674069139</v>
+        <v>0.05627203773197961</v>
       </c>
       <c r="Z7">
-        <v>3.228746216892087</v>
+        <v>4.718412360681634</v>
       </c>
       <c r="AA7">
-        <v>0.3311472078130272</v>
+        <v>0.2914496504584621</v>
       </c>
       <c r="AB7">
-        <v>0.07423692981121797</v>
+        <v>0.06508470103545541</v>
       </c>
       <c r="AC7">
-        <v>0.2569102780018092</v>
+        <v>0.2263649494230066</v>
       </c>
       <c r="AD7">
-        <v>4.92</v>
+        <v>2080</v>
       </c>
       <c r="AE7">
-        <v>0.1911573377003664</v>
+        <v>38.18101563289807</v>
       </c>
       <c r="AF7">
-        <v>5.111157337700366</v>
+        <v>2118.181015632898</v>
       </c>
       <c r="AG7">
-        <v>3.381157337700366</v>
+        <v>692.881015632898</v>
       </c>
       <c r="AH7">
-        <v>0.2019329764146114</v>
+        <v>0.192927050990132</v>
       </c>
       <c r="AI7">
-        <v>0.4312791731691034</v>
+        <v>0.3205100926513371</v>
       </c>
       <c r="AJ7">
-        <v>0.143383858954825</v>
+        <v>0.07252351316696799</v>
       </c>
       <c r="AK7">
-        <v>0.3340682517705629</v>
+        <v>0.1336709854908763</v>
       </c>
       <c r="AL7">
-        <v>0.242</v>
+        <v>109.1</v>
       </c>
       <c r="AM7">
-        <v>0.242</v>
+        <v>109.1</v>
       </c>
       <c r="AN7">
-        <v>1.602084011722566</v>
+        <v>1.989859370515641</v>
       </c>
       <c r="AO7">
-        <v>11.44628099173554</v>
+        <v>7.758020164986251</v>
       </c>
       <c r="AP7">
-        <v>1.100995551188657</v>
+        <v>0.6628537411584213</v>
       </c>
       <c r="AQ7">
-        <v>11.44628099173554</v>
+        <v>7.758020164986251</v>
       </c>
     </row>
     <row r="8">
@@ -1386,49 +1395,49 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0675</v>
+        <v>0.0696</v>
       </c>
       <c r="E8">
-        <v>0.166</v>
+        <v>0.141</v>
       </c>
       <c r="F8">
-        <v>0.121</v>
+        <v>0.13</v>
       </c>
       <c r="G8">
-        <v>0.2339311047251828</v>
+        <v>0.2637737159727347</v>
       </c>
       <c r="H8">
-        <v>0.2339311047251828</v>
+        <v>0.2637737159727347</v>
       </c>
       <c r="I8">
-        <v>0.21250534944393</v>
+        <v>0.2111717947138426</v>
       </c>
       <c r="J8">
-        <v>0.1775822396642978</v>
+        <v>0.1734457172302352</v>
       </c>
       <c r="K8">
-        <v>1088.1</v>
+        <v>1137.2</v>
       </c>
       <c r="L8">
-        <v>0.1319340875195519</v>
+        <v>0.1234315981417966</v>
       </c>
       <c r="M8">
-        <v>421.3</v>
+        <v>462.5</v>
       </c>
       <c r="N8">
-        <v>0.01059826221705684</v>
+        <v>0.009525457170455224</v>
       </c>
       <c r="O8">
-        <v>0.3871886775112582</v>
+        <v>0.4067006683081252</v>
       </c>
       <c r="P8">
-        <v>421.3</v>
+        <v>462.5</v>
       </c>
       <c r="Q8">
-        <v>0.01059826221705684</v>
+        <v>0.009525457170455224</v>
       </c>
       <c r="R8">
-        <v>0.3871886775112582</v>
+        <v>0.4067006683081252</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1437,73 +1446,73 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>553.7</v>
+        <v>1027.5</v>
       </c>
       <c r="V8">
-        <v>0.01392892900447275</v>
+        <v>0.02116196160571404</v>
       </c>
       <c r="W8">
-        <v>0.1292249590271015</v>
+        <v>0.1326366371970422</v>
       </c>
       <c r="X8">
-        <v>0.0795046658077041</v>
+        <v>0.07056540292141018</v>
       </c>
       <c r="Y8">
-        <v>0.04972029321939736</v>
+        <v>0.06207123427563198</v>
       </c>
       <c r="Z8">
-        <v>1.674026962501625</v>
+        <v>1.593108237223638</v>
       </c>
       <c r="AA8">
-        <v>0.2972774572594601</v>
+        <v>0.2763178008306495</v>
       </c>
       <c r="AB8">
-        <v>0.07445973741396962</v>
+        <v>0.06669372136906508</v>
       </c>
       <c r="AC8">
-        <v>0.2228177198454905</v>
+        <v>0.2096240794615844</v>
       </c>
       <c r="AD8">
-        <v>6247.6</v>
+        <v>6727.6</v>
       </c>
       <c r="AE8">
-        <v>358.0231576553791</v>
+        <v>352.6601047121264</v>
       </c>
       <c r="AF8">
-        <v>6605.623157655379</v>
+        <v>7080.260104712127</v>
       </c>
       <c r="AG8">
-        <v>6051.923157655379</v>
+        <v>6052.760104712127</v>
       </c>
       <c r="AH8">
-        <v>0.1424933205452456</v>
+        <v>0.127264159979301</v>
       </c>
       <c r="AI8">
-        <v>0.433589970050495</v>
+        <v>0.402510256389867</v>
       </c>
       <c r="AJ8">
-        <v>0.1321273193627688</v>
+        <v>0.1108424855980654</v>
       </c>
       <c r="AK8">
-        <v>0.4122276147013378</v>
+        <v>0.3654439276090287</v>
       </c>
       <c r="AL8">
-        <v>254.4</v>
+        <v>282.5</v>
       </c>
       <c r="AM8">
-        <v>148.2</v>
+        <v>-16.89999999999998</v>
       </c>
       <c r="AN8">
-        <v>2.590860081280584</v>
+        <v>2.517814371257485</v>
       </c>
       <c r="AO8">
-        <v>6.771226415094339</v>
+        <v>6.787610619469026</v>
       </c>
       <c r="AP8">
-        <v>2.509713509851281</v>
+        <v>2.265254530206634</v>
       </c>
       <c r="AQ8">
-        <v>11.62348178137652</v>
+        <v>-113.4615384615386</v>
       </c>
     </row>
     <row r="9">
@@ -1514,7 +1523,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>American International Group, Inc. (NYSE:AIG)</t>
+          <t>Goosehead Insurance, Inc (NasdaqGS:GSHD)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1523,118 +1532,118 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.0401</v>
+        <v>0.352</v>
+      </c>
+      <c r="F9">
+        <v>0.307</v>
       </c>
       <c r="G9">
-        <v>0.2662097072989996</v>
+        <v>0.0590318772136954</v>
       </c>
       <c r="H9">
-        <v>0.2662097072989996</v>
+        <v>0.0590318772136954</v>
       </c>
       <c r="I9">
-        <v>0.3128977748465749</v>
+        <v>0.1209664387837406</v>
       </c>
       <c r="J9">
-        <v>0.2495824149162013</v>
+        <v>0.09553599426670423</v>
       </c>
       <c r="K9">
-        <v>13751</v>
+        <v>11</v>
       </c>
       <c r="L9">
-        <v>0.2315840883829028</v>
+        <v>0.04329004329004329</v>
       </c>
       <c r="M9">
-        <v>6349</v>
+        <v>-0</v>
       </c>
       <c r="N9">
-        <v>0.1351250689033565</v>
+        <v>-0</v>
       </c>
       <c r="O9">
-        <v>0.4617118754999636</v>
+        <v>-0</v>
       </c>
       <c r="P9">
-        <v>1010</v>
+        <v>-0</v>
       </c>
       <c r="Q9">
-        <v>0.02149571894666721</v>
+        <v>-0</v>
       </c>
       <c r="R9">
-        <v>0.07344920369427678</v>
+        <v>-0</v>
       </c>
       <c r="S9">
-        <v>5339</v>
-      </c>
-      <c r="T9">
-        <v>0.8409198298944716</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>2294</v>
+        <v>35.2</v>
       </c>
       <c r="V9">
-        <v>0.04882294976599463</v>
+        <v>0.01866878811986211</v>
       </c>
       <c r="W9">
-        <v>0.2135978129174563</v>
+        <v>1.737756714060032</v>
       </c>
       <c r="X9">
-        <v>0.09321889424115629</v>
+        <v>0.06908774970016671</v>
       </c>
       <c r="Y9">
-        <v>0.1203789186763</v>
+        <v>1.668668964359865</v>
       </c>
       <c r="Z9">
-        <v>0.6356177618205863</v>
+        <v>1.735156293289297</v>
       </c>
       <c r="AA9">
-        <v>0.1586390159588128</v>
+        <v>0.165769881687522</v>
       </c>
       <c r="AB9">
-        <v>0.07291571855303169</v>
+        <v>0.06687482776760294</v>
       </c>
       <c r="AC9">
-        <v>0.08572329740578111</v>
+        <v>0.09889505391991905</v>
       </c>
       <c r="AD9">
-        <v>30432</v>
+        <v>78.8</v>
       </c>
       <c r="AE9">
-        <v>1113.779625800377</v>
+        <v>66.4121395252576</v>
       </c>
       <c r="AF9">
-        <v>31545.77962580038</v>
+        <v>145.2121395252576</v>
       </c>
       <c r="AG9">
-        <v>29251.77962580038</v>
+        <v>110.0121395252576</v>
       </c>
       <c r="AH9">
-        <v>0.4016939334205942</v>
+        <v>0.0715079881086472</v>
       </c>
       <c r="AI9">
-        <v>0.4348336313274684</v>
+        <v>0.9618472652099075</v>
       </c>
       <c r="AJ9">
-        <v>0.3836908865957102</v>
+        <v>0.05512977713652498</v>
       </c>
       <c r="AK9">
-        <v>0.4163789643855976</v>
+        <v>0.9502470972410131</v>
       </c>
       <c r="AL9">
-        <v>1108</v>
+        <v>6.65</v>
       </c>
       <c r="AM9">
-        <v>1108</v>
+        <v>5.12</v>
       </c>
       <c r="AN9">
-        <v>1.280646383032445</v>
+        <v>1.514801999231065</v>
       </c>
       <c r="AO9">
-        <v>16.77797833935018</v>
+        <v>5.293233082706767</v>
       </c>
       <c r="AP9">
-        <v>1.230980079358683</v>
+        <v>2.114804681377501</v>
       </c>
       <c r="AQ9">
-        <v>16.77797833935018</v>
+        <v>6.875</v>
       </c>
     </row>
     <row r="10">
@@ -1654,121 +1663,121 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.0145</v>
-      </c>
-      <c r="F10">
-        <v>0.12</v>
+        <v>0.0299</v>
+      </c>
+      <c r="E10">
+        <v>0.0759</v>
       </c>
       <c r="G10">
-        <v>0.06369591449750044</v>
+        <v>0.05798345559544248</v>
       </c>
       <c r="H10">
-        <v>0.06369591449750044</v>
+        <v>0.05798345559544248</v>
       </c>
       <c r="I10">
-        <v>0.04110144295346557</v>
+        <v>0.07195634877189723</v>
       </c>
       <c r="J10">
-        <v>0.04110144295346557</v>
+        <v>0.03597817438594861</v>
       </c>
       <c r="K10">
-        <v>-2.57</v>
+        <v>17.3</v>
       </c>
       <c r="L10">
-        <v>-0.002215135321496294</v>
+        <v>0.01350085843608553</v>
       </c>
       <c r="M10">
-        <v>53.2</v>
+        <v>13.49</v>
       </c>
       <c r="N10">
-        <v>0.2013626040878123</v>
+        <v>0.02099937733499377</v>
       </c>
       <c r="O10">
-        <v>-20.70038910505837</v>
+        <v>0.7797687861271675</v>
       </c>
       <c r="P10">
-        <v>12</v>
+        <v>12.2</v>
       </c>
       <c r="Q10">
-        <v>0.04542013626040878</v>
+        <v>0.01899128268991283</v>
       </c>
       <c r="R10">
-        <v>-4.669260700389105</v>
+        <v>0.7052023121387283</v>
       </c>
       <c r="S10">
-        <v>41.2</v>
+        <v>1.289999999999999</v>
       </c>
       <c r="T10">
-        <v>0.7744360902255639</v>
+        <v>0.09562638991845807</v>
       </c>
       <c r="U10">
-        <v>33.1</v>
+        <v>49.2</v>
       </c>
       <c r="V10">
-        <v>0.1252838758516276</v>
+        <v>0.07658779576587796</v>
       </c>
       <c r="W10">
-        <v>-0.01166061705989111</v>
+        <v>0.1062001227747084</v>
       </c>
       <c r="X10">
-        <v>0.1129553600419309</v>
+        <v>0.078327810294489</v>
       </c>
       <c r="Y10">
-        <v>-0.1246159771018221</v>
+        <v>0.02787231248021942</v>
       </c>
       <c r="Z10">
-        <v>3.310406732049743</v>
+        <v>3.066462303290925</v>
       </c>
       <c r="AA10">
-        <v>0.1360624934501109</v>
+        <v>0.1103257154957385</v>
       </c>
       <c r="AB10">
-        <v>0.06777934456465931</v>
+        <v>0.06333588717044751</v>
       </c>
       <c r="AC10">
-        <v>0.06828314888545156</v>
+        <v>0.04698982832529103</v>
       </c>
       <c r="AD10">
-        <v>257.4</v>
+        <v>218.4</v>
       </c>
       <c r="AE10">
-        <v>112.0705294269462</v>
+        <v>107.4756734184545</v>
       </c>
       <c r="AF10">
-        <v>369.4705294269462</v>
+        <v>325.8756734184545</v>
       </c>
       <c r="AG10">
-        <v>336.3705294269462</v>
+        <v>276.6756734184545</v>
       </c>
       <c r="AH10">
-        <v>0.5830640881485736</v>
+        <v>0.3365525772923374</v>
       </c>
       <c r="AI10">
-        <v>0.6961021928362341</v>
+        <v>0.666581896251402</v>
       </c>
       <c r="AJ10">
-        <v>0.5600849741127074</v>
+        <v>0.3010368802270368</v>
       </c>
       <c r="AK10">
-        <v>0.6758899905410665</v>
+        <v>0.6292721889007781</v>
       </c>
       <c r="AL10">
-        <v>8.970000000000001</v>
+        <v>19.2</v>
       </c>
       <c r="AM10">
-        <v>8.316000000000001</v>
+        <v>17.42</v>
       </c>
       <c r="AN10">
-        <v>2.853658536585366</v>
+        <v>1.637181409295352</v>
       </c>
       <c r="AO10">
-        <v>4.481605351170568</v>
+        <v>4.463541666666667</v>
       </c>
       <c r="AP10">
-        <v>3.729163297416255</v>
+        <v>2.074030535370723</v>
       </c>
       <c r="AQ10">
-        <v>4.834054834054834</v>
+        <v>4.919632606199771</v>
       </c>
     </row>
     <row r="11">
@@ -1779,7 +1788,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Assurant, Inc. (NYSE:AIZ)</t>
+          <t>Hagerty, Inc. (NYSE:HGTY)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1787,125 +1796,110 @@
           <t>Insurance (General)</t>
         </is>
       </c>
-      <c r="D11">
-        <v>0.09279999999999999</v>
-      </c>
-      <c r="E11">
-        <v>0.07389999999999999</v>
-      </c>
-      <c r="F11">
-        <v>0.127</v>
-      </c>
       <c r="G11">
-        <v>0.1076410514972665</v>
+        <v>-0.01617307288384793</v>
       </c>
       <c r="H11">
-        <v>0.1076410514972665</v>
+        <v>-0.01617307288384793</v>
       </c>
       <c r="I11">
-        <v>0.05334245401854962</v>
+        <v>0.006653078379801094</v>
       </c>
       <c r="J11">
-        <v>0.04317479588054818</v>
+        <v>0.003326539189900547</v>
       </c>
       <c r="K11">
-        <v>340</v>
+        <v>1.05</v>
       </c>
       <c r="L11">
-        <v>0.03361311306858063</v>
+        <v>0.001102709514807813</v>
       </c>
       <c r="M11">
-        <v>1023.7</v>
+        <v>-0</v>
       </c>
       <c r="N11">
-        <v>0.154939383390595</v>
+        <v>-0</v>
       </c>
       <c r="O11">
-        <v>3.010882352941177</v>
+        <v>-0</v>
       </c>
       <c r="P11">
-        <v>151.8</v>
+        <v>-0</v>
       </c>
       <c r="Q11">
-        <v>0.02297528416400539</v>
+        <v>-0</v>
       </c>
       <c r="R11">
-        <v>0.4464705882352942</v>
+        <v>-0</v>
       </c>
       <c r="S11">
-        <v>871.9000000000001</v>
-      </c>
-      <c r="T11">
-        <v>0.8517143694441731</v>
+        <v>0</v>
       </c>
       <c r="U11">
-        <v>1429.8</v>
+        <v>90.7</v>
       </c>
       <c r="V11">
-        <v>0.2164035658609677</v>
+        <v>0.1374658987571992</v>
       </c>
       <c r="W11">
-        <v>0.05918807882459439</v>
+        <v>0.01059535822401615</v>
       </c>
       <c r="X11">
-        <v>0.08398527727912342</v>
+        <v>0.07285717012666248</v>
       </c>
       <c r="Y11">
-        <v>-0.02479719845452902</v>
+        <v>-0.06226181190264634</v>
       </c>
       <c r="Z11">
-        <v>2.977061942328592</v>
+        <v>31.19441607459004</v>
       </c>
       <c r="AA11">
-        <v>0.1285340416837852</v>
+        <v>0.1037694475781874</v>
       </c>
       <c r="AB11">
-        <v>0.07191515514286217</v>
+        <v>0.06585770652710771</v>
       </c>
       <c r="AC11">
-        <v>0.05661888654092306</v>
+        <v>0.03791174105107965</v>
       </c>
       <c r="AD11">
-        <v>2129.3</v>
+        <v>75.8</v>
       </c>
       <c r="AE11">
-        <v>59.17871678484325</v>
+        <v>90.82469383376699</v>
       </c>
       <c r="AF11">
-        <v>2188.478716784844</v>
+        <v>166.624693833767</v>
       </c>
       <c r="AG11">
-        <v>758.6787167848436</v>
+        <v>75.92469383376697</v>
       </c>
       <c r="AH11">
-        <v>0.2488157729301552</v>
+        <v>0.2016211459761669</v>
       </c>
       <c r="AI11">
-        <v>0.3480748997897106</v>
+        <v>0.2582428965074537</v>
       </c>
       <c r="AJ11">
-        <v>0.1030004763862912</v>
+        <v>0.1031971530520923</v>
       </c>
       <c r="AK11">
-        <v>0.1561845439917032</v>
+        <v>0.1369185081891544</v>
       </c>
       <c r="AL11">
-        <v>107.5</v>
+        <v>0</v>
       </c>
       <c r="AM11">
-        <v>107.5</v>
+        <v>-18.1</v>
       </c>
       <c r="AN11">
-        <v>2.888361367335866</v>
-      </c>
-      <c r="AO11">
-        <v>4.967441860465116</v>
+        <v>1.098550724637681</v>
       </c>
       <c r="AP11">
-        <v>1.029135535519321</v>
+        <v>1.100357881648797</v>
       </c>
       <c r="AQ11">
-        <v>4.967441860465116</v>
+        <v>-0.6850828729281767</v>
       </c>
     </row>
     <row r="12">
@@ -1916,7 +1910,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The Hartford Financial Services Group, Inc. (NYSE:HIG)</t>
+          <t>The Marketing Alliance, Inc. (OTCPK:MAAL)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1925,124 +1919,121 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.0832</v>
+        <v>-0.11</v>
       </c>
       <c r="E12">
-        <v>0.318</v>
-      </c>
-      <c r="F12">
-        <v>0.07000000000000001</v>
+        <v>-0.0221</v>
       </c>
       <c r="G12">
-        <v>0.171764174384459</v>
+        <v>0.08022598870056497</v>
       </c>
       <c r="H12">
-        <v>0.171764174384459</v>
+        <v>0.08022598870056497</v>
       </c>
       <c r="I12">
-        <v>0.1211702008609304</v>
+        <v>0.06402165790542136</v>
       </c>
       <c r="J12">
-        <v>0.09764540094110423</v>
+        <v>0.05700752038490094</v>
       </c>
       <c r="K12">
-        <v>1955</v>
+        <v>1.2</v>
       </c>
       <c r="L12">
-        <v>0.08832166252541224</v>
+        <v>0.06779661016949153</v>
       </c>
       <c r="M12">
-        <v>2237</v>
+        <v>1.616</v>
       </c>
       <c r="N12">
-        <v>0.09273922740802772</v>
+        <v>0.09793939393939395</v>
       </c>
       <c r="O12">
-        <v>1.144245524296675</v>
+        <v>1.346666666666667</v>
       </c>
       <c r="P12">
-        <v>503</v>
+        <v>1.616</v>
       </c>
       <c r="Q12">
-        <v>0.02085285265366024</v>
+        <v>0.09793939393939395</v>
       </c>
       <c r="R12">
-        <v>0.2572890025575448</v>
+        <v>1.346666666666667</v>
       </c>
       <c r="S12">
-        <v>1734</v>
+        <v>0</v>
       </c>
       <c r="T12">
-        <v>0.7751452838623156</v>
+        <v>0</v>
       </c>
       <c r="U12">
-        <v>175</v>
+        <v>1.76</v>
       </c>
       <c r="V12">
-        <v>0.00725496861707861</v>
+        <v>0.1066666666666667</v>
       </c>
       <c r="W12">
-        <v>0.1115358283888635</v>
+        <v>0.1780415430267062</v>
       </c>
       <c r="X12">
-        <v>0.08009682728046619</v>
+        <v>0.07373857539450948</v>
       </c>
       <c r="Y12">
-        <v>0.03143900110839734</v>
+        <v>0.1043029676321967</v>
       </c>
       <c r="Z12">
-        <v>1.060283701889651</v>
+        <v>1.738006212381111</v>
       </c>
       <c r="AA12">
-        <v>0.1035318271823332</v>
+        <v>0.09907942458140068</v>
       </c>
       <c r="AB12">
-        <v>0.07303590000848924</v>
+        <v>0.06565968972081855</v>
       </c>
       <c r="AC12">
-        <v>0.03049592717384399</v>
+        <v>0.03341973486058213</v>
       </c>
       <c r="AD12">
-        <v>4365</v>
+        <v>4.59</v>
       </c>
       <c r="AE12">
-        <v>169.4880197165315</v>
+        <v>0.2540832753702097</v>
       </c>
       <c r="AF12">
-        <v>4534.488019716531</v>
+        <v>4.84408327537021</v>
       </c>
       <c r="AG12">
-        <v>4359.488019716531</v>
+        <v>3.08408327537021</v>
       </c>
       <c r="AH12">
-        <v>0.1582393125139448</v>
+        <v>0.226952041597401</v>
       </c>
       <c r="AI12">
-        <v>0.2592693402233752</v>
+        <v>0.4338988841168041</v>
       </c>
       <c r="AJ12">
-        <v>0.1530671380997172</v>
+        <v>0.1574790727758437</v>
       </c>
       <c r="AK12">
-        <v>0.2517826697937733</v>
+        <v>0.3279515062831894</v>
       </c>
       <c r="AL12">
-        <v>202</v>
+        <v>0.196</v>
       </c>
       <c r="AM12">
-        <v>202</v>
+        <v>0.173</v>
       </c>
       <c r="AN12">
-        <v>1.296791443850267</v>
+        <v>3.269230769230769</v>
       </c>
       <c r="AO12">
-        <v>13.23762376237624</v>
+        <v>5.255102040816326</v>
       </c>
       <c r="AP12">
-        <v>1.29515389771733</v>
+        <v>2.196640509522942</v>
       </c>
       <c r="AQ12">
-        <v>13.23762376237624</v>
+        <v>5.953757225433526</v>
       </c>
     </row>
     <row r="13">
@@ -2053,7 +2044,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Horace Mann Educators Corporation (NYSE:HMN)</t>
+          <t>American International Group, Inc. (NYSE:AIG)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2062,124 +2053,121 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.035</v>
-      </c>
-      <c r="E13">
-        <v>-0.0248</v>
+        <v>0.0107</v>
       </c>
       <c r="F13">
-        <v>0.127</v>
+        <v>0.09</v>
       </c>
       <c r="G13">
-        <v>0.1515173674588665</v>
+        <v>0.422543917369544</v>
       </c>
       <c r="H13">
-        <v>0.1515173674588665</v>
+        <v>0.422543917369544</v>
       </c>
       <c r="I13">
-        <v>0.06228777296790212</v>
+        <v>0.1403619302109863</v>
       </c>
       <c r="J13">
-        <v>0.05330850372366738</v>
+        <v>0.1157283287958662</v>
       </c>
       <c r="K13">
-        <v>56.4</v>
+        <v>4151</v>
       </c>
       <c r="L13">
-        <v>0.04124314442413163</v>
+        <v>0.08277003449582261</v>
       </c>
       <c r="M13">
-        <v>82.3</v>
+        <v>3713</v>
       </c>
       <c r="N13">
-        <v>0.05384716042920701</v>
+        <v>0.0780645541090591</v>
       </c>
       <c r="O13">
-        <v>1.459219858156028</v>
+        <v>0.8944832570464948</v>
       </c>
       <c r="P13">
-        <v>52.3</v>
+        <v>984</v>
       </c>
       <c r="Q13">
-        <v>0.03421879089243653</v>
+        <v>0.02068826319507519</v>
       </c>
       <c r="R13">
-        <v>0.927304964539007</v>
+        <v>0.2370513129366418</v>
       </c>
       <c r="S13">
-        <v>30</v>
+        <v>2729</v>
       </c>
       <c r="T13">
-        <v>0.3645200486026732</v>
+        <v>0.7349851871801778</v>
       </c>
       <c r="U13">
-        <v>35.2</v>
+        <v>1994</v>
       </c>
       <c r="V13">
-        <v>0.02303062025647736</v>
+        <v>0.04192316749083325</v>
       </c>
       <c r="W13">
-        <v>0.03139612558450233</v>
+        <v>0.107711868804816</v>
       </c>
       <c r="X13">
-        <v>0.0840075374701095</v>
+        <v>0.07874580134284137</v>
       </c>
       <c r="Y13">
-        <v>-0.05261141188560717</v>
+        <v>0.02896606746197465</v>
       </c>
       <c r="Z13">
-        <v>0.6474269670968715</v>
+        <v>0.7513309732466349</v>
       </c>
       <c r="AA13">
-        <v>0.03451336288628625</v>
+        <v>0.08695027790640467</v>
       </c>
       <c r="AB13">
-        <v>0.07190943312111005</v>
+        <v>0.06508198507722457</v>
       </c>
       <c r="AC13">
-        <v>-0.0373960702348238</v>
+        <v>0.0218682928291801</v>
       </c>
       <c r="AD13">
-        <v>497.9</v>
+        <v>24055</v>
       </c>
       <c r="AE13">
-        <v>9.607352331969262</v>
+        <v>998.5441899441462</v>
       </c>
       <c r="AF13">
-        <v>507.5073523319692</v>
+        <v>25053.54418994415</v>
       </c>
       <c r="AG13">
-        <v>472.3073523319692</v>
+        <v>23059.54418994415</v>
       </c>
       <c r="AH13">
-        <v>0.2492782158042015</v>
+        <v>0.3450105684222279</v>
       </c>
       <c r="AI13">
-        <v>0.3203743430550121</v>
+        <v>0.366995934644581</v>
       </c>
       <c r="AJ13">
-        <v>0.2360701837684861</v>
+        <v>0.3265172495694037</v>
       </c>
       <c r="AK13">
-        <v>0.3049293759377431</v>
+        <v>0.347950187695421</v>
       </c>
       <c r="AL13">
-        <v>17</v>
+        <v>1179</v>
       </c>
       <c r="AM13">
-        <v>17</v>
+        <v>1179</v>
       </c>
       <c r="AN13">
-        <v>4.547031963470319</v>
+        <v>2.002747481475314</v>
       </c>
       <c r="AO13">
-        <v>4.876470588235295</v>
+        <v>5.975402883799831</v>
       </c>
       <c r="AP13">
-        <v>4.313309153716614</v>
+        <v>1.919868802759483</v>
       </c>
       <c r="AQ13">
-        <v>4.876470588235295</v>
+        <v>5.975402883799831</v>
       </c>
     </row>
     <row r="14">
@@ -2199,121 +2187,121 @@
         </is>
       </c>
       <c r="D14">
-        <v>0.0222</v>
+        <v>0.00011</v>
       </c>
       <c r="E14">
-        <v>-0.0117</v>
+        <v>0.136</v>
       </c>
       <c r="G14">
-        <v>0.03996881496881497</v>
+        <v>0.0266594711279007</v>
       </c>
       <c r="H14">
-        <v>0.03996881496881497</v>
+        <v>0.0266594711279007</v>
       </c>
       <c r="I14">
-        <v>0.03087567761925105</v>
+        <v>0.03931865605134691</v>
       </c>
       <c r="J14">
-        <v>0.02356143942595275</v>
+        <v>0.03127345412084054</v>
       </c>
       <c r="K14">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="L14">
-        <v>0.01632016632016632</v>
+        <v>0.01672962763086886</v>
       </c>
       <c r="M14">
-        <v>0.516</v>
+        <v>0.42</v>
       </c>
       <c r="N14">
-        <v>0.01081761006289308</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="O14">
-        <v>0.1643312101910828</v>
+        <v>0.1354838709677419</v>
       </c>
       <c r="P14">
         <v>0.408</v>
       </c>
       <c r="Q14">
-        <v>0.008553459119496854</v>
+        <v>0.008159999999999999</v>
       </c>
       <c r="R14">
-        <v>0.1299363057324841</v>
+        <v>0.1316129032258064</v>
       </c>
       <c r="S14">
-        <v>0.108</v>
+        <v>0.01200000000000001</v>
       </c>
       <c r="T14">
-        <v>0.2093023255813954</v>
+        <v>0.0285714285714286</v>
       </c>
       <c r="U14">
-        <v>21.9</v>
+        <v>23.9</v>
       </c>
       <c r="V14">
-        <v>0.4591194968553459</v>
+        <v>0.478</v>
       </c>
       <c r="W14">
-        <v>0.0224446032880629</v>
+        <v>0.03166496424923391</v>
       </c>
       <c r="X14">
-        <v>0.09715840139421963</v>
+        <v>0.0848165244351636</v>
       </c>
       <c r="Y14">
-        <v>-0.07471379810615673</v>
+        <v>-0.0531515601859297</v>
       </c>
       <c r="Z14">
-        <v>1.176020443433224</v>
+        <v>1.619383449483839</v>
       </c>
       <c r="AA14">
-        <v>0.02770873444163399</v>
+        <v>0.05064371401148134</v>
       </c>
       <c r="AB14">
-        <v>0.07711841831041581</v>
+        <v>0.06393688486167123</v>
       </c>
       <c r="AC14">
-        <v>-0.04940968386878182</v>
+        <v>-0.01329317085018989</v>
       </c>
       <c r="AD14">
-        <v>34.7</v>
+        <v>36.8</v>
       </c>
       <c r="AE14">
-        <v>4.247598130280487</v>
+        <v>3.671265168427091</v>
       </c>
       <c r="AF14">
-        <v>38.94759813028049</v>
+        <v>40.47126516842709</v>
       </c>
       <c r="AG14">
-        <v>17.04759813028049</v>
+        <v>16.57126516842709</v>
       </c>
       <c r="AH14">
-        <v>0.4494942614764711</v>
+        <v>0.4473383354713034</v>
       </c>
       <c r="AI14">
-        <v>0.2846056391373558</v>
+        <v>0.2908018772370013</v>
       </c>
       <c r="AJ14">
-        <v>0.2632931355380709</v>
+        <v>0.2489251950748021</v>
       </c>
       <c r="AK14">
-        <v>0.1483075628162226</v>
+        <v>0.1437588556368684</v>
       </c>
       <c r="AL14">
-        <v>1.64</v>
+        <v>3.07</v>
       </c>
       <c r="AM14">
-        <v>1.64</v>
+        <v>3.07</v>
       </c>
       <c r="AN14">
-        <v>4.494818652849741</v>
+        <v>4.205714285714286</v>
       </c>
       <c r="AO14">
-        <v>3.51219512195122</v>
+        <v>2.270358306188925</v>
       </c>
       <c r="AP14">
-        <v>2.208238099777266</v>
+        <v>1.893858876391667</v>
       </c>
       <c r="AQ14">
-        <v>3.51219512195122</v>
+        <v>2.270358306188925</v>
       </c>
     </row>
     <row r="15">
@@ -2324,7 +2312,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Goosehead Insurance, Inc (NasdaqGS:GSHD)</t>
+          <t>BRP Group, Inc. (NasdaqGS:BRP)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2333,25 +2321,25 @@
         </is>
       </c>
       <c r="F15">
-        <v>0.195</v>
+        <v>0.289</v>
       </c>
       <c r="G15">
-        <v>0.06390780513357779</v>
+        <v>0.07618644067796611</v>
       </c>
       <c r="H15">
-        <v>0.06390780513357779</v>
+        <v>0.07618644067796611</v>
       </c>
       <c r="I15">
-        <v>0.003091907057473982</v>
+        <v>0.0193028480476655</v>
       </c>
       <c r="J15">
-        <v>0.00243684200292441</v>
+        <v>0.0193028480476655</v>
       </c>
       <c r="K15">
-        <v>0.34</v>
+        <v>-104.1</v>
       </c>
       <c r="L15">
-        <v>0.00178103719224725</v>
+        <v>-0.08822033898305084</v>
       </c>
       <c r="M15">
         <v>-0</v>
@@ -2360,7 +2348,7 @@
         <v>-0</v>
       </c>
       <c r="O15">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P15">
         <v>-0</v>
@@ -2369,79 +2357,79 @@
         <v>-0</v>
       </c>
       <c r="R15">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S15">
         <v>0</v>
       </c>
       <c r="U15">
-        <v>46.1</v>
+        <v>79</v>
       </c>
       <c r="V15">
-        <v>0.05918603158300167</v>
+        <v>0.05113599585733704</v>
       </c>
       <c r="W15">
-        <v>-0.01798941798941799</v>
+        <v>-0.1597360748810802</v>
       </c>
       <c r="X15">
-        <v>0.08078431090757876</v>
+        <v>0.08677837453991355</v>
       </c>
       <c r="Y15">
-        <v>-0.09877372889699676</v>
+        <v>-0.2465144494209938</v>
       </c>
       <c r="Z15">
-        <v>1.524166607110199</v>
+        <v>2.337498322423742</v>
       </c>
       <c r="AA15">
-        <v>0.003714153207660919</v>
+        <v>0.04512037492941851</v>
       </c>
       <c r="AB15">
-        <v>0.0738337941806165</v>
+        <v>0.07807028709421993</v>
       </c>
       <c r="AC15">
-        <v>-0.07011964097295559</v>
+        <v>-0.03294991216480141</v>
       </c>
       <c r="AD15">
-        <v>119.8</v>
+        <v>1305.5</v>
       </c>
       <c r="AE15">
-        <v>46.34877471364108</v>
+        <v>86.11319651877353</v>
       </c>
       <c r="AF15">
-        <v>166.1487747136411</v>
+        <v>1391.613196518774</v>
       </c>
       <c r="AG15">
-        <v>120.0487747136411</v>
+        <v>1312.613196518774</v>
       </c>
       <c r="AH15">
-        <v>0.1758097350731826</v>
+        <v>0.4738998612941792</v>
       </c>
       <c r="AI15">
-        <v>1.379414403414636</v>
+        <v>0.5644314532502552</v>
       </c>
       <c r="AJ15">
-        <v>0.1335435100313502</v>
+        <v>0.4593550777360862</v>
       </c>
       <c r="AK15">
-        <v>1.614670519803674</v>
+        <v>0.5500129638643914</v>
       </c>
       <c r="AL15">
-        <v>4.36</v>
+        <v>112.9</v>
       </c>
       <c r="AM15">
-        <v>3.04</v>
+        <v>112.9</v>
       </c>
       <c r="AN15">
-        <v>7.358722358722358</v>
+        <v>9.536157779401023</v>
       </c>
       <c r="AO15">
-        <v>0.9587155963302751</v>
+        <v>0.1877767936226749</v>
       </c>
       <c r="AP15">
-        <v>7.374003360788763</v>
+        <v>9.588116848201413</v>
       </c>
       <c r="AQ15">
-        <v>1.375</v>
+        <v>0.1877767936226749</v>
       </c>
     </row>
     <row r="16">
@@ -2452,7 +2440,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>eHealth, Inc. (NasdaqGS:EHTH)</t>
+          <t>SelectQuote, Inc. (NYSE:SLQT)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2460,35 +2448,32 @@
           <t>Insurance (General)</t>
         </is>
       </c>
-      <c r="D16">
-        <v>0.245</v>
-      </c>
       <c r="G16">
-        <v>-0.1009944751381215</v>
+        <v>0.07119560152828255</v>
       </c>
       <c r="H16">
-        <v>-0.1604419889502762</v>
+        <v>0.04556891249650545</v>
       </c>
       <c r="I16">
-        <v>-0.2401079154985536</v>
+        <v>0.04445063856433878</v>
       </c>
       <c r="J16">
-        <v>-0.2401079154985536</v>
+        <v>0.04445063856433878</v>
       </c>
       <c r="K16">
-        <v>-141.5</v>
+        <v>-47.1</v>
       </c>
       <c r="L16">
-        <v>-0.312707182320442</v>
+        <v>-0.0438915292144255</v>
       </c>
       <c r="M16">
-        <v>4.27</v>
+        <v>0.354</v>
       </c>
       <c r="N16">
-        <v>0.03217784476262246</v>
+        <v>0.001540469973890339</v>
       </c>
       <c r="O16">
-        <v>-0.03017667844522968</v>
+        <v>-0.00751592356687898</v>
       </c>
       <c r="P16">
         <v>-0</v>
@@ -2500,73 +2485,79 @@
         <v>0</v>
       </c>
       <c r="S16">
-        <v>4.27</v>
+        <v>0.354</v>
       </c>
       <c r="T16">
         <v>1</v>
       </c>
       <c r="U16">
-        <v>160.3</v>
+        <v>48.5</v>
       </c>
       <c r="V16">
-        <v>1.207987942727958</v>
+        <v>0.211053089643168</v>
       </c>
       <c r="W16">
-        <v>-0.1819467661051819</v>
+        <v>-0.1320437342304458</v>
       </c>
       <c r="X16">
-        <v>0.09676831848028891</v>
+        <v>0.1354484982438952</v>
       </c>
       <c r="Y16">
-        <v>-0.2787150845854708</v>
+        <v>-0.267492232474341</v>
       </c>
       <c r="Z16">
-        <v>0.5347788497807011</v>
+        <v>1.095558848164743</v>
       </c>
       <c r="AA16">
-        <v>-0.1284046348735583</v>
+        <v>0.04869829038573432</v>
       </c>
       <c r="AB16">
-        <v>0.07332540904595992</v>
+        <v>0.08449223758051724</v>
       </c>
       <c r="AC16">
-        <v>-0.2017300439195182</v>
+        <v>-0.03579394719478292</v>
       </c>
       <c r="AD16">
-        <v>65.7</v>
+        <v>695.3</v>
       </c>
       <c r="AE16">
-        <v>40.74415881547765</v>
+        <v>32.50009878304029</v>
       </c>
       <c r="AF16">
-        <v>106.4441588154776</v>
+        <v>727.8000987830402</v>
       </c>
       <c r="AG16">
-        <v>-53.85584118452236</v>
+        <v>679.3000987830402</v>
       </c>
       <c r="AH16">
-        <v>0.445104573503756</v>
+        <v>0.7600250874117078</v>
       </c>
       <c r="AI16">
-        <v>0.106963556860122</v>
+        <v>0.6967927524669543</v>
       </c>
       <c r="AJ16">
-        <v>-0.6830669765982729</v>
+        <v>0.7472225552415844</v>
       </c>
       <c r="AK16">
-        <v>-0.06451005330256603</v>
+        <v>0.6820281439861714</v>
       </c>
       <c r="AL16">
-        <v>0</v>
+        <v>85.3</v>
       </c>
       <c r="AM16">
-        <v>0</v>
+        <v>85.3</v>
       </c>
       <c r="AN16">
-        <v>-0.6865203761755486</v>
+        <v>9.511627906976743</v>
+      </c>
+      <c r="AO16">
+        <v>0.5392731535756154</v>
       </c>
       <c r="AP16">
-        <v>0.5627569611757822</v>
+        <v>9.292751009343915</v>
+      </c>
+      <c r="AQ16">
+        <v>0.5392731535756154</v>
       </c>
     </row>
     <row r="17">
@@ -2577,7 +2568,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hagerty, Inc. (NYSE:HGTY)</t>
+          <t>Horace Mann Educators Corporation (NYSE:HMN)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2585,113 +2576,122 @@
           <t>Insurance (General)</t>
         </is>
       </c>
+      <c r="D17">
+        <v>0.0339</v>
+      </c>
+      <c r="F17">
+        <v>0.127</v>
+      </c>
       <c r="G17">
-        <v>0.01624161073825503</v>
+        <v>0.02777197744831906</v>
       </c>
       <c r="H17">
-        <v>0.01624161073825503</v>
+        <v>0.02777197744831906</v>
       </c>
       <c r="I17">
-        <v>-0.07823386918352739</v>
+        <v>-0.01043890138029927</v>
       </c>
       <c r="J17">
-        <v>-0.07823386918352739</v>
+        <v>-0.01043890138029927</v>
       </c>
       <c r="K17">
-        <v>-15</v>
+        <v>-33.6</v>
       </c>
       <c r="L17">
-        <v>-0.02013422818791946</v>
+        <v>-0.02338692837753184</v>
       </c>
       <c r="M17">
-        <v>-0</v>
+        <v>61.8</v>
       </c>
       <c r="N17">
-        <v>-0</v>
+        <v>0.0462817344416985</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>-1.839285714285714</v>
       </c>
       <c r="P17">
-        <v>-0</v>
+        <v>53.5</v>
       </c>
       <c r="Q17">
-        <v>-0</v>
+        <v>0.04006590279337977</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>-1.592261904761905</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>8.299999999999997</v>
+      </c>
+      <c r="T17">
+        <v>0.1343042071197411</v>
       </c>
       <c r="U17">
-        <v>180.4</v>
+        <v>33.7</v>
       </c>
       <c r="V17">
-        <v>0.2578247820494498</v>
+        <v>0.02523777428293268</v>
       </c>
       <c r="W17">
-        <v>-0.1265822784810127</v>
+        <v>-0.03120936280884266</v>
       </c>
       <c r="X17">
-        <v>0.08309330740141679</v>
+        <v>0.07641265320054294</v>
       </c>
       <c r="Y17">
-        <v>-0.2096755858824295</v>
+        <v>-0.1076220160093856</v>
       </c>
       <c r="Z17">
-        <v>2.982730239635589</v>
+        <v>0.9610111559496564</v>
       </c>
       <c r="AA17">
-        <v>-0.2333505273774019</v>
+        <v>-0.01003190068232587</v>
       </c>
       <c r="AB17">
-        <v>0.07347750857768411</v>
+        <v>0.06384390119397174</v>
       </c>
       <c r="AC17">
-        <v>-0.3068280359550861</v>
+        <v>-0.07387580187629761</v>
       </c>
       <c r="AD17">
-        <v>136</v>
+        <v>546.3</v>
       </c>
       <c r="AE17">
-        <v>72.77116270863954</v>
+        <v>11.98784806537985</v>
       </c>
       <c r="AF17">
-        <v>208.7711627086395</v>
+        <v>558.2878480653798</v>
       </c>
       <c r="AG17">
-        <v>28.37116270863953</v>
+        <v>524.5878480653797</v>
       </c>
       <c r="AH17">
-        <v>0.2298049418389691</v>
+        <v>0.2948307091407273</v>
       </c>
       <c r="AI17">
-        <v>0.3487825269829462</v>
+        <v>0.3468514307786342</v>
       </c>
       <c r="AJ17">
-        <v>0.03896756822930664</v>
+        <v>0.2820534843598479</v>
       </c>
       <c r="AK17">
-        <v>0.0678458134818998</v>
+        <v>0.3328839985087669</v>
       </c>
       <c r="AL17">
-        <v>1.33</v>
+        <v>27</v>
       </c>
       <c r="AM17">
-        <v>1.33</v>
+        <v>27</v>
       </c>
       <c r="AN17">
-        <v>-10.85395051875499</v>
+        <v>39.58695652173913</v>
       </c>
       <c r="AO17">
-        <v>-39.69924812030074</v>
+        <v>-0.6074074074074074</v>
       </c>
       <c r="AP17">
-        <v>-2.264258795581766</v>
+        <v>38.0136121786507</v>
       </c>
       <c r="AQ17">
-        <v>-39.69924812030074</v>
+        <v>-0.6074074074074074</v>
       </c>
     </row>
     <row r="18">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SelectQuote, Inc. (NYSE:SLQT)</t>
+          <t>eHealth, Inc. (NasdaqGS:EHTH)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2710,32 +2710,35 @@
           <t>Insurance (General)</t>
         </is>
       </c>
+      <c r="D18">
+        <v>0.15</v>
+      </c>
       <c r="G18">
-        <v>-0.3305645684620376</v>
+        <v>-0.1230386052303861</v>
       </c>
       <c r="H18">
-        <v>-0.3631408176508761</v>
+        <v>-0.1975093399750934</v>
       </c>
       <c r="I18">
-        <v>-0.3649976031113151</v>
+        <v>-0.1194943065893871</v>
       </c>
       <c r="J18">
-        <v>-0.3649976031113151</v>
+        <v>-0.1194943065893871</v>
       </c>
       <c r="K18">
-        <v>-291.8</v>
+        <v>-59.7</v>
       </c>
       <c r="L18">
-        <v>-0.3787151200519144</v>
+        <v>-0.148692403486924</v>
       </c>
       <c r="M18">
-        <v>7.87</v>
+        <v>2.14</v>
       </c>
       <c r="N18">
-        <v>0.07070979335130279</v>
+        <v>0.008653457339264052</v>
       </c>
       <c r="O18">
-        <v>-0.02697052775873886</v>
+        <v>-0.03584589614740369</v>
       </c>
       <c r="P18">
         <v>-0</v>
@@ -2747,79 +2750,79 @@
         <v>0</v>
       </c>
       <c r="S18">
-        <v>7.87</v>
+        <v>2.14</v>
       </c>
       <c r="T18">
         <v>1</v>
       </c>
       <c r="U18">
-        <v>71.09999999999999</v>
+        <v>152.1</v>
       </c>
       <c r="V18">
-        <v>0.6388140161725067</v>
+        <v>0.6150424585523655</v>
       </c>
       <c r="W18">
-        <v>-0.460397601767119</v>
+        <v>-0.09423835832675612</v>
       </c>
       <c r="X18">
-        <v>0.2533299551484498</v>
+        <v>0.07665918056850263</v>
       </c>
       <c r="Y18">
-        <v>-0.7137275569155688</v>
+        <v>-0.1708975388952587</v>
       </c>
       <c r="Z18">
-        <v>0.8759630958577692</v>
+        <v>0.4819726500382339</v>
       </c>
       <c r="AA18">
-        <v>-0.3197244304020529</v>
+        <v>-0.0575929876113681</v>
       </c>
       <c r="AB18">
-        <v>0.07909599690303717</v>
+        <v>0.06734391127104881</v>
       </c>
       <c r="AC18">
-        <v>-0.39882042730509</v>
+        <v>-0.1249368988824169</v>
       </c>
       <c r="AD18">
-        <v>690.5</v>
+        <v>67.3</v>
       </c>
       <c r="AE18">
-        <v>40.70326598634115</v>
+        <v>38.9348204781946</v>
       </c>
       <c r="AF18">
-        <v>731.2032659863412</v>
+        <v>106.2348204781946</v>
       </c>
       <c r="AG18">
-        <v>660.1032659863412</v>
+        <v>-45.8651795218054</v>
       </c>
       <c r="AH18">
-        <v>0.867893687189808</v>
+        <v>0.3004932310047999</v>
       </c>
       <c r="AI18">
-        <v>0.6721215836441119</v>
+        <v>0.1112715470301849</v>
       </c>
       <c r="AJ18">
-        <v>0.855717489272374</v>
+        <v>-0.2276924089535469</v>
       </c>
       <c r="AK18">
-        <v>0.6491946751823361</v>
+        <v>-0.05714327157458706</v>
       </c>
       <c r="AL18">
-        <v>51.8</v>
+        <v>2.9</v>
       </c>
       <c r="AM18">
-        <v>51.8</v>
+        <v>2.9</v>
       </c>
       <c r="AN18">
-        <v>-2.725048344449268</v>
+        <v>-1.799946509761968</v>
       </c>
       <c r="AO18">
-        <v>-5.440154440154441</v>
+        <v>-16.82758620689655</v>
       </c>
       <c r="AP18">
-        <v>-2.605088069719962</v>
+        <v>1.226669684990784</v>
       </c>
       <c r="AQ18">
-        <v>-5.440154440154441</v>
+        <v>-16.82758620689655</v>
       </c>
     </row>
     <row r="19">
@@ -2839,31 +2842,31 @@
         </is>
       </c>
       <c r="G19">
-        <v>0.04952366834667457</v>
+        <v>-0.260523321956769</v>
       </c>
       <c r="H19">
-        <v>0.0004081430971439866</v>
+        <v>-0.3424345847554039</v>
       </c>
       <c r="I19">
-        <v>-0.1755140967305918</v>
+        <v>-0.4255038048212481</v>
       </c>
       <c r="J19">
-        <v>-0.1755140967305918</v>
+        <v>-0.4255038048212481</v>
       </c>
       <c r="K19">
-        <v>-242.3</v>
+        <v>-123.4</v>
       </c>
       <c r="L19">
-        <v>-0.2394505385907699</v>
+        <v>-0.2339780053090633</v>
       </c>
       <c r="M19">
-        <v>-0</v>
+        <v>2.42</v>
       </c>
       <c r="N19">
-        <v>-0</v>
+        <v>0.01898039215686274</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>-0.01961102106969206</v>
       </c>
       <c r="P19">
         <v>-0</v>
@@ -2875,76 +2878,79 @@
         <v>0</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>2.42</v>
+      </c>
+      <c r="T19">
+        <v>1</v>
       </c>
       <c r="U19">
-        <v>215.4</v>
+        <v>26.4</v>
       </c>
       <c r="V19">
-        <v>2.318622174381055</v>
+        <v>0.2070588235294118</v>
       </c>
       <c r="W19">
-        <v>-0.4871330920788098</v>
+        <v>-0.3798091720529394</v>
       </c>
       <c r="X19">
-        <v>0.2767036561989509</v>
+        <v>0.15957636513676</v>
       </c>
       <c r="Y19">
-        <v>-0.7638367482777607</v>
+        <v>-0.5393855371896994</v>
       </c>
       <c r="Z19">
-        <v>2.049568933387344</v>
+        <v>0.603671798818983</v>
       </c>
       <c r="AA19">
-        <v>-0.3597282400305622</v>
+        <v>-0.2568646472607643</v>
       </c>
       <c r="AB19">
-        <v>0.07915976933291002</v>
+        <v>0.06719116920675008</v>
       </c>
       <c r="AC19">
-        <v>-0.4388880093634722</v>
+        <v>-0.3240558164675144</v>
       </c>
       <c r="AD19">
-        <v>665.7</v>
+        <v>497</v>
       </c>
       <c r="AE19">
-        <v>24.61357240842958</v>
+        <v>50.05353331363106</v>
       </c>
       <c r="AF19">
-        <v>690.3135724084296</v>
+        <v>547.0535333136311</v>
       </c>
       <c r="AG19">
-        <v>474.9135724084297</v>
+        <v>520.6535333136311</v>
       </c>
       <c r="AH19">
-        <v>0.881386120883571</v>
+        <v>0.8109860912392266</v>
       </c>
       <c r="AI19">
-        <v>0.4834082712842671</v>
+        <v>0.5465323964666216</v>
       </c>
       <c r="AJ19">
-        <v>0.8363899622794209</v>
+        <v>0.8032873486808491</v>
       </c>
       <c r="AK19">
-        <v>0.3916446122775792</v>
+        <v>0.5342482639648635</v>
       </c>
       <c r="AL19">
-        <v>49.4</v>
+        <v>69</v>
       </c>
       <c r="AM19">
-        <v>49.4</v>
+        <v>69</v>
       </c>
       <c r="AN19">
-        <v>-10.07415254237288</v>
+        <v>-4.306759098786828</v>
       </c>
       <c r="AO19">
-        <v>-3.647773279352227</v>
+        <v>-3.288405797101449</v>
       </c>
       <c r="AP19">
-        <v>-7.186948734994396</v>
+        <v>-4.511729058177045</v>
       </c>
       <c r="AQ19">
-        <v>-3.647773279352227</v>
+        <v>-3.288405797101449</v>
       </c>
     </row>
     <row r="20">
@@ -2964,22 +2970,22 @@
         </is>
       </c>
       <c r="G20">
-        <v>-0.1006578947368421</v>
+        <v>-0.2369565217391305</v>
       </c>
       <c r="H20">
-        <v>-0.1006578947368421</v>
+        <v>-0.2369565217391305</v>
       </c>
       <c r="I20">
-        <v>-0.4300809731665705</v>
+        <v>-0.2442586861548831</v>
       </c>
       <c r="J20">
-        <v>-0.4300809731665705</v>
+        <v>-0.2442586861548831</v>
       </c>
       <c r="K20">
-        <v>7.35</v>
+        <v>-22.5</v>
       </c>
       <c r="L20">
-        <v>0.4835526315789473</v>
+        <v>-1.222826086956522</v>
       </c>
       <c r="M20">
         <v>-0</v>
@@ -2988,7 +2994,7 @@
         <v>-0</v>
       </c>
       <c r="O20">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P20">
         <v>-0</v>
@@ -2997,73 +3003,79 @@
         <v>-0</v>
       </c>
       <c r="R20">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S20">
         <v>0</v>
       </c>
       <c r="U20">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="V20">
-        <v>0.1572815533980582</v>
+        <v>0.9081632653061225</v>
       </c>
       <c r="W20">
-        <v>0.5742187499999999</v>
+        <v>-0.7922535211267606</v>
       </c>
       <c r="X20">
-        <v>0.1187194552912791</v>
+        <v>0.2292857500266476</v>
       </c>
       <c r="Y20">
-        <v>0.4554992947087207</v>
+        <v>-1.021539271153408</v>
       </c>
       <c r="Z20">
-        <v>2.215370779777588</v>
+        <v>1.812486611602036</v>
       </c>
       <c r="AA20">
-        <v>-0.9527888208915289</v>
+        <v>-0.4427155984232292</v>
       </c>
       <c r="AB20">
-        <v>0.09752980510868717</v>
+        <v>0.06716966482966391</v>
       </c>
       <c r="AC20">
-        <v>-1.050318626000216</v>
+        <v>-0.5098852632528932</v>
       </c>
       <c r="AD20">
-        <v>15.7</v>
+        <v>13.6</v>
       </c>
       <c r="AE20">
-        <v>0.8911539606593526</v>
+        <v>1.171799126249246</v>
       </c>
       <c r="AF20">
-        <v>16.59115396065935</v>
+        <v>14.77179912624925</v>
       </c>
       <c r="AG20">
-        <v>14.97115396065935</v>
+        <v>12.99179912624925</v>
       </c>
       <c r="AH20">
-        <v>0.6169744141486648</v>
+        <v>0.882857785632562</v>
       </c>
       <c r="AI20">
-        <v>0.3687648015244686</v>
+        <v>0.5152030767656136</v>
       </c>
       <c r="AJ20">
-        <v>0.5924206699846617</v>
+        <v>0.8689120965677608</v>
       </c>
       <c r="AK20">
-        <v>0.3451868948250542</v>
+        <v>0.4831137948508574</v>
       </c>
       <c r="AL20">
-        <v>0</v>
+        <v>0.66</v>
       </c>
       <c r="AM20">
-        <v>0</v>
+        <v>0.66</v>
       </c>
       <c r="AN20">
-        <v>-4.176642724128757</v>
+        <v>-9.714285714285715</v>
+      </c>
+      <c r="AO20">
+        <v>-7.318181818181818</v>
       </c>
       <c r="AP20">
-        <v>-3.982749124942631</v>
+        <v>-9.279856518749462</v>
+      </c>
+      <c r="AQ20">
+        <v>-7.318181818181818</v>
       </c>
     </row>
     <row r="21">
@@ -3074,7 +3086,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Marpai, Inc. (NasdaqCM:MRAI)</t>
+          <t>Hippo Holdings Inc. (NYSE:HIPO)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3083,31 +3095,31 @@
         </is>
       </c>
       <c r="G21">
-        <v>-0.6681415929203539</v>
+        <v>-1.470718232044199</v>
       </c>
       <c r="H21">
-        <v>-0.6681415929203539</v>
+        <v>-1.470718232044199</v>
       </c>
       <c r="I21">
-        <v>-1.027513021453123</v>
+        <v>-1.563691995768235</v>
       </c>
       <c r="J21">
-        <v>-1.027513021453123</v>
+        <v>-1.563691995768235</v>
       </c>
       <c r="K21">
-        <v>-23.7</v>
+        <v>-293.9</v>
       </c>
       <c r="L21">
-        <v>-1.048672566371681</v>
+        <v>-1.623756906077348</v>
       </c>
       <c r="M21">
-        <v>-0</v>
+        <v>6.2</v>
       </c>
       <c r="N21">
-        <v>-0</v>
+        <v>0.02845341899954107</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>-0.02109561075195645</v>
       </c>
       <c r="P21">
         <v>-0</v>
@@ -3119,76 +3131,79 @@
         <v>0</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>6.2</v>
+      </c>
+      <c r="T21">
+        <v>1</v>
       </c>
       <c r="U21">
-        <v>4.75</v>
+        <v>228.4</v>
       </c>
       <c r="V21">
-        <v>0.3145695364238411</v>
+        <v>1.048187241854061</v>
       </c>
       <c r="W21">
-        <v>-5.129870129870129</v>
+        <v>-0.4628346456692913</v>
       </c>
       <c r="X21">
-        <v>0.07865934567326352</v>
+        <v>0.07020731168336125</v>
       </c>
       <c r="Y21">
-        <v>-5.208529475543393</v>
+        <v>-0.5330419573526526</v>
       </c>
       <c r="Z21">
-        <v>1.936760248904606</v>
+        <v>0.5716248166432222</v>
       </c>
       <c r="AA21">
-        <v>-1.990046375182275</v>
+        <v>-0.8938451503674913</v>
       </c>
       <c r="AB21">
-        <v>0.07454792518466717</v>
+        <v>0.06653971840958052</v>
       </c>
       <c r="AC21">
-        <v>-2.064594300366942</v>
+        <v>-0.9603848687770719</v>
       </c>
       <c r="AD21">
         <v>0</v>
       </c>
       <c r="AE21">
-        <v>2.038971424202927</v>
+        <v>28.14125617025227</v>
       </c>
       <c r="AF21">
-        <v>2.038971424202927</v>
+        <v>28.14125617025227</v>
       </c>
       <c r="AG21">
-        <v>-2.711028575797073</v>
+        <v>-200.2587438297477</v>
       </c>
       <c r="AH21">
-        <v>0.1189669656210278</v>
+        <v>0.1143761684860667</v>
       </c>
       <c r="AI21">
-        <v>0.1271260712595388</v>
+        <v>0.06403872138793798</v>
       </c>
       <c r="AJ21">
-        <v>-0.21882596084618</v>
+        <v>-11.35172812508873</v>
       </c>
       <c r="AK21">
-        <v>-0.2401484133430242</v>
+        <v>-0.9489080356316397</v>
       </c>
       <c r="AL21">
-        <v>0.05</v>
+        <v>0.5</v>
       </c>
       <c r="AM21">
-        <v>0.05</v>
+        <v>0.5</v>
       </c>
       <c r="AN21">
         <v>-0</v>
       </c>
       <c r="AO21">
-        <v>-473.9999999999999</v>
+        <v>-568.2</v>
       </c>
       <c r="AP21">
-        <v>0.1237121737609324</v>
+        <v>0.7386895751742816</v>
       </c>
       <c r="AQ21">
-        <v>-473.9999999999999</v>
+        <v>-568.2</v>
       </c>
     </row>
     <row r="22">
@@ -3199,7 +3214,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Hippo Holdings Inc. (NYSE:HIPO)</t>
+          <t>Marpai, Inc. (NasdaqCM:MRAI)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3208,31 +3223,31 @@
         </is>
       </c>
       <c r="G22">
-        <v>-1.800862068965517</v>
+        <v>-0.6421052631578947</v>
       </c>
       <c r="H22">
-        <v>-1.800862068965517</v>
+        <v>-0.706371191135734</v>
       </c>
       <c r="I22">
-        <v>-2.373483700753234</v>
+        <v>-0.8415950478705295</v>
       </c>
       <c r="J22">
-        <v>-2.373483700753234</v>
+        <v>-0.8415950478705295</v>
       </c>
       <c r="K22">
-        <v>-331</v>
+        <v>-32.3</v>
       </c>
       <c r="L22">
-        <v>-2.853448275862069</v>
+        <v>-0.8947368421052631</v>
       </c>
       <c r="M22">
-        <v>3.5</v>
+        <v>-0</v>
       </c>
       <c r="N22">
-        <v>0.01116071428571428</v>
+        <v>-0</v>
       </c>
       <c r="O22">
-        <v>-0.01057401812688822</v>
+        <v>0</v>
       </c>
       <c r="P22">
         <v>-0</v>
@@ -3244,73 +3259,76 @@
         <v>0</v>
       </c>
       <c r="S22">
-        <v>3.5</v>
-      </c>
-      <c r="T22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U22">
-        <v>346.5</v>
+        <v>3.02</v>
       </c>
       <c r="V22">
-        <v>1.104910714285714</v>
+        <v>0.2126760563380282</v>
       </c>
       <c r="W22">
-        <v>-0.3672065675615709</v>
+        <v>-2.307142857142857</v>
       </c>
       <c r="X22">
-        <v>0.07764440159137836</v>
+        <v>0.105783841303738</v>
       </c>
       <c r="Y22">
-        <v>-0.4448509691529492</v>
+        <v>-2.412926698446595</v>
       </c>
       <c r="Z22">
-        <v>1.158603344950143</v>
+        <v>2.952263419821961</v>
       </c>
       <c r="AA22">
-        <v>-2.749926154877341</v>
+        <v>-2.484610274131477</v>
       </c>
       <c r="AB22">
-        <v>0.07440689448871776</v>
+        <v>0.09754090524695472</v>
       </c>
       <c r="AC22">
-        <v>-2.824333049366059</v>
+        <v>-2.582151179378432</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AE22">
-        <v>30.6205464368755</v>
+        <v>5.35790614063058</v>
       </c>
       <c r="AF22">
-        <v>30.6205464368755</v>
+        <v>25.35790614063058</v>
       </c>
       <c r="AG22">
-        <v>-315.8794535631245</v>
+        <v>22.33790614063058</v>
       </c>
       <c r="AH22">
-        <v>0.0889561844981</v>
+        <v>0.6410325675601181</v>
       </c>
       <c r="AI22">
-        <v>0.04572820622038972</v>
+        <v>1.573275456463137</v>
       </c>
       <c r="AJ22">
-        <v>138.5768320413347</v>
+        <v>0.6113625136222726</v>
       </c>
       <c r="AK22">
-        <v>-0.9775901193730941</v>
+        <v>1.705456269177018</v>
       </c>
       <c r="AL22">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AM22">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN22">
-        <v>-0</v>
+        <v>-0.7217610970768675</v>
+      </c>
+      <c r="AO22">
+        <v>-22.94117647058823</v>
       </c>
       <c r="AP22">
-        <v>1.202892054695828</v>
+        <v>-0.8061315821230811</v>
+      </c>
+      <c r="AQ22">
+        <v>-22.94117647058823</v>
       </c>
     </row>
     <row r="23">
@@ -3330,22 +3348,22 @@
         </is>
       </c>
       <c r="G23">
-        <v>0.03106796116504855</v>
+        <v>0</v>
       </c>
       <c r="H23">
         <v>0</v>
       </c>
       <c r="I23">
-        <v>-0.03902912621359223</v>
+        <v>-0.3602150537634408</v>
       </c>
       <c r="J23">
-        <v>-0.03902912621359223</v>
+        <v>-0.3602150537634408</v>
       </c>
       <c r="K23">
-        <v>-9.77</v>
+        <v>-9.92</v>
       </c>
       <c r="L23">
-        <v>-0.1897087378640777</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="M23">
         <v>-0</v>
@@ -3369,58 +3387,67 @@
         <v>0</v>
       </c>
       <c r="U23">
-        <v>0.785</v>
+        <v>0.002</v>
       </c>
       <c r="V23">
-        <v>0.1068027210884354</v>
+        <v>0.03773584905660377</v>
       </c>
       <c r="W23">
-        <v>0.7816</v>
+        <v>1.900383141762452</v>
       </c>
       <c r="X23">
-        <v>0.09316466847550452</v>
+        <v>2.097463632919192</v>
       </c>
       <c r="Y23">
-        <v>0.6884353315244954</v>
+        <v>-0.1970804911567399</v>
+      </c>
+      <c r="Z23">
+        <v>65.72438162544162</v>
+      </c>
+      <c r="AA23">
+        <v>-23.67491166077735</v>
       </c>
       <c r="AB23">
-        <v>0.1022710116784807</v>
+        <v>0.06167924205899994</v>
+      </c>
+      <c r="AC23">
+        <v>-23.73659090283635</v>
       </c>
       <c r="AD23">
-        <v>4.92</v>
+        <v>5.01</v>
       </c>
       <c r="AE23">
         <v>0</v>
       </c>
       <c r="AF23">
-        <v>4.92</v>
+        <v>5.01</v>
       </c>
       <c r="AG23">
-        <v>4.135</v>
+        <v>5.008</v>
       </c>
       <c r="AH23">
-        <v>0.4009779951100245</v>
+        <v>0.9895318980841399</v>
       </c>
       <c r="AI23">
-        <v>2.86046511627907</v>
+        <v>0.9154028868993239</v>
       </c>
       <c r="AJ23">
-        <v>0.3600348280365694</v>
+        <v>0.9895277613119937</v>
       </c>
       <c r="AK23">
-        <v>4.42245989304813</v>
+        <v>0.9153719612502285</v>
       </c>
       <c r="AL23">
-        <v>2.16</v>
+        <v>0.728</v>
       </c>
       <c r="AM23">
-        <v>2.16</v>
+        <v>0.728</v>
       </c>
       <c r="AO23">
-        <v>-0.9305555555555554</v>
+        <v>-9.203296703296704</v>
       </c>
       <c r="AQ23">
-        <v>-0.9305555555555554</v>
+        <v>-9.203296703296704</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/united_states/united_states_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/united_states/united_states_insurance_general.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ9"/>
+  <dimension ref="A1:AQ22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.11885</v>
+        <v>0.0738</v>
       </c>
       <c r="E2">
-        <v>0.217</v>
+        <v>0.133</v>
       </c>
       <c r="F2">
-        <v>0.205</v>
+        <v>0.195</v>
       </c>
       <c r="G2">
-        <v>0.2326926165266936</v>
+        <v>0.2173082162778176</v>
       </c>
       <c r="H2">
-        <v>0.2326926165266936</v>
+        <v>0.2161864384628654</v>
       </c>
       <c r="I2">
-        <v>0.1767090073678439</v>
+        <v>0.1649674733959386</v>
       </c>
       <c r="J2">
-        <v>0.1573704247946022</v>
+        <v>0.149168918910754</v>
       </c>
       <c r="K2">
-        <v>4126.9</v>
+        <v>3977.73</v>
       </c>
       <c r="L2">
-        <v>0.04667287931256771</v>
+        <v>0.04158826081728884</v>
       </c>
       <c r="M2">
-        <v>10561.1</v>
+        <v>10683.6955</v>
       </c>
       <c r="N2">
-        <v>0.04150429540434964</v>
+        <v>0.04104650320236395</v>
       </c>
       <c r="O2">
-        <v>2.559087935254065</v>
+        <v>2.685877497969948</v>
       </c>
       <c r="P2">
-        <v>3229.8</v>
+        <v>3300.3385</v>
       </c>
       <c r="Q2">
-        <v>0.01269286090435357</v>
+        <v>0.01267982177226364</v>
       </c>
       <c r="R2">
-        <v>0.7826213380503527</v>
+        <v>0.8297040020313092</v>
       </c>
       <c r="S2">
-        <v>7331.3</v>
+        <v>7383.357</v>
       </c>
       <c r="T2">
-        <v>0.6941795835661058</v>
+        <v>0.6910864316565368</v>
       </c>
       <c r="U2">
-        <v>6713.9</v>
+        <v>7301.075</v>
       </c>
       <c r="V2">
-        <v>0.02638510088108843</v>
+        <v>0.02805055594931542</v>
       </c>
       <c r="W2">
-        <v>0.1911602209944751</v>
+        <v>0.1055238924403321</v>
       </c>
       <c r="X2">
-        <v>0.07560956446928985</v>
+        <v>0.07918291626455226</v>
       </c>
       <c r="Y2">
-        <v>0.1155506565251853</v>
+        <v>0.02634097617577985</v>
       </c>
       <c r="Z2">
-        <v>1.14273038110348</v>
+        <v>1.161783891222047</v>
       </c>
       <c r="AA2">
-        <v>0.3435485544778235</v>
+        <v>0.09648522928922734</v>
       </c>
       <c r="AB2">
-        <v>0.07188534376549904</v>
+        <v>0.0715897867079642</v>
       </c>
       <c r="AC2">
-        <v>0.2719005007354128</v>
+        <v>0.02628657764946524</v>
       </c>
       <c r="AD2">
-        <v>38935.5</v>
+        <v>41380.52</v>
       </c>
       <c r="AE2">
-        <v>3571.357461609886</v>
+        <v>3860.987616543744</v>
       </c>
       <c r="AF2">
-        <v>42506.85746160988</v>
+        <v>45241.50761654374</v>
       </c>
       <c r="AG2">
-        <v>35792.95746160988</v>
+        <v>37940.43261654375</v>
       </c>
       <c r="AH2">
-        <v>0.1431376689651063</v>
+        <v>0.1480782979781403</v>
       </c>
       <c r="AI2">
-        <v>0.3475854870732345</v>
+        <v>0.3500136817270637</v>
       </c>
       <c r="AJ2">
-        <v>0.1233172761069843</v>
+        <v>0.1272216200642466</v>
       </c>
       <c r="AK2">
-        <v>0.3096868445511423</v>
+        <v>0.3111010803180555</v>
       </c>
       <c r="AL2">
-        <v>2564.34</v>
+        <v>2827.888</v>
       </c>
       <c r="AM2">
-        <v>2201.11</v>
+        <v>2412.606</v>
       </c>
       <c r="AN2">
-        <v>1.748809737693137</v>
+        <v>1.823710253543222</v>
       </c>
       <c r="AO2">
-        <v>6.075949367088607</v>
+        <v>5.558491354678828</v>
       </c>
       <c r="AP2">
-        <v>1.607660683687113</v>
+        <v>1.672099721962327</v>
       </c>
       <c r="AQ2">
-        <v>7.078610337511527</v>
+        <v>6.515274769274386</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ryan Specialty Holdings, Inc. (NYSE:RYAN)</t>
+          <t>Health In Tech, Inc. (NasdaqCM:HIT)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,119 +724,107 @@
           <t>Insurance (General)</t>
         </is>
       </c>
-      <c r="F3">
-        <v>0.22</v>
-      </c>
       <c r="G3">
-        <v>0.2140215053763441</v>
+        <v>0.143939393939394</v>
       </c>
       <c r="H3">
-        <v>0.2140215053763441</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>0.2034060759603494</v>
+        <v>0.1406866849633948</v>
       </c>
       <c r="J3">
-        <v>0.1903979980154165</v>
+        <v>0.1030756881364872</v>
       </c>
       <c r="K3">
-        <v>103.8</v>
+        <v>1.82</v>
       </c>
       <c r="L3">
-        <v>0.04464516129032258</v>
+        <v>0.09191919191919191</v>
       </c>
       <c r="M3">
-        <v>131.3</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.01634914705516125</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>1.264932562620424</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>111.1</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.01383389366205952</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>1.070327552986513</v>
+        <v>-0</v>
       </c>
       <c r="S3">
-        <v>20.19999999999999</v>
-      </c>
-      <c r="T3">
-        <v>0.1538461538461538</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>235.2</v>
+        <v>1.75</v>
       </c>
       <c r="V3">
-        <v>0.02928651475532312</v>
-      </c>
-      <c r="W3">
-        <v>0.1911602209944751</v>
+        <v>0.006044905008635579</v>
       </c>
       <c r="X3">
-        <v>0.07993323293634128</v>
-      </c>
-      <c r="Y3">
-        <v>0.1112269880581339</v>
+        <v>0.07277248290521897</v>
       </c>
       <c r="Z3">
-        <v>6.608786639246444</v>
+        <v>71.47545111877425</v>
       </c>
       <c r="AA3">
-        <v>1.258299745423556</v>
+        <v>5</v>
       </c>
       <c r="AB3">
-        <v>0.0723670780522457</v>
+        <v>0.0727443558889008</v>
       </c>
       <c r="AC3">
-        <v>1.18593266737131</v>
+        <v>4.927255644111099</v>
       </c>
       <c r="AD3">
-        <v>2679.9</v>
+        <v>0</v>
       </c>
       <c r="AE3">
-        <v>163.9043669609381</v>
+        <v>0.2770181886239148</v>
       </c>
       <c r="AF3">
-        <v>2843.804366960938</v>
+        <v>0.2770181886239148</v>
       </c>
       <c r="AG3">
-        <v>2608.604366960938</v>
+        <v>-1.472981811376085</v>
       </c>
       <c r="AH3">
-        <v>0.2615039563930717</v>
+        <v>0.0009559701813329997</v>
       </c>
       <c r="AI3">
-        <v>0.7208073452521779</v>
+        <v>0.03854424482498143</v>
       </c>
       <c r="AJ3">
-        <v>0.2451786999769853</v>
+        <v>-0.005114040414123424</v>
       </c>
       <c r="AK3">
-        <v>0.7031080824008537</v>
+        <v>-0.2709172123900675</v>
       </c>
       <c r="AL3">
-        <v>161.6</v>
+        <v>0.494</v>
       </c>
       <c r="AM3">
-        <v>69.5</v>
+        <v>0.376</v>
       </c>
       <c r="AN3">
-        <v>4.185381852256755</v>
+        <v>0</v>
       </c>
       <c r="AO3">
-        <v>2.94740099009901</v>
+        <v>5.587044534412955</v>
       </c>
       <c r="AP3">
-        <v>4.074034619648506</v>
+        <v>-18.18496063427266</v>
       </c>
       <c r="AQ3">
-        <v>6.853237410071943</v>
+        <v>7.340425531914893</v>
       </c>
     </row>
     <row r="4">
@@ -847,7 +835,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown, Inc. (NYSE:BRO)</t>
+          <t>Ryan Specialty Holdings, Inc. (NYSE:RYAN)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -855,125 +843,119 @@
           <t>Insurance (General)</t>
         </is>
       </c>
-      <c r="D4">
-        <v>0.145</v>
-      </c>
-      <c r="E4">
-        <v>0.216</v>
-      </c>
       <c r="F4">
-        <v>0.113</v>
+        <v>0.22</v>
       </c>
       <c r="G4">
-        <v>0.3030030491148792</v>
+        <v>0.2140215053763441</v>
       </c>
       <c r="H4">
-        <v>0.3030030491148792</v>
+        <v>0.2140215053763441</v>
       </c>
       <c r="I4">
-        <v>0.2901155408454905</v>
+        <v>0.2034060759603494</v>
       </c>
       <c r="J4">
-        <v>0.2222380272762614</v>
+        <v>0.1903979980154165</v>
       </c>
       <c r="K4">
-        <v>1051.5</v>
+        <v>103.8</v>
       </c>
       <c r="L4">
-        <v>0.2306578629872552</v>
+        <v>0.04464516129032258</v>
       </c>
       <c r="M4">
-        <v>201.9</v>
+        <v>131.3</v>
       </c>
       <c r="N4">
-        <v>0.006920664301506505</v>
+        <v>0.01634914705516125</v>
       </c>
       <c r="O4">
-        <v>0.1920114122681883</v>
+        <v>1.264932562620424</v>
       </c>
       <c r="P4">
-        <v>148</v>
+        <v>111.1</v>
       </c>
       <c r="Q4">
-        <v>0.005073097160093921</v>
+        <v>0.01383389366205952</v>
       </c>
       <c r="R4">
-        <v>0.1407513076557299</v>
+        <v>1.070327552986513</v>
       </c>
       <c r="S4">
-        <v>53.90000000000001</v>
+        <v>20.19999999999999</v>
       </c>
       <c r="T4">
-        <v>0.2669638434868747</v>
+        <v>0.1538461538461538</v>
       </c>
       <c r="U4">
-        <v>957</v>
+        <v>235.2</v>
       </c>
       <c r="V4">
-        <v>0.03280374312303975</v>
+        <v>0.02928651475532312</v>
       </c>
       <c r="W4">
-        <v>0.2022621039875354</v>
+        <v>0.1911602209944751</v>
       </c>
       <c r="X4">
-        <v>0.07540058383342343</v>
+        <v>0.07991128830236709</v>
       </c>
       <c r="Y4">
-        <v>0.1268615201541119</v>
+        <v>0.111248932692108</v>
       </c>
       <c r="Z4">
-        <v>3.027524955475234</v>
+        <v>6.608786639246444</v>
       </c>
       <c r="AA4">
-        <v>0.6728311736344671</v>
+        <v>1.258299745423556</v>
       </c>
       <c r="AB4">
-        <v>0.07188534376549904</v>
+        <v>0.07235087202687736</v>
       </c>
       <c r="AC4">
-        <v>0.6009458298689681</v>
+        <v>1.185948873396678</v>
       </c>
       <c r="AD4">
-        <v>3592</v>
+        <v>2679.9</v>
       </c>
       <c r="AE4">
-        <v>201.2514197383119</v>
+        <v>163.9043669609381</v>
       </c>
       <c r="AF4">
-        <v>3793.251419738312</v>
+        <v>2843.804366960938</v>
       </c>
       <c r="AG4">
-        <v>2836.251419738312</v>
+        <v>2608.604366960938</v>
       </c>
       <c r="AH4">
-        <v>0.1150629424004199</v>
+        <v>0.2615039563930717</v>
       </c>
       <c r="AI4">
-        <v>0.3692357234098469</v>
+        <v>0.7208073452521779</v>
       </c>
       <c r="AJ4">
-        <v>0.08860585583896106</v>
+        <v>0.2451786999769853</v>
       </c>
       <c r="AK4">
-        <v>0.304441270630498</v>
+        <v>0.7031080824008537</v>
       </c>
       <c r="AL4">
-        <v>194</v>
+        <v>161.6</v>
       </c>
       <c r="AM4">
-        <v>104.6</v>
+        <v>69.5</v>
       </c>
       <c r="AN4">
-        <v>2.273705532345867</v>
+        <v>4.185381852256755</v>
       </c>
       <c r="AO4">
-        <v>6.759278350515464</v>
+        <v>2.94740099009901</v>
       </c>
       <c r="AP4">
-        <v>1.795323091364927</v>
+        <v>4.074034619648506</v>
       </c>
       <c r="AQ4">
-        <v>12.53632887189293</v>
+        <v>6.853237410071943</v>
       </c>
     </row>
     <row r="5">
@@ -984,7 +966,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Marsh &amp; McLennan Companies, Inc. (NYSE:MMC)</t>
+          <t>Brown &amp; Brown, Inc. (NYSE:BRO)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -993,124 +975,124 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.08259999999999999</v>
+        <v>0.145</v>
       </c>
       <c r="E5">
-        <v>0.218</v>
+        <v>0.216</v>
       </c>
       <c r="F5">
-        <v>0.08779999999999999</v>
+        <v>0.113</v>
       </c>
       <c r="G5">
-        <v>0.2747964084359992</v>
+        <v>0.3030030491148792</v>
       </c>
       <c r="H5">
-        <v>0.2747964084359992</v>
+        <v>0.3030030491148792</v>
       </c>
       <c r="I5">
-        <v>0.2726353891581973</v>
+        <v>0.2901155408454905</v>
       </c>
       <c r="J5">
-        <v>0.2015990257573117</v>
+        <v>0.2222380272762614</v>
       </c>
       <c r="K5">
-        <v>4028</v>
+        <v>1051.5</v>
       </c>
       <c r="L5">
-        <v>0.1682188348298183</v>
+        <v>0.2306578629872552</v>
       </c>
       <c r="M5">
-        <v>2781</v>
+        <v>201.9</v>
       </c>
       <c r="N5">
-        <v>0.02665858888736578</v>
+        <v>0.006920664301506505</v>
       </c>
       <c r="O5">
-        <v>0.6904170804369414</v>
+        <v>0.1920114122681883</v>
       </c>
       <c r="P5">
-        <v>1451</v>
+        <v>148</v>
       </c>
       <c r="Q5">
-        <v>0.0139092457661157</v>
+        <v>0.005073097160093921</v>
       </c>
       <c r="R5">
-        <v>0.3602284011916584</v>
+        <v>0.1407513076557299</v>
       </c>
       <c r="S5">
-        <v>1330</v>
+        <v>53.90000000000001</v>
       </c>
       <c r="T5">
-        <v>0.4782452355267889</v>
+        <v>0.2669638434868747</v>
       </c>
       <c r="U5">
-        <v>1798</v>
+        <v>957</v>
       </c>
       <c r="V5">
-        <v>0.01723557814436666</v>
+        <v>0.03280374312303975</v>
       </c>
       <c r="W5">
-        <v>0.3531474662458355</v>
+        <v>0.2022621039875354</v>
       </c>
       <c r="X5">
-        <v>0.07560956446928985</v>
+        <v>0.07538155328982216</v>
       </c>
       <c r="Y5">
-        <v>0.2775379017765457</v>
+        <v>0.1268805506977132</v>
       </c>
       <c r="Z5">
-        <v>3.283407785335362</v>
+        <v>3.027524955475234</v>
       </c>
       <c r="AA5">
-        <v>0.6619318106875813</v>
+        <v>0.6728311736344671</v>
       </c>
       <c r="AB5">
-        <v>0.07140827386170726</v>
+        <v>0.07186850293224001</v>
       </c>
       <c r="AC5">
-        <v>0.5905235368258741</v>
+        <v>0.6009626707022271</v>
       </c>
       <c r="AD5">
-        <v>12848</v>
+        <v>3592</v>
       </c>
       <c r="AE5">
-        <v>1793.72803303483</v>
+        <v>201.2514197383119</v>
       </c>
       <c r="AF5">
-        <v>14641.72803303483</v>
+        <v>3793.251419738312</v>
       </c>
       <c r="AG5">
-        <v>12843.72803303483</v>
+        <v>2836.251419738312</v>
       </c>
       <c r="AH5">
-        <v>0.1230802464570009</v>
+        <v>0.1150629424004199</v>
       </c>
       <c r="AI5">
-        <v>0.5133174743524925</v>
+        <v>0.3692357234098469</v>
       </c>
       <c r="AJ5">
-        <v>0.1096228919074355</v>
+        <v>0.08860585583896106</v>
       </c>
       <c r="AK5">
-        <v>0.4805754221983813</v>
+        <v>0.304441270630498</v>
       </c>
       <c r="AL5">
-        <v>620</v>
+        <v>194</v>
       </c>
       <c r="AM5">
-        <v>519</v>
+        <v>104.6</v>
       </c>
       <c r="AN5">
-        <v>1.686531898135994</v>
+        <v>2.273705532345867</v>
       </c>
       <c r="AO5">
-        <v>10.50806451612903</v>
+        <v>6.759278350515464</v>
       </c>
       <c r="AP5">
-        <v>1.685971125365559</v>
+        <v>1.795323091364927</v>
       </c>
       <c r="AQ5">
-        <v>12.55298651252408</v>
+        <v>12.53632887189293</v>
       </c>
     </row>
     <row r="6">
@@ -1121,7 +1103,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Arthur J. Gallagher &amp; Co. (NYSE:AJG)</t>
+          <t>Marsh &amp; McLennan Companies, Inc. (NYSE:MMC)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1130,121 +1112,124 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.09269999999999999</v>
+        <v>0.08259999999999999</v>
       </c>
       <c r="E6">
-        <v>0.113</v>
+        <v>0.218</v>
+      </c>
+      <c r="F6">
+        <v>0.08779999999999999</v>
       </c>
       <c r="G6">
-        <v>0.2784761476231989</v>
+        <v>0.2747964084359992</v>
       </c>
       <c r="H6">
-        <v>0.2784761476231989</v>
+        <v>0.2747964084359992</v>
       </c>
       <c r="I6">
-        <v>0.2446447862014885</v>
+        <v>0.2726353891581973</v>
       </c>
       <c r="J6">
-        <v>0.1965674087295227</v>
+        <v>0.2015990257573117</v>
       </c>
       <c r="K6">
-        <v>1172.2</v>
+        <v>4028</v>
       </c>
       <c r="L6">
-        <v>0.1098831050741959</v>
+        <v>0.1682188348298183</v>
       </c>
       <c r="M6">
-        <v>512.7</v>
+        <v>2781</v>
       </c>
       <c r="N6">
-        <v>0.008230908530476999</v>
+        <v>0.02665858888736578</v>
       </c>
       <c r="O6">
-        <v>0.4373826991980891</v>
+        <v>0.6904170804369414</v>
       </c>
       <c r="P6">
-        <v>512.7</v>
+        <v>1451</v>
       </c>
       <c r="Q6">
-        <v>0.008230908530476999</v>
+        <v>0.0139092457661157</v>
       </c>
       <c r="R6">
-        <v>0.4373826991980891</v>
+        <v>0.3602284011916584</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1330</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>0.4782452355267889</v>
       </c>
       <c r="U6">
-        <v>2022.4</v>
+        <v>1798</v>
       </c>
       <c r="V6">
-        <v>0.03246769926279829</v>
+        <v>0.01723557814436666</v>
       </c>
       <c r="W6">
-        <v>0.1120275242509677</v>
+        <v>0.3531474662458355</v>
       </c>
       <c r="X6">
-        <v>0.07558382724198921</v>
+        <v>0.0755903995697203</v>
       </c>
       <c r="Y6">
-        <v>0.03644369700897844</v>
+        <v>0.2775570666761152</v>
       </c>
       <c r="Z6">
-        <v>1.747739143016059</v>
+        <v>3.283407785335362</v>
       </c>
       <c r="AA6">
-        <v>0.3435485544778235</v>
+        <v>0.6619318106875813</v>
       </c>
       <c r="AB6">
-        <v>0.07164805374241069</v>
+        <v>0.07139146778270006</v>
       </c>
       <c r="AC6">
-        <v>0.2719005007354128</v>
+        <v>0.5905403429048812</v>
       </c>
       <c r="AD6">
-        <v>8253.9</v>
+        <v>12848</v>
       </c>
       <c r="AE6">
-        <v>409.5140711919055</v>
+        <v>1793.72803303483</v>
       </c>
       <c r="AF6">
-        <v>8663.414071191904</v>
+        <v>14641.72803303483</v>
       </c>
       <c r="AG6">
-        <v>6641.014071191905</v>
+        <v>12843.72803303483</v>
       </c>
       <c r="AH6">
-        <v>0.1221007195339062</v>
+        <v>0.1230802464570009</v>
       </c>
       <c r="AI6">
-        <v>0.4150533335359938</v>
+        <v>0.5133174743524925</v>
       </c>
       <c r="AJ6">
-        <v>0.09634346307045852</v>
+        <v>0.1096228919074355</v>
       </c>
       <c r="AK6">
-        <v>0.3522969621101579</v>
+        <v>0.4805754221983813</v>
       </c>
       <c r="AL6">
-        <v>357.6</v>
+        <v>620</v>
       </c>
       <c r="AM6">
-        <v>278.9</v>
+        <v>519</v>
       </c>
       <c r="AN6">
-        <v>2.364269141531322</v>
+        <v>1.686531898135994</v>
       </c>
       <c r="AO6">
-        <v>7.222595078299777</v>
+        <v>10.50806451612903</v>
       </c>
       <c r="AP6">
-        <v>1.902269792097592</v>
+        <v>1.685971125365559</v>
       </c>
       <c r="AQ6">
-        <v>9.260666905700967</v>
+        <v>12.55298651252408</v>
       </c>
     </row>
     <row r="7">
@@ -1255,7 +1240,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Goosehead Insurance, Inc (NasdaqGS:GSHD)</t>
+          <t>Hagerty, Inc. (NYSE:HGTY)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1263,41 +1248,32 @@
           <t>Insurance (General)</t>
         </is>
       </c>
-      <c r="D7">
-        <v>0.294</v>
-      </c>
-      <c r="E7">
-        <v>0.339</v>
-      </c>
-      <c r="F7">
-        <v>0.309</v>
-      </c>
       <c r="G7">
-        <v>0.1450813871196037</v>
+        <v>0.05982313161088954</v>
       </c>
       <c r="H7">
-        <v>0.1450813871196037</v>
+        <v>0.05982313161088954</v>
       </c>
       <c r="I7">
-        <v>0.1257086657075828</v>
+        <v>0.0448128825737703</v>
       </c>
       <c r="J7">
-        <v>0.1257086657075828</v>
+        <v>0.03756888260365136</v>
       </c>
       <c r="K7">
-        <v>19.2</v>
+        <v>24.8</v>
       </c>
       <c r="L7">
-        <v>0.06794055201698514</v>
+        <v>0.02150164730362407</v>
       </c>
       <c r="M7">
-        <v>63.2</v>
+        <v>5.71</v>
       </c>
       <c r="N7">
-        <v>0.02416456373786037</v>
+        <v>0.006572283609576427</v>
       </c>
       <c r="O7">
-        <v>3.291666666666667</v>
+        <v>0.230241935483871</v>
       </c>
       <c r="P7">
         <v>-0</v>
@@ -1309,79 +1285,76 @@
         <v>-0</v>
       </c>
       <c r="S7">
-        <v>63.2</v>
+        <v>5.71</v>
       </c>
       <c r="T7">
         <v>1</v>
       </c>
       <c r="U7">
-        <v>47.5</v>
+        <v>147.1</v>
       </c>
       <c r="V7">
-        <v>0.01816165787260075</v>
+        <v>0.1693139963167588</v>
       </c>
       <c r="W7">
-        <v>0.4120171673819742</v>
+        <v>0.3337819650067295</v>
       </c>
       <c r="X7">
-        <v>0.07394663757569656</v>
+        <v>0.07690207348934079</v>
       </c>
       <c r="Y7">
-        <v>0.3380705298062777</v>
+        <v>0.2568798915173887</v>
       </c>
       <c r="Z7">
-        <v>1.914975944180744</v>
+        <v>14.13236085946934</v>
       </c>
       <c r="AA7">
-        <v>0.2407290708050798</v>
+        <v>0.5309370060418411</v>
       </c>
       <c r="AB7">
-        <v>0.07284644151549516</v>
+        <v>0.07086916178750884</v>
       </c>
       <c r="AC7">
-        <v>0.1678826292895847</v>
+        <v>0.4600678442543323</v>
       </c>
       <c r="AD7">
-        <v>94.7</v>
+        <v>122.9</v>
       </c>
       <c r="AE7">
-        <v>57.3736553551855</v>
+        <v>55.41410619706668</v>
       </c>
       <c r="AF7">
-        <v>152.0736553551855</v>
+        <v>178.3141061970667</v>
       </c>
       <c r="AG7">
-        <v>104.5736553551855</v>
+        <v>31.21410619706668</v>
       </c>
       <c r="AH7">
-        <v>0.05495035338851958</v>
+        <v>0.1702909980314103</v>
       </c>
       <c r="AI7">
-        <v>0.9854202520357525</v>
+        <v>0.2267144413458095</v>
       </c>
       <c r="AJ7">
-        <v>0.03844656919720417</v>
+        <v>0.03468179663200974</v>
       </c>
       <c r="AK7">
-        <v>0.9789372495022866</v>
+        <v>0.04881673065161708</v>
       </c>
       <c r="AL7">
-        <v>7.04</v>
+        <v>0</v>
       </c>
       <c r="AM7">
-        <v>5.01</v>
+        <v>-35.1</v>
       </c>
       <c r="AN7">
-        <v>1.644097222222223</v>
-      </c>
-      <c r="AO7">
-        <v>5.071022727272728</v>
+        <v>1.187783898714603</v>
       </c>
       <c r="AP7">
-        <v>1.815514849916415</v>
+        <v>0.3016730085731776</v>
       </c>
       <c r="AQ7">
-        <v>7.125748502994012</v>
+        <v>-1.52991452991453</v>
       </c>
     </row>
     <row r="8">
@@ -1392,7 +1365,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Baldwin Insurance Group, Inc. (NasdaqGS:BWIN)</t>
+          <t>Arthur J. Gallagher &amp; Co. (NYSE:AJG)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1401,118 +1374,121 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.615</v>
-      </c>
-      <c r="F8">
-        <v>0.334</v>
+        <v>0.09269999999999999</v>
+      </c>
+      <c r="E8">
+        <v>0.113</v>
       </c>
       <c r="G8">
-        <v>0.1060425658580146</v>
+        <v>0.2784761476231989</v>
       </c>
       <c r="H8">
-        <v>0.1060425658580146</v>
+        <v>0.2784761476231989</v>
       </c>
       <c r="I8">
-        <v>0.06802842265679529</v>
+        <v>0.2446447862014885</v>
       </c>
       <c r="J8">
-        <v>0.06802842265679529</v>
+        <v>0.1965674087295227</v>
       </c>
       <c r="K8">
-        <v>-38.8</v>
+        <v>1172.2</v>
       </c>
       <c r="L8">
-        <v>-0.0288733442476559</v>
+        <v>0.1098831050741959</v>
       </c>
       <c r="M8">
-        <v>-0</v>
+        <v>512.7</v>
       </c>
       <c r="N8">
-        <v>-0</v>
+        <v>0.008230908530476999</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>0.4373826991980891</v>
       </c>
       <c r="P8">
-        <v>-0</v>
+        <v>512.7</v>
       </c>
       <c r="Q8">
-        <v>-0</v>
+        <v>0.008230908530476999</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>0.4373826991980891</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
       <c r="U8">
-        <v>181.8</v>
+        <v>2022.4</v>
       </c>
       <c r="V8">
-        <v>0.06941580756013746</v>
+        <v>0.03246769926279829</v>
       </c>
       <c r="W8">
-        <v>-0.06567366283006093</v>
+        <v>0.1120275242509677</v>
       </c>
       <c r="X8">
-        <v>0.08432420178594074</v>
+        <v>0.07556467888916851</v>
       </c>
       <c r="Y8">
-        <v>-0.1499978646160017</v>
+        <v>0.03646284536179914</v>
       </c>
       <c r="Z8">
-        <v>2.808846510215197</v>
+        <v>1.747739143016059</v>
       </c>
       <c r="AA8">
-        <v>0.1910813975749839</v>
+        <v>0.3435485544778235</v>
       </c>
       <c r="AB8">
-        <v>0.07820801286532508</v>
+        <v>0.07163124341724729</v>
       </c>
       <c r="AC8">
-        <v>0.1128733847096588</v>
+        <v>0.2719173110605762</v>
       </c>
       <c r="AD8">
-        <v>1413</v>
+        <v>8253.9</v>
       </c>
       <c r="AE8">
-        <v>82.91702816899243</v>
+        <v>409.5140711919055</v>
       </c>
       <c r="AF8">
-        <v>1495.917028168992</v>
+        <v>8663.414071191904</v>
       </c>
       <c r="AG8">
-        <v>1314.117028168992</v>
+        <v>6641.014071191905</v>
       </c>
       <c r="AH8">
-        <v>0.3635351619312305</v>
+        <v>0.1221007195339062</v>
       </c>
       <c r="AI8">
-        <v>0.5906838972966507</v>
+        <v>0.4150533335359938</v>
       </c>
       <c r="AJ8">
-        <v>0.3341159235174757</v>
+        <v>0.09634346307045852</v>
       </c>
       <c r="AK8">
-        <v>0.5590281656285007</v>
+        <v>0.3522969621101579</v>
       </c>
       <c r="AL8">
-        <v>126.1</v>
+        <v>357.6</v>
       </c>
       <c r="AM8">
-        <v>126.1</v>
+        <v>278.9</v>
       </c>
       <c r="AN8">
-        <v>6.658812441093308</v>
+        <v>2.364269141531322</v>
       </c>
       <c r="AO8">
-        <v>0.6875495638382236</v>
+        <v>7.222595078299777</v>
       </c>
       <c r="AP8">
-        <v>6.192822941418437</v>
+        <v>1.902269792097592</v>
       </c>
       <c r="AQ8">
-        <v>0.6875495638382236</v>
+        <v>9.260666905700967</v>
       </c>
     </row>
     <row r="9">
@@ -1523,130 +1499,1827 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>Goosehead Insurance, Inc (NasdaqGS:GSHD)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Insurance (General)</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>0.294</v>
+      </c>
+      <c r="E9">
+        <v>0.339</v>
+      </c>
+      <c r="F9">
+        <v>0.309</v>
+      </c>
+      <c r="G9">
+        <v>0.1450813871196037</v>
+      </c>
+      <c r="H9">
+        <v>0.1450813871196037</v>
+      </c>
+      <c r="I9">
+        <v>0.1257086657075828</v>
+      </c>
+      <c r="J9">
+        <v>0.1257086657075828</v>
+      </c>
+      <c r="K9">
+        <v>19.2</v>
+      </c>
+      <c r="L9">
+        <v>0.06794055201698514</v>
+      </c>
+      <c r="M9">
+        <v>63.2</v>
+      </c>
+      <c r="N9">
+        <v>0.02416456373786037</v>
+      </c>
+      <c r="O9">
+        <v>3.291666666666667</v>
+      </c>
+      <c r="P9">
+        <v>-0</v>
+      </c>
+      <c r="Q9">
+        <v>-0</v>
+      </c>
+      <c r="R9">
+        <v>-0</v>
+      </c>
+      <c r="S9">
+        <v>63.2</v>
+      </c>
+      <c r="T9">
+        <v>1</v>
+      </c>
+      <c r="U9">
+        <v>47.5</v>
+      </c>
+      <c r="V9">
+        <v>0.01816165787260075</v>
+      </c>
+      <c r="W9">
+        <v>0.4120171673819742</v>
+      </c>
+      <c r="X9">
+        <v>0.07392854179026789</v>
+      </c>
+      <c r="Y9">
+        <v>0.3380886255917064</v>
+      </c>
+      <c r="Z9">
+        <v>1.914975944180744</v>
+      </c>
+      <c r="AA9">
+        <v>0.2407290708050798</v>
+      </c>
+      <c r="AB9">
+        <v>0.07282934009987065</v>
+      </c>
+      <c r="AC9">
+        <v>0.1678997307052092</v>
+      </c>
+      <c r="AD9">
+        <v>94.7</v>
+      </c>
+      <c r="AE9">
+        <v>57.3736553551855</v>
+      </c>
+      <c r="AF9">
+        <v>152.0736553551855</v>
+      </c>
+      <c r="AG9">
+        <v>104.5736553551855</v>
+      </c>
+      <c r="AH9">
+        <v>0.05495035338851958</v>
+      </c>
+      <c r="AI9">
+        <v>0.9854202520357525</v>
+      </c>
+      <c r="AJ9">
+        <v>0.03844656919720417</v>
+      </c>
+      <c r="AK9">
+        <v>0.9789372495022866</v>
+      </c>
+      <c r="AL9">
+        <v>7.04</v>
+      </c>
+      <c r="AM9">
+        <v>5.01</v>
+      </c>
+      <c r="AN9">
+        <v>1.644097222222223</v>
+      </c>
+      <c r="AO9">
+        <v>5.071022727272728</v>
+      </c>
+      <c r="AP9">
+        <v>1.815514849916415</v>
+      </c>
+      <c r="AQ9">
+        <v>7.125748502994012</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Abacus Life, Inc. (NasdaqCM:ABL)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Insurance (General)</t>
+        </is>
+      </c>
+      <c r="G10">
+        <v>0.2783203125</v>
+      </c>
+      <c r="H10">
+        <v>0.2783203125</v>
+      </c>
+      <c r="I10">
+        <v>0.2021715009613278</v>
+      </c>
+      <c r="J10">
+        <v>0.2021715009613278</v>
+      </c>
+      <c r="K10">
+        <v>-11.9</v>
+      </c>
+      <c r="L10">
+        <v>-0.1162109375</v>
+      </c>
+      <c r="M10">
+        <v>12</v>
+      </c>
+      <c r="N10">
+        <v>0.01632208922742111</v>
+      </c>
+      <c r="O10">
+        <v>-1.008403361344538</v>
+      </c>
+      <c r="P10">
+        <v>-0</v>
+      </c>
+      <c r="Q10">
+        <v>-0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>12</v>
+      </c>
+      <c r="T10">
+        <v>1</v>
+      </c>
+      <c r="U10">
+        <v>19.4</v>
+      </c>
+      <c r="V10">
+        <v>0.02638737758433079</v>
+      </c>
+      <c r="W10">
+        <v>-0.07177322074788901</v>
+      </c>
+      <c r="X10">
+        <v>0.07776501007012696</v>
+      </c>
+      <c r="Y10">
+        <v>-0.149538230818016</v>
+      </c>
+      <c r="Z10">
+        <v>0.9327900067721927</v>
+      </c>
+      <c r="AA10">
+        <v>0.1885835557508613</v>
+      </c>
+      <c r="AB10">
+        <v>0.0709276750202375</v>
+      </c>
+      <c r="AC10">
+        <v>0.1176558807306238</v>
+      </c>
+      <c r="AD10">
+        <v>180.2</v>
+      </c>
+      <c r="AE10">
+        <v>2.078191507800172</v>
+      </c>
+      <c r="AF10">
+        <v>182.2781915078002</v>
+      </c>
+      <c r="AG10">
+        <v>162.8781915078002</v>
+      </c>
+      <c r="AH10">
+        <v>0.1986730509727331</v>
+      </c>
+      <c r="AI10">
+        <v>0.4141009141852729</v>
+      </c>
+      <c r="AJ10">
+        <v>0.1813630405993279</v>
+      </c>
+      <c r="AK10">
+        <v>0.3870880069239064</v>
+      </c>
+      <c r="AL10">
+        <v>18.7</v>
+      </c>
+      <c r="AM10">
+        <v>16.51</v>
+      </c>
+      <c r="AN10">
+        <v>6.43157969876508</v>
+      </c>
+      <c r="AO10">
+        <v>1.122994652406417</v>
+      </c>
+      <c r="AP10">
+        <v>5.813341120272688</v>
+      </c>
+      <c r="AQ10">
+        <v>1.271956390066626</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>The Baldwin Insurance Group, Inc. (NasdaqGS:BWIN)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Insurance (General)</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>0.615</v>
+      </c>
+      <c r="F11">
+        <v>0.334</v>
+      </c>
+      <c r="G11">
+        <v>0.1060425658580146</v>
+      </c>
+      <c r="H11">
+        <v>0.1060425658580146</v>
+      </c>
+      <c r="I11">
+        <v>0.06802842265679529</v>
+      </c>
+      <c r="J11">
+        <v>0.06802842265679529</v>
+      </c>
+      <c r="K11">
+        <v>-38.8</v>
+      </c>
+      <c r="L11">
+        <v>-0.0288733442476559</v>
+      </c>
+      <c r="M11">
+        <v>-0</v>
+      </c>
+      <c r="N11">
+        <v>-0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>-0</v>
+      </c>
+      <c r="Q11">
+        <v>-0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>181.8</v>
+      </c>
+      <c r="V11">
+        <v>0.06941580756013746</v>
+      </c>
+      <c r="W11">
+        <v>-0.06567366283006093</v>
+      </c>
+      <c r="X11">
+        <v>0.08429943414939964</v>
+      </c>
+      <c r="Y11">
+        <v>-0.1499730969794606</v>
+      </c>
+      <c r="Z11">
+        <v>2.808846510215197</v>
+      </c>
+      <c r="AA11">
+        <v>0.1910813975749839</v>
+      </c>
+      <c r="AB11">
+        <v>0.07819224913554459</v>
+      </c>
+      <c r="AC11">
+        <v>0.1128891484394393</v>
+      </c>
+      <c r="AD11">
+        <v>1413</v>
+      </c>
+      <c r="AE11">
+        <v>82.91702816899243</v>
+      </c>
+      <c r="AF11">
+        <v>1495.917028168992</v>
+      </c>
+      <c r="AG11">
+        <v>1314.117028168992</v>
+      </c>
+      <c r="AH11">
+        <v>0.3635351619312305</v>
+      </c>
+      <c r="AI11">
+        <v>0.5906838972966507</v>
+      </c>
+      <c r="AJ11">
+        <v>0.3341159235174757</v>
+      </c>
+      <c r="AK11">
+        <v>0.5590281656285007</v>
+      </c>
+      <c r="AL11">
+        <v>126.1</v>
+      </c>
+      <c r="AM11">
+        <v>126.1</v>
+      </c>
+      <c r="AN11">
+        <v>6.658812441093308</v>
+      </c>
+      <c r="AO11">
+        <v>0.6875495638382236</v>
+      </c>
+      <c r="AP11">
+        <v>6.192822941418437</v>
+      </c>
+      <c r="AQ11">
+        <v>0.6875495638382236</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Crawford &amp; Company (NYSE:CRD.B)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Insurance (General)</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>0.0396</v>
+      </c>
+      <c r="E12">
+        <v>-0.0877</v>
+      </c>
+      <c r="G12">
+        <v>0.06895440631545029</v>
+      </c>
+      <c r="H12">
+        <v>0.06895440631545029</v>
+      </c>
+      <c r="I12">
+        <v>0.04438472598947633</v>
+      </c>
+      <c r="J12">
+        <v>0.02876247046028564</v>
+      </c>
+      <c r="K12">
+        <v>20.1</v>
+      </c>
+      <c r="L12">
+        <v>0.01619139681005317</v>
+      </c>
+      <c r="M12">
+        <v>21.4</v>
+      </c>
+      <c r="N12">
+        <v>0.03768269061454482</v>
+      </c>
+      <c r="O12">
+        <v>1.064676616915423</v>
+      </c>
+      <c r="P12">
+        <v>13.7</v>
+      </c>
+      <c r="Q12">
+        <v>0.02412396548688149</v>
+      </c>
+      <c r="R12">
+        <v>0.6815920398009949</v>
+      </c>
+      <c r="S12">
+        <v>7.699999999999999</v>
+      </c>
+      <c r="T12">
+        <v>0.3598130841121495</v>
+      </c>
+      <c r="U12">
+        <v>52.3</v>
+      </c>
+      <c r="V12">
+        <v>0.09209367846451839</v>
+      </c>
+      <c r="W12">
+        <v>0.1221142162818955</v>
+      </c>
+      <c r="X12">
+        <v>0.08478110295976926</v>
+      </c>
+      <c r="Y12">
+        <v>0.03733311332212626</v>
+      </c>
+      <c r="Z12">
+        <v>3.480196408991514</v>
+      </c>
+      <c r="AA12">
+        <v>0.1000990464096106</v>
+      </c>
+      <c r="AB12">
+        <v>0.06862605664562058</v>
+      </c>
+      <c r="AC12">
+        <v>0.03147298976399003</v>
+      </c>
+      <c r="AD12">
+        <v>238.4</v>
+      </c>
+      <c r="AE12">
+        <v>99.50400578332039</v>
+      </c>
+      <c r="AF12">
+        <v>337.9040057833204</v>
+      </c>
+      <c r="AG12">
+        <v>285.6040057833204</v>
+      </c>
+      <c r="AH12">
+        <v>0.3730431789061344</v>
+      </c>
+      <c r="AI12">
+        <v>0.6797450872496233</v>
+      </c>
+      <c r="AJ12">
+        <v>0.334625266956072</v>
+      </c>
+      <c r="AK12">
+        <v>0.642089554207945</v>
+      </c>
+      <c r="AL12">
+        <v>20</v>
+      </c>
+      <c r="AM12">
+        <v>16.35</v>
+      </c>
+      <c r="AN12">
+        <v>2.58008658008658</v>
+      </c>
+      <c r="AO12">
+        <v>2.275</v>
+      </c>
+      <c r="AP12">
+        <v>3.090952443542428</v>
+      </c>
+      <c r="AQ12">
+        <v>2.782874617737003</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>The Marketing Alliance, Inc. (OTCPK:MAAL)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Insurance (General)</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>-0.116</v>
+      </c>
+      <c r="E13">
+        <v>0.133</v>
+      </c>
+      <c r="G13">
+        <v>0.06834170854271358</v>
+      </c>
+      <c r="H13">
+        <v>0.06834170854271358</v>
+      </c>
+      <c r="I13">
+        <v>0.053177368120239</v>
+      </c>
+      <c r="J13">
+        <v>0.04335019049161883</v>
+      </c>
+      <c r="K13">
+        <v>1.02</v>
+      </c>
+      <c r="L13">
+        <v>0.05125628140703518</v>
+      </c>
+      <c r="M13">
+        <v>1.2315</v>
+      </c>
+      <c r="N13">
+        <v>0.1099553571428572</v>
+      </c>
+      <c r="O13">
+        <v>1.207352941176471</v>
+      </c>
+      <c r="P13">
+        <v>1.2315</v>
+      </c>
+      <c r="Q13">
+        <v>0.1099553571428572</v>
+      </c>
+      <c r="R13">
+        <v>1.207352941176471</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>1.37</v>
+      </c>
+      <c r="V13">
+        <v>0.1223214285714286</v>
+      </c>
+      <c r="W13">
+        <v>0.1613924050632911</v>
+      </c>
+      <c r="X13">
+        <v>0.07845454422673742</v>
+      </c>
+      <c r="Y13">
+        <v>0.08293786083655372</v>
+      </c>
+      <c r="Z13">
+        <v>2.142353035029904</v>
+      </c>
+      <c r="AA13">
+        <v>0.09287141216884408</v>
+      </c>
+      <c r="AB13">
+        <v>0.07177124663390363</v>
+      </c>
+      <c r="AC13">
+        <v>0.02110016553494044</v>
+      </c>
+      <c r="AD13">
+        <v>3.02</v>
+      </c>
+      <c r="AE13">
+        <v>0.1388518720362198</v>
+      </c>
+      <c r="AF13">
+        <v>3.15885187203622</v>
+      </c>
+      <c r="AG13">
+        <v>1.78885187203622</v>
+      </c>
+      <c r="AH13">
+        <v>0.2199933462777804</v>
+      </c>
+      <c r="AI13">
+        <v>0.3301181703175458</v>
+      </c>
+      <c r="AJ13">
+        <v>0.1377220935044652</v>
+      </c>
+      <c r="AK13">
+        <v>0.218183216376606</v>
+      </c>
+      <c r="AL13">
+        <v>0.174</v>
+      </c>
+      <c r="AM13">
+        <v>-0.32</v>
+      </c>
+      <c r="AN13">
+        <v>2.245353159851301</v>
+      </c>
+      <c r="AO13">
+        <v>5.695402298850575</v>
+      </c>
+      <c r="AP13">
+        <v>1.330001391848491</v>
+      </c>
+      <c r="AQ13">
+        <v>-3.096875</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Horace Mann Educators Corporation (NYSE:HMN)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Insurance (General)</t>
+        </is>
+      </c>
+      <c r="D14">
+        <v>0.028</v>
+      </c>
+      <c r="E14">
+        <v>-0.0452</v>
+      </c>
+      <c r="F14">
+        <v>0.127</v>
+      </c>
+      <c r="G14">
+        <v>0.06871814234472344</v>
+      </c>
+      <c r="H14">
+        <v>0.06871814234472344</v>
+      </c>
+      <c r="I14">
+        <v>0.102070354288591</v>
+      </c>
+      <c r="J14">
+        <v>0.0833374422073908</v>
+      </c>
+      <c r="K14">
+        <v>104.1</v>
+      </c>
+      <c r="L14">
+        <v>0.06550877855389843</v>
+      </c>
+      <c r="M14">
+        <v>65.5</v>
+      </c>
+      <c r="N14">
+        <v>0.04096566389392707</v>
+      </c>
+      <c r="O14">
+        <v>0.6292026897214218</v>
+      </c>
+      <c r="P14">
+        <v>55.2</v>
+      </c>
+      <c r="Q14">
+        <v>0.03452373506785916</v>
+      </c>
+      <c r="R14">
+        <v>0.5302593659942364</v>
+      </c>
+      <c r="S14">
+        <v>10.3</v>
+      </c>
+      <c r="T14">
+        <v>0.1572519083969465</v>
+      </c>
+      <c r="U14">
+        <v>39.4</v>
+      </c>
+      <c r="V14">
+        <v>0.02464194133466758</v>
+      </c>
+      <c r="W14">
+        <v>0.09902026062969657</v>
+      </c>
+      <c r="X14">
+        <v>0.08023398865698621</v>
+      </c>
+      <c r="Y14">
+        <v>0.01878627197271036</v>
+      </c>
+      <c r="Z14">
+        <v>1.052662957074722</v>
+      </c>
+      <c r="AA14">
+        <v>0.08772623834907572</v>
+      </c>
+      <c r="AB14">
+        <v>0.06905581551340055</v>
+      </c>
+      <c r="AC14">
+        <v>0.01867042283567517</v>
+      </c>
+      <c r="AD14">
+        <v>591.7</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>591.7</v>
+      </c>
+      <c r="AG14">
+        <v>552.3000000000001</v>
+      </c>
+      <c r="AH14">
+        <v>0.2701086460330503</v>
+      </c>
+      <c r="AI14">
+        <v>0.3149518283919732</v>
+      </c>
+      <c r="AJ14">
+        <v>0.2567404239494236</v>
+      </c>
+      <c r="AK14">
+        <v>0.3002772793997717</v>
+      </c>
+      <c r="AL14">
+        <v>34.7</v>
+      </c>
+      <c r="AM14">
+        <v>34.7</v>
+      </c>
+      <c r="AN14">
+        <v>3.142326075411577</v>
+      </c>
+      <c r="AO14">
+        <v>4.674351585014408</v>
+      </c>
+      <c r="AP14">
+        <v>2.933085501858736</v>
+      </c>
+      <c r="AQ14">
+        <v>4.674351585014408</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>American International Group, Inc. (NYSE:AIG)</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Insurance (General)</t>
         </is>
       </c>
-      <c r="D9">
+      <c r="D15">
         <v>-0.0227</v>
       </c>
-      <c r="F9">
+      <c r="F15">
         <v>0.19</v>
       </c>
-      <c r="G9">
+      <c r="G15">
         <v>0.1978410119428685</v>
       </c>
-      <c r="H9">
+      <c r="H15">
         <v>0.1978410119428685</v>
       </c>
-      <c r="I9">
+      <c r="I15">
         <v>0.1007630681155888</v>
       </c>
-      <c r="J9">
+      <c r="J15">
         <v>0.09964760979696601</v>
       </c>
-      <c r="K9">
+      <c r="K15">
         <v>-2209</v>
       </c>
-      <c r="L9">
+      <c r="L15">
         <v>-0.04876487339676373</v>
       </c>
-      <c r="M9">
+      <c r="M15">
         <v>6871</v>
       </c>
-      <c r="N9">
+      <c r="N15">
         <v>0.1513089512534574</v>
       </c>
-      <c r="O9">
+      <c r="O15">
         <v>-3.110457220461747</v>
       </c>
-      <c r="P9">
+      <c r="P15">
         <v>1007</v>
       </c>
-      <c r="Q9">
+      <c r="Q15">
         <v>0.02217553688141924</v>
       </c>
-      <c r="R9">
+      <c r="R15">
         <v>-0.4558623811679493</v>
       </c>
-      <c r="S9">
+      <c r="S15">
         <v>5864</v>
       </c>
-      <c r="T9">
+      <c r="T15">
         <v>0.853442002619706</v>
       </c>
-      <c r="U9">
+      <c r="U15">
         <v>1472</v>
       </c>
-      <c r="V9">
+      <c r="V15">
         <v>0.03241548191603685</v>
       </c>
-      <c r="W9">
+      <c r="W15">
         <v>-0.05592546646750551</v>
       </c>
-      <c r="X9">
-        <v>0.07763326052910564</v>
-      </c>
-      <c r="Y9">
-        <v>-0.1335587269966111</v>
-      </c>
-      <c r="Z9">
+      <c r="X15">
+        <v>0.07761279457289752</v>
+      </c>
+      <c r="Y15">
+        <v>-0.133538261040403</v>
+      </c>
+      <c r="Z15">
         <v>0.7365970258664245</v>
       </c>
-      <c r="AA9">
+      <c r="AA15">
         <v>0.07340013301114315</v>
       </c>
-      <c r="AB9">
-        <v>0.07078537169837819</v>
-      </c>
-      <c r="AC9">
-        <v>0.00261476131276496</v>
-      </c>
-      <c r="AD9">
+      <c r="AB15">
+        <v>0.07076887221995415</v>
+      </c>
+      <c r="AC15">
+        <v>0.002631260791189</v>
+      </c>
+      <c r="AD15">
         <v>10054</v>
       </c>
-      <c r="AE9">
+      <c r="AE15">
         <v>862.668887159723</v>
       </c>
-      <c r="AF9">
+      <c r="AF15">
         <v>10916.66888715972</v>
       </c>
-      <c r="AG9">
+      <c r="AG15">
         <v>9444.668887159723</v>
       </c>
-      <c r="AH9">
+      <c r="AH15">
         <v>0.1938085737965371</v>
       </c>
-      <c r="AI9">
+      <c r="AI15">
         <v>0.1949764859149448</v>
       </c>
-      <c r="AJ9">
+      <c r="AJ15">
         <v>0.1721749526299565</v>
       </c>
-      <c r="AK9">
+      <c r="AK15">
         <v>0.1732405122953483</v>
       </c>
-      <c r="AL9">
+      <c r="AL15">
         <v>1098</v>
       </c>
-      <c r="AM9">
+      <c r="AM15">
         <v>1098</v>
       </c>
-      <c r="AN9">
+      <c r="AN15">
         <v>1.160300057703405</v>
       </c>
-      <c r="AO9">
+      <c r="AO15">
         <v>4.164845173041894</v>
       </c>
-      <c r="AP9">
+      <c r="AP15">
         <v>1.089979098345034</v>
       </c>
-      <c r="AQ9">
+      <c r="AQ15">
         <v>4.164845173041894</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SelectQuote, Inc. (NYSE:SLQT)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Insurance (General)</t>
+        </is>
+      </c>
+      <c r="D16">
+        <v>0.344</v>
+      </c>
+      <c r="G16">
+        <v>0.08368927821617317</v>
+      </c>
+      <c r="H16">
+        <v>0.05835082892926953</v>
+      </c>
+      <c r="I16">
+        <v>0.05585086468281561</v>
+      </c>
+      <c r="J16">
+        <v>0.05585086468281561</v>
+      </c>
+      <c r="K16">
+        <v>-47.6</v>
+      </c>
+      <c r="L16">
+        <v>-0.03446029103018895</v>
+      </c>
+      <c r="M16">
+        <v>3.94</v>
+      </c>
+      <c r="N16">
+        <v>0.006175548589341693</v>
+      </c>
+      <c r="O16">
+        <v>-0.08277310924369748</v>
+      </c>
+      <c r="P16">
+        <v>-0</v>
+      </c>
+      <c r="Q16">
+        <v>-0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>3.94</v>
+      </c>
+      <c r="T16">
+        <v>1</v>
+      </c>
+      <c r="U16">
+        <v>10.4</v>
+      </c>
+      <c r="V16">
+        <v>0.01630094043887147</v>
+      </c>
+      <c r="W16">
+        <v>-0.1502999684243764</v>
+      </c>
+      <c r="X16">
+        <v>0.09527198090546721</v>
+      </c>
+      <c r="Y16">
+        <v>-0.2455719493298436</v>
+      </c>
+      <c r="Z16">
+        <v>1.434050094267685</v>
+      </c>
+      <c r="AA16">
+        <v>0.08009293776332344</v>
+      </c>
+      <c r="AB16">
+        <v>0.09194056569990466</v>
+      </c>
+      <c r="AC16">
+        <v>-0.01184762793658123</v>
+      </c>
+      <c r="AD16">
+        <v>681.9</v>
+      </c>
+      <c r="AE16">
+        <v>28.81600306813395</v>
+      </c>
+      <c r="AF16">
+        <v>710.7160030681339</v>
+      </c>
+      <c r="AG16">
+        <v>700.3160030681339</v>
+      </c>
+      <c r="AH16">
+        <v>0.5269574924975738</v>
+      </c>
+      <c r="AI16">
+        <v>0.7251345767677744</v>
+      </c>
+      <c r="AJ16">
+        <v>0.5232814981384338</v>
+      </c>
+      <c r="AK16">
+        <v>0.7221867029649592</v>
+      </c>
+      <c r="AL16">
+        <v>97.8</v>
+      </c>
+      <c r="AM16">
+        <v>95.2</v>
+      </c>
+      <c r="AN16">
+        <v>6.908114679363793</v>
+      </c>
+      <c r="AO16">
+        <v>0.7668711656441718</v>
+      </c>
+      <c r="AP16">
+        <v>7.0946814210124</v>
+      </c>
+      <c r="AQ16">
+        <v>0.7878151260504201</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>eHealth, Inc. (NasdaqGS:EHTH)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Insurance (General)</t>
+        </is>
+      </c>
+      <c r="D17">
+        <v>0.065</v>
+      </c>
+      <c r="G17">
+        <v>0.005162400516240049</v>
+      </c>
+      <c r="H17">
+        <v>-0.05700150570015057</v>
+      </c>
+      <c r="I17">
+        <v>-0.03906704943714328</v>
+      </c>
+      <c r="J17">
+        <v>-0.03906704943714328</v>
+      </c>
+      <c r="K17">
+        <v>-35.2</v>
+      </c>
+      <c r="L17">
+        <v>-0.07571520757152077</v>
+      </c>
+      <c r="M17">
+        <v>3.7</v>
+      </c>
+      <c r="N17">
+        <v>0.01328068916008614</v>
+      </c>
+      <c r="O17">
+        <v>-0.1051136363636364</v>
+      </c>
+      <c r="P17">
+        <v>-0</v>
+      </c>
+      <c r="Q17">
+        <v>-0</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>3.7</v>
+      </c>
+      <c r="T17">
+        <v>1</v>
+      </c>
+      <c r="U17">
+        <v>64</v>
+      </c>
+      <c r="V17">
+        <v>0.2297200287150036</v>
+      </c>
+      <c r="W17">
+        <v>-0.06290207290922087</v>
+      </c>
+      <c r="X17">
+        <v>0.08022751005173041</v>
+      </c>
+      <c r="Y17">
+        <v>-0.1431295829609513</v>
+      </c>
+      <c r="Z17">
+        <v>0.5829384074088656</v>
+      </c>
+      <c r="AA17">
+        <v>-0.02277368358105172</v>
+      </c>
+      <c r="AB17">
+        <v>0.0715483299986811</v>
+      </c>
+      <c r="AC17">
+        <v>-0.09432201357973283</v>
+      </c>
+      <c r="AD17">
+        <v>69.2</v>
+      </c>
+      <c r="AE17">
+        <v>33.81135641663956</v>
+      </c>
+      <c r="AF17">
+        <v>103.0113564166396</v>
+      </c>
+      <c r="AG17">
+        <v>39.01135641663956</v>
+      </c>
+      <c r="AH17">
+        <v>0.2699378692078879</v>
+      </c>
+      <c r="AI17">
+        <v>0.1108231284163744</v>
+      </c>
+      <c r="AJ17">
+        <v>0.1228273348181695</v>
+      </c>
+      <c r="AK17">
+        <v>0.0450731883844402</v>
+      </c>
+      <c r="AL17">
+        <v>11.4</v>
+      </c>
+      <c r="AM17">
+        <v>3.5</v>
+      </c>
+      <c r="AN17">
+        <v>-7.440860215053765</v>
+      </c>
+      <c r="AO17">
+        <v>-1.780701754385965</v>
+      </c>
+      <c r="AP17">
+        <v>-4.194769507165544</v>
+      </c>
+      <c r="AQ17">
+        <v>-5.8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Atlantic American Corporation (NasdaqGM:AAME)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Insurance (General)</t>
+        </is>
+      </c>
+      <c r="D18">
+        <v>-0.00957</v>
+      </c>
+      <c r="G18">
+        <v>0.01807423345884884</v>
+      </c>
+      <c r="H18">
+        <v>0.01807423345884884</v>
+      </c>
+      <c r="I18">
+        <v>-0.02661134243053524</v>
+      </c>
+      <c r="J18">
+        <v>-0.02661134243053524</v>
+      </c>
+      <c r="K18">
+        <v>-6.91</v>
+      </c>
+      <c r="L18">
+        <v>-0.0371705217859064</v>
+      </c>
+      <c r="M18">
+        <v>0.414</v>
+      </c>
+      <c r="N18">
+        <v>0.01318471337579618</v>
+      </c>
+      <c r="O18">
+        <v>-0.05991316931982633</v>
+      </c>
+      <c r="P18">
+        <v>0.407</v>
+      </c>
+      <c r="Q18">
+        <v>0.01296178343949045</v>
+      </c>
+      <c r="R18">
+        <v>-0.05890014471780029</v>
+      </c>
+      <c r="S18">
+        <v>0.007000000000000006</v>
+      </c>
+      <c r="T18">
+        <v>0.01690821256038649</v>
+      </c>
+      <c r="U18">
+        <v>23</v>
+      </c>
+      <c r="V18">
+        <v>0.7324840764331211</v>
+      </c>
+      <c r="W18">
+        <v>-0.07001013171225937</v>
+      </c>
+      <c r="X18">
+        <v>0.09888131752652371</v>
+      </c>
+      <c r="Y18">
+        <v>-0.1688914492387831</v>
+      </c>
+      <c r="Z18">
+        <v>1.624428570485104</v>
+      </c>
+      <c r="AA18">
+        <v>-0.04322822494312396</v>
+      </c>
+      <c r="AB18">
+        <v>0.066515665287632</v>
+      </c>
+      <c r="AC18">
+        <v>-0.109743890230756</v>
+      </c>
+      <c r="AD18">
+        <v>37.8</v>
+      </c>
+      <c r="AE18">
+        <v>2.785242789182508</v>
+      </c>
+      <c r="AF18">
+        <v>40.58524278918251</v>
+      </c>
+      <c r="AG18">
+        <v>17.58524278918251</v>
+      </c>
+      <c r="AH18">
+        <v>0.5637994846810659</v>
+      </c>
+      <c r="AI18">
+        <v>0.2772495506779434</v>
+      </c>
+      <c r="AJ18">
+        <v>0.3589906222342106</v>
+      </c>
+      <c r="AK18">
+        <v>0.1425230634690152</v>
+      </c>
+      <c r="AL18">
+        <v>3.45</v>
+      </c>
+      <c r="AM18">
+        <v>3.45</v>
+      </c>
+      <c r="AN18">
+        <v>-9.545454545454545</v>
+      </c>
+      <c r="AO18">
+        <v>-1.582608695652174</v>
+      </c>
+      <c r="AP18">
+        <v>-4.440717876056189</v>
+      </c>
+      <c r="AQ18">
+        <v>-1.582608695652174</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>GoHealth, Inc. (NasdaqCM:GOCO)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Insurance (General)</t>
+        </is>
+      </c>
+      <c r="F19">
+        <v>0.2</v>
+      </c>
+      <c r="G19">
+        <v>0.101238164603059</v>
+      </c>
+      <c r="H19">
+        <v>0.04224326292789512</v>
+      </c>
+      <c r="I19">
+        <v>-0.08913385744651509</v>
+      </c>
+      <c r="J19">
+        <v>-0.08913385744651509</v>
+      </c>
+      <c r="K19">
+        <v>-29.7</v>
+      </c>
+      <c r="L19">
+        <v>-0.04326292789512017</v>
+      </c>
+      <c r="M19">
+        <v>1.7</v>
+      </c>
+      <c r="N19">
+        <v>0.01253687315634218</v>
+      </c>
+      <c r="O19">
+        <v>-0.05723905723905724</v>
+      </c>
+      <c r="P19">
+        <v>-0</v>
+      </c>
+      <c r="Q19">
+        <v>-0</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>1.7</v>
+      </c>
+      <c r="T19">
+        <v>1</v>
+      </c>
+      <c r="U19">
+        <v>35.5</v>
+      </c>
+      <c r="V19">
+        <v>0.2617994100294985</v>
+      </c>
+      <c r="W19">
+        <v>-0.1303203159280386</v>
+      </c>
+      <c r="X19">
+        <v>0.1516003106546208</v>
+      </c>
+      <c r="Y19">
+        <v>-0.2819206265826594</v>
+      </c>
+      <c r="Z19">
+        <v>0.8630856216311279</v>
+      </c>
+      <c r="AA19">
+        <v>-0.07693015076260581</v>
+      </c>
+      <c r="AB19">
+        <v>0.06920064424138621</v>
+      </c>
+      <c r="AC19">
+        <v>-0.146130795003992</v>
+      </c>
+      <c r="AD19">
+        <v>481.3</v>
+      </c>
+      <c r="AE19">
+        <v>47.60196568516304</v>
+      </c>
+      <c r="AF19">
+        <v>528.9019656851631</v>
+      </c>
+      <c r="AG19">
+        <v>493.4019656851631</v>
+      </c>
+      <c r="AH19">
+        <v>0.7959373982284855</v>
+      </c>
+      <c r="AI19">
+        <v>0.5710438816591206</v>
+      </c>
+      <c r="AJ19">
+        <v>0.7844203875383874</v>
+      </c>
+      <c r="AK19">
+        <v>0.5539473187371029</v>
+      </c>
+      <c r="AL19">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="AM19">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="AN19">
+        <v>10.3661425802283</v>
+      </c>
+      <c r="AO19">
+        <v>-0.8422496570644717</v>
+      </c>
+      <c r="AP19">
+        <v>10.62679228268712</v>
+      </c>
+      <c r="AQ19">
+        <v>-0.8422496570644717</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Reliance Global Group, Inc. (NasdaqCM:RELI)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Insurance (General)</t>
+        </is>
+      </c>
+      <c r="G20">
+        <v>-0.1390070921985816</v>
+      </c>
+      <c r="H20">
+        <v>-0.1390070921985816</v>
+      </c>
+      <c r="I20">
+        <v>-0.2914518711223494</v>
+      </c>
+      <c r="J20">
+        <v>-0.2914518711223494</v>
+      </c>
+      <c r="K20">
+        <v>-16.7</v>
+      </c>
+      <c r="L20">
+        <v>-1.184397163120567</v>
+      </c>
+      <c r="M20">
+        <v>-0</v>
+      </c>
+      <c r="N20">
+        <v>-0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>-0</v>
+      </c>
+      <c r="Q20">
+        <v>-0</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>0.925</v>
+      </c>
+      <c r="V20">
+        <v>0.2092760180995475</v>
+      </c>
+      <c r="W20">
+        <v>-1.201438848920863</v>
+      </c>
+      <c r="X20">
+        <v>0.1328825309860607</v>
+      </c>
+      <c r="Y20">
+        <v>-1.334321379906924</v>
+      </c>
+      <c r="Z20">
+        <v>1.168441449137468</v>
+      </c>
+      <c r="AA20">
+        <v>-0.3405444466480245</v>
+      </c>
+      <c r="AB20">
+        <v>0.1000035573397641</v>
+      </c>
+      <c r="AC20">
+        <v>-0.4405480039877886</v>
+      </c>
+      <c r="AD20">
+        <v>12.5</v>
+      </c>
+      <c r="AE20">
+        <v>0.6473569141256338</v>
+      </c>
+      <c r="AF20">
+        <v>13.14735691412563</v>
+      </c>
+      <c r="AG20">
+        <v>12.22235691412563</v>
+      </c>
+      <c r="AH20">
+        <v>0.7483969830176361</v>
+      </c>
+      <c r="AI20">
+        <v>0.8233896808866803</v>
+      </c>
+      <c r="AJ20">
+        <v>0.734412618188208</v>
+      </c>
+      <c r="AK20">
+        <v>0.8125293784678211</v>
+      </c>
+      <c r="AL20">
+        <v>1.61</v>
+      </c>
+      <c r="AM20">
+        <v>1.61</v>
+      </c>
+      <c r="AN20">
+        <v>-6.544502617801047</v>
+      </c>
+      <c r="AO20">
+        <v>-2.670807453416149</v>
+      </c>
+      <c r="AP20">
+        <v>-6.399139745615515</v>
+      </c>
+      <c r="AQ20">
+        <v>-2.670807453416149</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Hippo Holdings Inc. (NYSE:HIPO)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Insurance (General)</t>
+        </is>
+      </c>
+      <c r="G21">
+        <v>-0.7502240812668061</v>
+      </c>
+      <c r="H21">
+        <v>-0.7502240812668061</v>
+      </c>
+      <c r="I21">
+        <v>-0.3381928849304961</v>
+      </c>
+      <c r="J21">
+        <v>-0.3381928849304961</v>
+      </c>
+      <c r="K21">
+        <v>-127</v>
+      </c>
+      <c r="L21">
+        <v>-0.3794442784583209</v>
+      </c>
+      <c r="M21">
+        <v>7</v>
+      </c>
+      <c r="N21">
+        <v>0.01073454991565711</v>
+      </c>
+      <c r="O21">
+        <v>-0.05511811023622047</v>
+      </c>
+      <c r="P21">
+        <v>-0</v>
+      </c>
+      <c r="Q21">
+        <v>-0</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>7</v>
+      </c>
+      <c r="T21">
+        <v>1</v>
+      </c>
+      <c r="U21">
+        <v>191.2</v>
+      </c>
+      <c r="V21">
+        <v>0.2932065634105198</v>
+      </c>
+      <c r="W21">
+        <v>-0.3120393120393121</v>
+      </c>
+      <c r="X21">
+        <v>0.07318607394289618</v>
+      </c>
+      <c r="Y21">
+        <v>-0.3852253859822082</v>
+      </c>
+      <c r="Z21">
+        <v>1.738107245867949</v>
+      </c>
+      <c r="AA21">
+        <v>-0.5878155037986806</v>
+      </c>
+      <c r="AB21">
+        <v>0.07265955529760915</v>
+      </c>
+      <c r="AC21">
+        <v>-0.6604750590962898</v>
+      </c>
+      <c r="AD21">
+        <v>0</v>
+      </c>
+      <c r="AE21">
+        <v>13.96579293118518</v>
+      </c>
+      <c r="AF21">
+        <v>13.96579293118518</v>
+      </c>
+      <c r="AG21">
+        <v>-177.2342070688148</v>
+      </c>
+      <c r="AH21">
+        <v>0.0209675877059011</v>
+      </c>
+      <c r="AI21">
+        <v>0.04059047199143801</v>
+      </c>
+      <c r="AJ21">
+        <v>-0.3732300993398751</v>
+      </c>
+      <c r="AK21">
+        <v>-1.159410510817154</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>0</v>
+      </c>
+      <c r="AN21">
+        <v>-0</v>
+      </c>
+      <c r="AP21">
+        <v>1.71075489448663</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Marpai, Inc. (OTCPK:MRAI)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Insurance (General)</t>
+        </is>
+      </c>
+      <c r="G22">
+        <v>-0.8203630363036303</v>
+      </c>
+      <c r="H22">
+        <v>-0.8217821782178217</v>
+      </c>
+      <c r="I22">
+        <v>-0.5151502546572948</v>
+      </c>
+      <c r="J22">
+        <v>-0.5151502546572948</v>
+      </c>
+      <c r="K22">
+        <v>-26</v>
+      </c>
+      <c r="L22">
+        <v>-0.858085808580858</v>
+      </c>
+      <c r="M22">
+        <v>-0</v>
+      </c>
+      <c r="N22">
+        <v>-0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>-0</v>
+      </c>
+      <c r="Q22">
+        <v>-0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0.83</v>
+      </c>
+      <c r="V22">
+        <v>0.0633587786259542</v>
+      </c>
+      <c r="W22">
+        <v>2.813852813852814</v>
+      </c>
+      <c r="X22">
+        <v>0.1201118586487207</v>
+      </c>
+      <c r="Y22">
+        <v>2.693740955204093</v>
+      </c>
+      <c r="Z22">
+        <v>4.816968257664866</v>
+      </c>
+      <c r="AA22">
+        <v>-1</v>
+      </c>
+      <c r="AB22">
+        <v>0.06631356007192862</v>
+      </c>
+      <c r="AC22">
+        <v>-1.066313560071929</v>
+      </c>
+      <c r="AD22">
+        <v>26.1</v>
+      </c>
+      <c r="AE22">
+        <v>4.590263580580165</v>
+      </c>
+      <c r="AF22">
+        <v>30.69026358058017</v>
+      </c>
+      <c r="AG22">
+        <v>29.86026358058017</v>
+      </c>
+      <c r="AH22">
+        <v>0.7008467424295316</v>
+      </c>
+      <c r="AI22">
+        <v>9.931276986676457</v>
+      </c>
+      <c r="AJ22">
+        <v>0.6950670478213326</v>
+      </c>
+      <c r="AK22">
+        <v>13.21096523305287</v>
+      </c>
+      <c r="AL22">
+        <v>2.32</v>
+      </c>
+      <c r="AM22">
+        <v>2.32</v>
+      </c>
+      <c r="AN22">
+        <v>-1.906361843546856</v>
+      </c>
+      <c r="AO22">
+        <v>-6.724137931034483</v>
+      </c>
+      <c r="AP22">
+        <v>-2.181014066217235</v>
+      </c>
+      <c r="AQ22">
+        <v>-6.724137931034483</v>
       </c>
     </row>
   </sheetData>
